--- a/weight/bathroom-scale.xlsx
+++ b/weight/bathroom-scale.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\lucent\health-data\weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F054D4D5-75EB-404C-932A-6AFAFA18376B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029A4F5-1BCB-4286-AC3C-3F8CAC99E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26190" yWindow="375" windowWidth="19110" windowHeight="20505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="nweest-weightgurus" sheetId="1" r:id="rId1"/>
+    <sheet name="weight" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3181,8 +3181,8 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mmm\ dd\ yyyy\ hh:mm:ss\ AM/PM\ "/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="168" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -3683,9 +3683,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3802,7 +3802,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'nweest-weightgurus'!$B$1</c:f>
+              <c:f>weight!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3825,10 +3825,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'nweest-weightgurus'!$A$2:$A$1393</c:f>
+              <c:f>weight!$A$2:$A$1402</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1392"/>
+                <c:ptCount val="1401"/>
                 <c:pt idx="0">
                   <c:v>36297</c:v>
                 </c:pt>
@@ -8004,16 +8004,43 @@
                 </c:pt>
                 <c:pt idx="1391" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@">
                   <c:v>45560.453634259262</c:v>
+                </c:pt>
+                <c:pt idx="1392">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="1393">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="1394">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="1395">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="1396">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="1397">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="1398">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="1399">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="1400">
+                  <c:v>45575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'nweest-weightgurus'!$B$2:$B$1393</c:f>
+              <c:f>weight!$B$2:$B$1402</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="1392"/>
+                <c:ptCount val="1401"/>
                 <c:pt idx="0">
                   <c:v>217</c:v>
                 </c:pt>
@@ -12189,6 +12216,33 @@
                 </c:pt>
                 <c:pt idx="1391" formatCode="General">
                   <c:v>227.1</c:v>
+                </c:pt>
+                <c:pt idx="1392" formatCode="General">
+                  <c:v>226.3</c:v>
+                </c:pt>
+                <c:pt idx="1393" formatCode="General">
+                  <c:v>226.3</c:v>
+                </c:pt>
+                <c:pt idx="1394" formatCode="General">
+                  <c:v>226.1</c:v>
+                </c:pt>
+                <c:pt idx="1395" formatCode="General">
+                  <c:v>227.1</c:v>
+                </c:pt>
+                <c:pt idx="1396" formatCode="General">
+                  <c:v>226.7</c:v>
+                </c:pt>
+                <c:pt idx="1397" formatCode="General">
+                  <c:v>226.2</c:v>
+                </c:pt>
+                <c:pt idx="1398" formatCode="General">
+                  <c:v>226.3</c:v>
+                </c:pt>
+                <c:pt idx="1399" formatCode="General">
+                  <c:v>227.8</c:v>
+                </c:pt>
+                <c:pt idx="1400" formatCode="General">
+                  <c:v>225.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12470,7 +12524,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'nweest-weightgurus'!$A$352:$A$439</c:f>
+              <c:f>weight!$A$352:$A$439</c:f>
               <c:numCache>
                 <c:formatCode>[$-409]m/d/yy\ h:mm\ AM/PM;@</c:formatCode>
                 <c:ptCount val="88"/>
@@ -12743,7 +12797,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'nweest-weightgurus'!$B$352:$B$439</c:f>
+              <c:f>weight!$B$352:$B$439</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="88"/>
@@ -14309,13 +14363,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>476249</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>119061</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
@@ -14678,7 +14732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1393"/>
+  <dimension ref="A1:F1402"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="8" bestFit="1" customWidth="1"/>
@@ -18516,7 +18570,7 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="10">
-        <f>DATEVALUE(MID(F352,5,2) &amp; "-" &amp; LEFT(F352,3) &amp; "-" &amp; MID(F352,8,4)) + TIMEVALUE(MID(F352,13,11))</f>
+        <f t="shared" ref="A352:A415" si="0">DATEVALUE(MID(F352,5,2) &amp; "-" &amp; LEFT(F352,3) &amp; "-" &amp; MID(F352,8,4)) + TIMEVALUE(MID(F352,13,11))</f>
         <v>43761.672152777777</v>
       </c>
       <c r="B352">
@@ -18535,7 +18589,7 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="10">
-        <f>DATEVALUE(MID(F353,5,2) &amp; "-" &amp; LEFT(F353,3) &amp; "-" &amp; MID(F353,8,4)) + TIMEVALUE(MID(F353,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43762.404710648145</v>
       </c>
       <c r="B353">
@@ -18556,7 +18610,7 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="10">
-        <f>DATEVALUE(MID(F354,5,2) &amp; "-" &amp; LEFT(F354,3) &amp; "-" &amp; MID(F354,8,4)) + TIMEVALUE(MID(F354,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43762.439953703702</v>
       </c>
       <c r="B354">
@@ -18577,7 +18631,7 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="10">
-        <f>DATEVALUE(MID(F355,5,2) &amp; "-" &amp; LEFT(F355,3) &amp; "-" &amp; MID(F355,8,4)) + TIMEVALUE(MID(F355,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43762.473136574074</v>
       </c>
       <c r="B355">
@@ -18598,7 +18652,7 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="10">
-        <f>DATEVALUE(MID(F356,5,2) &amp; "-" &amp; LEFT(F356,3) &amp; "-" &amp; MID(F356,8,4)) + TIMEVALUE(MID(F356,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43764.48101851852</v>
       </c>
       <c r="B356">
@@ -18619,7 +18673,7 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="10">
-        <f>DATEVALUE(MID(F357,5,2) &amp; "-" &amp; LEFT(F357,3) &amp; "-" &amp; MID(F357,8,4)) + TIMEVALUE(MID(F357,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43764.681932870371</v>
       </c>
       <c r="B357">
@@ -18640,7 +18694,7 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="10">
-        <f>DATEVALUE(MID(F358,5,2) &amp; "-" &amp; LEFT(F358,3) &amp; "-" &amp; MID(F358,8,4)) + TIMEVALUE(MID(F358,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43764.83084490741</v>
       </c>
       <c r="B358">
@@ -18661,7 +18715,7 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="10">
-        <f>DATEVALUE(MID(F359,5,2) &amp; "-" &amp; LEFT(F359,3) &amp; "-" &amp; MID(F359,8,4)) + TIMEVALUE(MID(F359,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43765.458715277775</v>
       </c>
       <c r="B359">
@@ -18682,7 +18736,7 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="10">
-        <f>DATEVALUE(MID(F360,5,2) &amp; "-" &amp; LEFT(F360,3) &amp; "-" &amp; MID(F360,8,4)) + TIMEVALUE(MID(F360,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43766.474166666667</v>
       </c>
       <c r="B360">
@@ -18703,7 +18757,7 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="10">
-        <f>DATEVALUE(MID(F361,5,2) &amp; "-" &amp; LEFT(F361,3) &amp; "-" &amp; MID(F361,8,4)) + TIMEVALUE(MID(F361,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43766.520358796297</v>
       </c>
       <c r="B361">
@@ -18724,7 +18778,7 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="10">
-        <f>DATEVALUE(MID(F362,5,2) &amp; "-" &amp; LEFT(F362,3) &amp; "-" &amp; MID(F362,8,4)) + TIMEVALUE(MID(F362,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43766.945300925923</v>
       </c>
       <c r="B362">
@@ -18745,7 +18799,7 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="10">
-        <f>DATEVALUE(MID(F363,5,2) &amp; "-" &amp; LEFT(F363,3) &amp; "-" &amp; MID(F363,8,4)) + TIMEVALUE(MID(F363,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43767.429432870369</v>
       </c>
       <c r="B363">
@@ -18766,7 +18820,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="10">
-        <f>DATEVALUE(MID(F364,5,2) &amp; "-" &amp; LEFT(F364,3) &amp; "-" &amp; MID(F364,8,4)) + TIMEVALUE(MID(F364,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43768.453067129631</v>
       </c>
       <c r="B364">
@@ -18787,7 +18841,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="10">
-        <f>DATEVALUE(MID(F365,5,2) &amp; "-" &amp; LEFT(F365,3) &amp; "-" &amp; MID(F365,8,4)) + TIMEVALUE(MID(F365,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43769.513784722221</v>
       </c>
       <c r="B365">
@@ -18808,7 +18862,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="10">
-        <f>DATEVALUE(MID(F366,5,2) &amp; "-" &amp; LEFT(F366,3) &amp; "-" &amp; MID(F366,8,4)) + TIMEVALUE(MID(F366,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43770.537881944445</v>
       </c>
       <c r="B366">
@@ -18829,7 +18883,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="10">
-        <f>DATEVALUE(MID(F367,5,2) &amp; "-" &amp; LEFT(F367,3) &amp; "-" &amp; MID(F367,8,4)) + TIMEVALUE(MID(F367,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43771.54996527778</v>
       </c>
       <c r="B367">
@@ -18850,7 +18904,7 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="10">
-        <f>DATEVALUE(MID(F368,5,2) &amp; "-" &amp; LEFT(F368,3) &amp; "-" &amp; MID(F368,8,4)) + TIMEVALUE(MID(F368,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43772.430787037039</v>
       </c>
       <c r="B368">
@@ -18871,7 +18925,7 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="10">
-        <f>DATEVALUE(MID(F369,5,2) &amp; "-" &amp; LEFT(F369,3) &amp; "-" &amp; MID(F369,8,4)) + TIMEVALUE(MID(F369,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43772.704155092593</v>
       </c>
       <c r="B369">
@@ -18892,7 +18946,7 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="10">
-        <f>DATEVALUE(MID(F370,5,2) &amp; "-" &amp; LEFT(F370,3) &amp; "-" &amp; MID(F370,8,4)) + TIMEVALUE(MID(F370,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43772.77884259259</v>
       </c>
       <c r="B370">
@@ -18913,7 +18967,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="10">
-        <f>DATEVALUE(MID(F371,5,2) &amp; "-" &amp; LEFT(F371,3) &amp; "-" &amp; MID(F371,8,4)) + TIMEVALUE(MID(F371,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43773.006597222222</v>
       </c>
       <c r="B371">
@@ -18934,7 +18988,7 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="10">
-        <f>DATEVALUE(MID(F372,5,2) &amp; "-" &amp; LEFT(F372,3) &amp; "-" &amp; MID(F372,8,4)) + TIMEVALUE(MID(F372,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43773.426377314812</v>
       </c>
       <c r="B372">
@@ -18955,7 +19009,7 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="10">
-        <f>DATEVALUE(MID(F373,5,2) &amp; "-" &amp; LEFT(F373,3) &amp; "-" &amp; MID(F373,8,4)) + TIMEVALUE(MID(F373,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43773.713136574072</v>
       </c>
       <c r="B373">
@@ -18976,7 +19030,7 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="10">
-        <f>DATEVALUE(MID(F374,5,2) &amp; "-" &amp; LEFT(F374,3) &amp; "-" &amp; MID(F374,8,4)) + TIMEVALUE(MID(F374,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43773.912210648145</v>
       </c>
       <c r="B374">
@@ -18997,7 +19051,7 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="10">
-        <f>DATEVALUE(MID(F375,5,2) &amp; "-" &amp; LEFT(F375,3) &amp; "-" &amp; MID(F375,8,4)) + TIMEVALUE(MID(F375,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43774.47315972222</v>
       </c>
       <c r="B375">
@@ -19018,7 +19072,7 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="10">
-        <f>DATEVALUE(MID(F376,5,2) &amp; "-" &amp; LEFT(F376,3) &amp; "-" &amp; MID(F376,8,4)) + TIMEVALUE(MID(F376,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43775.443252314813</v>
       </c>
       <c r="B376">
@@ -19039,7 +19093,7 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="10">
-        <f>DATEVALUE(MID(F377,5,2) &amp; "-" &amp; LEFT(F377,3) &amp; "-" &amp; MID(F377,8,4)) + TIMEVALUE(MID(F377,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43775.664039351854</v>
       </c>
       <c r="B377">
@@ -19060,7 +19114,7 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="10">
-        <f>DATEVALUE(MID(F378,5,2) &amp; "-" &amp; LEFT(F378,3) &amp; "-" &amp; MID(F378,8,4)) + TIMEVALUE(MID(F378,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43776.432430555556</v>
       </c>
       <c r="B378">
@@ -19081,7 +19135,7 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="10">
-        <f>DATEVALUE(MID(F379,5,2) &amp; "-" &amp; LEFT(F379,3) &amp; "-" &amp; MID(F379,8,4)) + TIMEVALUE(MID(F379,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43776.48510416667</v>
       </c>
       <c r="B379">
@@ -19102,7 +19156,7 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="10">
-        <f>DATEVALUE(MID(F380,5,2) &amp; "-" &amp; LEFT(F380,3) &amp; "-" &amp; MID(F380,8,4)) + TIMEVALUE(MID(F380,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43777.464837962965</v>
       </c>
       <c r="B380">
@@ -19123,7 +19177,7 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="10">
-        <f>DATEVALUE(MID(F381,5,2) &amp; "-" &amp; LEFT(F381,3) &amp; "-" &amp; MID(F381,8,4)) + TIMEVALUE(MID(F381,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43777.510717592595</v>
       </c>
       <c r="B381">
@@ -19144,7 +19198,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="10">
-        <f>DATEVALUE(MID(F382,5,2) &amp; "-" &amp; LEFT(F382,3) &amp; "-" &amp; MID(F382,8,4)) + TIMEVALUE(MID(F382,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43778.473240740743</v>
       </c>
       <c r="B382">
@@ -19165,7 +19219,7 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="10">
-        <f>DATEVALUE(MID(F383,5,2) &amp; "-" &amp; LEFT(F383,3) &amp; "-" &amp; MID(F383,8,4)) + TIMEVALUE(MID(F383,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43778.836354166669</v>
       </c>
       <c r="B383">
@@ -19186,7 +19240,7 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="10">
-        <f>DATEVALUE(MID(F384,5,2) &amp; "-" &amp; LEFT(F384,3) &amp; "-" &amp; MID(F384,8,4)) + TIMEVALUE(MID(F384,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.486134259256</v>
       </c>
       <c r="B384">
@@ -19207,7 +19261,7 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="10">
-        <f>DATEVALUE(MID(F385,5,2) &amp; "-" &amp; LEFT(F385,3) &amp; "-" &amp; MID(F385,8,4)) + TIMEVALUE(MID(F385,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.525625000002</v>
       </c>
       <c r="B385">
@@ -19228,7 +19282,7 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="10">
-        <f>DATEVALUE(MID(F386,5,2) &amp; "-" &amp; LEFT(F386,3) &amp; "-" &amp; MID(F386,8,4)) + TIMEVALUE(MID(F386,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.604687500003</v>
       </c>
       <c r="B386">
@@ -19249,7 +19303,7 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="10">
-        <f>DATEVALUE(MID(F387,5,2) &amp; "-" &amp; LEFT(F387,3) &amp; "-" &amp; MID(F387,8,4)) + TIMEVALUE(MID(F387,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.631354166668</v>
       </c>
       <c r="B387">
@@ -19270,7 +19324,7 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="10">
-        <f>DATEVALUE(MID(F388,5,2) &amp; "-" &amp; LEFT(F388,3) &amp; "-" &amp; MID(F388,8,4)) + TIMEVALUE(MID(F388,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.681886574072</v>
       </c>
       <c r="B388">
@@ -19291,7 +19345,7 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="10">
-        <f>DATEVALUE(MID(F389,5,2) &amp; "-" &amp; LEFT(F389,3) &amp; "-" &amp; MID(F389,8,4)) + TIMEVALUE(MID(F389,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.908888888887</v>
       </c>
       <c r="B389">
@@ -19312,7 +19366,7 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="10">
-        <f>DATEVALUE(MID(F390,5,2) &amp; "-" &amp; LEFT(F390,3) &amp; "-" &amp; MID(F390,8,4)) + TIMEVALUE(MID(F390,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43779.947731481479</v>
       </c>
       <c r="B390">
@@ -19333,7 +19387,7 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="10">
-        <f>DATEVALUE(MID(F391,5,2) &amp; "-" &amp; LEFT(F391,3) &amp; "-" &amp; MID(F391,8,4)) + TIMEVALUE(MID(F391,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43780.061956018515</v>
       </c>
       <c r="B391">
@@ -19354,7 +19408,7 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="10">
-        <f>DATEVALUE(MID(F392,5,2) &amp; "-" &amp; LEFT(F392,3) &amp; "-" &amp; MID(F392,8,4)) + TIMEVALUE(MID(F392,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43780.446168981478</v>
       </c>
       <c r="B392">
@@ -19375,7 +19429,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="10">
-        <f>DATEVALUE(MID(F393,5,2) &amp; "-" &amp; LEFT(F393,3) &amp; "-" &amp; MID(F393,8,4)) + TIMEVALUE(MID(F393,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43780.454201388886</v>
       </c>
       <c r="B393">
@@ -19396,7 +19450,7 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="10">
-        <f>DATEVALUE(MID(F394,5,2) &amp; "-" &amp; LEFT(F394,3) &amp; "-" &amp; MID(F394,8,4)) + TIMEVALUE(MID(F394,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43780.72761574074</v>
       </c>
       <c r="B394">
@@ -19417,7 +19471,7 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="10">
-        <f>DATEVALUE(MID(F395,5,2) &amp; "-" &amp; LEFT(F395,3) &amp; "-" &amp; MID(F395,8,4)) + TIMEVALUE(MID(F395,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43781.47928240741</v>
       </c>
       <c r="B395">
@@ -19438,7 +19492,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="10">
-        <f>DATEVALUE(MID(F396,5,2) &amp; "-" &amp; LEFT(F396,3) &amp; "-" &amp; MID(F396,8,4)) + TIMEVALUE(MID(F396,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43783.476956018516</v>
       </c>
       <c r="B396">
@@ -19459,7 +19513,7 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="10">
-        <f>DATEVALUE(MID(F397,5,2) &amp; "-" &amp; LEFT(F397,3) &amp; "-" &amp; MID(F397,8,4)) + TIMEVALUE(MID(F397,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43784.496504629627</v>
       </c>
       <c r="B397">
@@ -19480,7 +19534,7 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="10">
-        <f>DATEVALUE(MID(F398,5,2) &amp; "-" &amp; LEFT(F398,3) &amp; "-" &amp; MID(F398,8,4)) + TIMEVALUE(MID(F398,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43785.877754629626</v>
       </c>
       <c r="B398">
@@ -19501,7 +19555,7 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="10">
-        <f>DATEVALUE(MID(F399,5,2) &amp; "-" &amp; LEFT(F399,3) &amp; "-" &amp; MID(F399,8,4)) + TIMEVALUE(MID(F399,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43786.477268518516</v>
       </c>
       <c r="B399">
@@ -19522,7 +19576,7 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="10">
-        <f>DATEVALUE(MID(F400,5,2) &amp; "-" &amp; LEFT(F400,3) &amp; "-" &amp; MID(F400,8,4)) + TIMEVALUE(MID(F400,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43787.000833333332</v>
       </c>
       <c r="B400">
@@ -19543,7 +19597,7 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="10">
-        <f>DATEVALUE(MID(F401,5,2) &amp; "-" &amp; LEFT(F401,3) &amp; "-" &amp; MID(F401,8,4)) + TIMEVALUE(MID(F401,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43787.397916666669</v>
       </c>
       <c r="B401">
@@ -19564,7 +19618,7 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="10">
-        <f>DATEVALUE(MID(F402,5,2) &amp; "-" &amp; LEFT(F402,3) &amp; "-" &amp; MID(F402,8,4)) + TIMEVALUE(MID(F402,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43788.453553240739</v>
       </c>
       <c r="B402">
@@ -19585,7 +19639,7 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="10">
-        <f>DATEVALUE(MID(F403,5,2) &amp; "-" &amp; LEFT(F403,3) &amp; "-" &amp; MID(F403,8,4)) + TIMEVALUE(MID(F403,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43789.546469907407</v>
       </c>
       <c r="B403">
@@ -19606,7 +19660,7 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="10">
-        <f>DATEVALUE(MID(F404,5,2) &amp; "-" &amp; LEFT(F404,3) &amp; "-" &amp; MID(F404,8,4)) + TIMEVALUE(MID(F404,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43790.419583333336</v>
       </c>
       <c r="B404">
@@ -19627,7 +19681,7 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="10">
-        <f>DATEVALUE(MID(F405,5,2) &amp; "-" &amp; LEFT(F405,3) &amp; "-" &amp; MID(F405,8,4)) + TIMEVALUE(MID(F405,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43791.431840277779</v>
       </c>
       <c r="B405">
@@ -19648,7 +19702,7 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="10">
-        <f>DATEVALUE(MID(F406,5,2) &amp; "-" &amp; LEFT(F406,3) &amp; "-" &amp; MID(F406,8,4)) + TIMEVALUE(MID(F406,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43791.465358796297</v>
       </c>
       <c r="B406">
@@ -19669,7 +19723,7 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="10">
-        <f>DATEVALUE(MID(F407,5,2) &amp; "-" &amp; LEFT(F407,3) &amp; "-" &amp; MID(F407,8,4)) + TIMEVALUE(MID(F407,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43791.490185185183</v>
       </c>
       <c r="B407">
@@ -19690,7 +19744,7 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="10">
-        <f>DATEVALUE(MID(F408,5,2) &amp; "-" &amp; LEFT(F408,3) &amp; "-" &amp; MID(F408,8,4)) + TIMEVALUE(MID(F408,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43792.516736111109</v>
       </c>
       <c r="B408">
@@ -19711,7 +19765,7 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="10">
-        <f>DATEVALUE(MID(F409,5,2) &amp; "-" &amp; LEFT(F409,3) &amp; "-" &amp; MID(F409,8,4)) + TIMEVALUE(MID(F409,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43792.639432870368</v>
       </c>
       <c r="B409">
@@ -19732,7 +19786,7 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="10">
-        <f>DATEVALUE(MID(F410,5,2) &amp; "-" &amp; LEFT(F410,3) &amp; "-" &amp; MID(F410,8,4)) + TIMEVALUE(MID(F410,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43792.909351851849</v>
       </c>
       <c r="B410">
@@ -19753,7 +19807,7 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="10">
-        <f>DATEVALUE(MID(F411,5,2) &amp; "-" &amp; LEFT(F411,3) &amp; "-" &amp; MID(F411,8,4)) + TIMEVALUE(MID(F411,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43792.963750000003</v>
       </c>
       <c r="B411">
@@ -19774,7 +19828,7 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="10">
-        <f>DATEVALUE(MID(F412,5,2) &amp; "-" &amp; LEFT(F412,3) &amp; "-" &amp; MID(F412,8,4)) + TIMEVALUE(MID(F412,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43793.501400462963</v>
       </c>
       <c r="B412">
@@ -19795,7 +19849,7 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="10">
-        <f>DATEVALUE(MID(F413,5,2) &amp; "-" &amp; LEFT(F413,3) &amp; "-" &amp; MID(F413,8,4)) + TIMEVALUE(MID(F413,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43793.542928240742</v>
       </c>
       <c r="B413">
@@ -19816,7 +19870,7 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="10">
-        <f>DATEVALUE(MID(F414,5,2) &amp; "-" &amp; LEFT(F414,3) &amp; "-" &amp; MID(F414,8,4)) + TIMEVALUE(MID(F414,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43793.893738425926</v>
       </c>
       <c r="B414">
@@ -19837,7 +19891,7 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="10">
-        <f>DATEVALUE(MID(F415,5,2) &amp; "-" &amp; LEFT(F415,3) &amp; "-" &amp; MID(F415,8,4)) + TIMEVALUE(MID(F415,13,11))</f>
+        <f t="shared" si="0"/>
         <v>43793.932256944441</v>
       </c>
       <c r="B415">
@@ -19858,7 +19912,7 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="10">
-        <f>DATEVALUE(MID(F416,5,2) &amp; "-" &amp; LEFT(F416,3) &amp; "-" &amp; MID(F416,8,4)) + TIMEVALUE(MID(F416,13,11))</f>
+        <f t="shared" ref="A416:A479" si="1">DATEVALUE(MID(F416,5,2) &amp; "-" &amp; LEFT(F416,3) &amp; "-" &amp; MID(F416,8,4)) + TIMEVALUE(MID(F416,13,11))</f>
         <v>43794.019976851851</v>
       </c>
       <c r="B416">
@@ -19879,7 +19933,7 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="10">
-        <f>DATEVALUE(MID(F417,5,2) &amp; "-" &amp; LEFT(F417,3) &amp; "-" &amp; MID(F417,8,4)) + TIMEVALUE(MID(F417,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43794.455752314818</v>
       </c>
       <c r="B417">
@@ -19900,7 +19954,7 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="10">
-        <f>DATEVALUE(MID(F418,5,2) &amp; "-" &amp; LEFT(F418,3) &amp; "-" &amp; MID(F418,8,4)) + TIMEVALUE(MID(F418,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43795.465439814812</v>
       </c>
       <c r="B418">
@@ -19921,7 +19975,7 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="10">
-        <f>DATEVALUE(MID(F419,5,2) &amp; "-" &amp; LEFT(F419,3) &amp; "-" &amp; MID(F419,8,4)) + TIMEVALUE(MID(F419,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43796.504247685189</v>
       </c>
       <c r="B419">
@@ -19942,7 +19996,7 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="10">
-        <f>DATEVALUE(MID(F420,5,2) &amp; "-" &amp; LEFT(F420,3) &amp; "-" &amp; MID(F420,8,4)) + TIMEVALUE(MID(F420,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43796.528506944444</v>
       </c>
       <c r="B420">
@@ -19963,7 +20017,7 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="10">
-        <f>DATEVALUE(MID(F421,5,2) &amp; "-" &amp; LEFT(F421,3) &amp; "-" &amp; MID(F421,8,4)) + TIMEVALUE(MID(F421,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43797.41511574074</v>
       </c>
       <c r="B421">
@@ -19984,7 +20038,7 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="10">
-        <f>DATEVALUE(MID(F422,5,2) &amp; "-" &amp; LEFT(F422,3) &amp; "-" &amp; MID(F422,8,4)) + TIMEVALUE(MID(F422,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43798.441770833335</v>
       </c>
       <c r="B422">
@@ -20005,7 +20059,7 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="10">
-        <f>DATEVALUE(MID(F423,5,2) &amp; "-" &amp; LEFT(F423,3) &amp; "-" &amp; MID(F423,8,4)) + TIMEVALUE(MID(F423,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43799.487326388888</v>
       </c>
       <c r="B423">
@@ -20026,7 +20080,7 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="10">
-        <f>DATEVALUE(MID(F424,5,2) &amp; "-" &amp; LEFT(F424,3) &amp; "-" &amp; MID(F424,8,4)) + TIMEVALUE(MID(F424,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43800.494039351855</v>
       </c>
       <c r="B424">
@@ -20047,7 +20101,7 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="10">
-        <f>DATEVALUE(MID(F425,5,2) &amp; "-" &amp; LEFT(F425,3) &amp; "-" &amp; MID(F425,8,4)) + TIMEVALUE(MID(F425,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43801.524178240739</v>
       </c>
       <c r="B425">
@@ -20068,7 +20122,7 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="10">
-        <f>DATEVALUE(MID(F426,5,2) &amp; "-" &amp; LEFT(F426,3) &amp; "-" &amp; MID(F426,8,4)) + TIMEVALUE(MID(F426,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43802.478483796294</v>
       </c>
       <c r="B426">
@@ -20089,7 +20143,7 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="10">
-        <f>DATEVALUE(MID(F427,5,2) &amp; "-" &amp; LEFT(F427,3) &amp; "-" &amp; MID(F427,8,4)) + TIMEVALUE(MID(F427,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43803.445</v>
       </c>
       <c r="B427">
@@ -20110,7 +20164,7 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="10">
-        <f>DATEVALUE(MID(F428,5,2) &amp; "-" &amp; LEFT(F428,3) &amp; "-" &amp; MID(F428,8,4)) + TIMEVALUE(MID(F428,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43804.438009259262</v>
       </c>
       <c r="B428">
@@ -20131,7 +20185,7 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="10">
-        <f>DATEVALUE(MID(F429,5,2) &amp; "-" &amp; LEFT(F429,3) &amp; "-" &amp; MID(F429,8,4)) + TIMEVALUE(MID(F429,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43804.460104166668</v>
       </c>
       <c r="B429">
@@ -20152,7 +20206,7 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="10">
-        <f>DATEVALUE(MID(F430,5,2) &amp; "-" &amp; LEFT(F430,3) &amp; "-" &amp; MID(F430,8,4)) + TIMEVALUE(MID(F430,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43805.48810185185</v>
       </c>
       <c r="B430">
@@ -20173,7 +20227,7 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="10">
-        <f>DATEVALUE(MID(F431,5,2) &amp; "-" &amp; LEFT(F431,3) &amp; "-" &amp; MID(F431,8,4)) + TIMEVALUE(MID(F431,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43808.553553240738</v>
       </c>
       <c r="B431">
@@ -20194,7 +20248,7 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="10">
-        <f>DATEVALUE(MID(F432,5,2) &amp; "-" &amp; LEFT(F432,3) &amp; "-" &amp; MID(F432,8,4)) + TIMEVALUE(MID(F432,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43813.543379629627</v>
       </c>
       <c r="B432">
@@ -20215,7 +20269,7 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="10">
-        <f>DATEVALUE(MID(F433,5,2) &amp; "-" &amp; LEFT(F433,3) &amp; "-" &amp; MID(F433,8,4)) + TIMEVALUE(MID(F433,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43814.556574074071</v>
       </c>
       <c r="B433">
@@ -20236,7 +20290,7 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="10">
-        <f>DATEVALUE(MID(F434,5,2) &amp; "-" &amp; LEFT(F434,3) &amp; "-" &amp; MID(F434,8,4)) + TIMEVALUE(MID(F434,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43815.457118055558</v>
       </c>
       <c r="B434">
@@ -20257,7 +20311,7 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="10">
-        <f>DATEVALUE(MID(F435,5,2) &amp; "-" &amp; LEFT(F435,3) &amp; "-" &amp; MID(F435,8,4)) + TIMEVALUE(MID(F435,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43816.561527777776</v>
       </c>
       <c r="B435">
@@ -20278,7 +20332,7 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="10">
-        <f>DATEVALUE(MID(F436,5,2) &amp; "-" &amp; LEFT(F436,3) &amp; "-" &amp; MID(F436,8,4)) + TIMEVALUE(MID(F436,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43820.53565972222</v>
       </c>
       <c r="B436">
@@ -20299,7 +20353,7 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="10">
-        <f>DATEVALUE(MID(F437,5,2) &amp; "-" &amp; LEFT(F437,3) &amp; "-" &amp; MID(F437,8,4)) + TIMEVALUE(MID(F437,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43822.492569444446</v>
       </c>
       <c r="B437">
@@ -20320,7 +20374,7 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="10">
-        <f>DATEVALUE(MID(F438,5,2) &amp; "-" &amp; LEFT(F438,3) &amp; "-" &amp; MID(F438,8,4)) + TIMEVALUE(MID(F438,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43824.500844907408</v>
       </c>
       <c r="B438">
@@ -20341,7 +20395,7 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="10">
-        <f>DATEVALUE(MID(F439,5,2) &amp; "-" &amp; LEFT(F439,3) &amp; "-" &amp; MID(F439,8,4)) + TIMEVALUE(MID(F439,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43840.445219907408</v>
       </c>
       <c r="B439">
@@ -20362,7 +20416,7 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="10">
-        <f>DATEVALUE(MID(F440,5,2) &amp; "-" &amp; LEFT(F440,3) &amp; "-" &amp; MID(F440,8,4)) + TIMEVALUE(MID(F440,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43847.452013888891</v>
       </c>
       <c r="B440">
@@ -20383,7 +20437,7 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="10">
-        <f>DATEVALUE(MID(F441,5,2) &amp; "-" &amp; LEFT(F441,3) &amp; "-" &amp; MID(F441,8,4)) + TIMEVALUE(MID(F441,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43860.494155092594</v>
       </c>
       <c r="B441">
@@ -20404,7 +20458,7 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="10">
-        <f>DATEVALUE(MID(F442,5,2) &amp; "-" &amp; LEFT(F442,3) &amp; "-" &amp; MID(F442,8,4)) + TIMEVALUE(MID(F442,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43861.426701388889</v>
       </c>
       <c r="B442">
@@ -20425,7 +20479,7 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="10">
-        <f>DATEVALUE(MID(F443,5,2) &amp; "-" &amp; LEFT(F443,3) &amp; "-" &amp; MID(F443,8,4)) + TIMEVALUE(MID(F443,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43862.526122685187</v>
       </c>
       <c r="B443">
@@ -20446,7 +20500,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="10">
-        <f>DATEVALUE(MID(F444,5,2) &amp; "-" &amp; LEFT(F444,3) &amp; "-" &amp; MID(F444,8,4)) + TIMEVALUE(MID(F444,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43862.545659722222</v>
       </c>
       <c r="B444">
@@ -20467,7 +20521,7 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="10">
-        <f>DATEVALUE(MID(F445,5,2) &amp; "-" &amp; LEFT(F445,3) &amp; "-" &amp; MID(F445,8,4)) + TIMEVALUE(MID(F445,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43865.449247685188</v>
       </c>
       <c r="B445">
@@ -20488,7 +20542,7 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="10">
-        <f>DATEVALUE(MID(F446,5,2) &amp; "-" &amp; LEFT(F446,3) &amp; "-" &amp; MID(F446,8,4)) + TIMEVALUE(MID(F446,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43866.413634259261</v>
       </c>
       <c r="B446">
@@ -20509,7 +20563,7 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="10">
-        <f>DATEVALUE(MID(F447,5,2) &amp; "-" &amp; LEFT(F447,3) &amp; "-" &amp; MID(F447,8,4)) + TIMEVALUE(MID(F447,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43867.441168981481</v>
       </c>
       <c r="B447">
@@ -20530,7 +20584,7 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="10">
-        <f>DATEVALUE(MID(F448,5,2) &amp; "-" &amp; LEFT(F448,3) &amp; "-" &amp; MID(F448,8,4)) + TIMEVALUE(MID(F448,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43867.464375000003</v>
       </c>
       <c r="B448">
@@ -20551,7 +20605,7 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="10">
-        <f>DATEVALUE(MID(F449,5,2) &amp; "-" &amp; LEFT(F449,3) &amp; "-" &amp; MID(F449,8,4)) + TIMEVALUE(MID(F449,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43867.52239583333</v>
       </c>
       <c r="B449">
@@ -20572,7 +20626,7 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="10">
-        <f>DATEVALUE(MID(F450,5,2) &amp; "-" &amp; LEFT(F450,3) &amp; "-" &amp; MID(F450,8,4)) + TIMEVALUE(MID(F450,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43868.519826388889</v>
       </c>
       <c r="B450">
@@ -20593,7 +20647,7 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="10">
-        <f>DATEVALUE(MID(F451,5,2) &amp; "-" &amp; LEFT(F451,3) &amp; "-" &amp; MID(F451,8,4)) + TIMEVALUE(MID(F451,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43869.611678240741</v>
       </c>
       <c r="B451">
@@ -20614,7 +20668,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="10">
-        <f>DATEVALUE(MID(F452,5,2) &amp; "-" &amp; LEFT(F452,3) &amp; "-" &amp; MID(F452,8,4)) + TIMEVALUE(MID(F452,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43870.528483796297</v>
       </c>
       <c r="B452">
@@ -20635,7 +20689,7 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="10">
-        <f>DATEVALUE(MID(F453,5,2) &amp; "-" &amp; LEFT(F453,3) &amp; "-" &amp; MID(F453,8,4)) + TIMEVALUE(MID(F453,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43874.462280092594</v>
       </c>
       <c r="B453">
@@ -20656,7 +20710,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="10">
-        <f>DATEVALUE(MID(F454,5,2) &amp; "-" &amp; LEFT(F454,3) &amp; "-" &amp; MID(F454,8,4)) + TIMEVALUE(MID(F454,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43935.466631944444</v>
       </c>
       <c r="B454">
@@ -20677,7 +20731,7 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="10">
-        <f>DATEVALUE(MID(F455,5,2) &amp; "-" &amp; LEFT(F455,3) &amp; "-" &amp; MID(F455,8,4)) + TIMEVALUE(MID(F455,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43936.517488425925</v>
       </c>
       <c r="B455">
@@ -20698,7 +20752,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="10">
-        <f>DATEVALUE(MID(F456,5,2) &amp; "-" &amp; LEFT(F456,3) &amp; "-" &amp; MID(F456,8,4)) + TIMEVALUE(MID(F456,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43939.52416666667</v>
       </c>
       <c r="B456">
@@ -20719,7 +20773,7 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="10">
-        <f>DATEVALUE(MID(F457,5,2) &amp; "-" &amp; LEFT(F457,3) &amp; "-" &amp; MID(F457,8,4)) + TIMEVALUE(MID(F457,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43940.630925925929</v>
       </c>
       <c r="B457">
@@ -20740,7 +20794,7 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="10">
-        <f>DATEVALUE(MID(F458,5,2) &amp; "-" &amp; LEFT(F458,3) &amp; "-" &amp; MID(F458,8,4)) + TIMEVALUE(MID(F458,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43941.485081018516</v>
       </c>
       <c r="B458">
@@ -20761,7 +20815,7 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="10">
-        <f>DATEVALUE(MID(F459,5,2) &amp; "-" &amp; LEFT(F459,3) &amp; "-" &amp; MID(F459,8,4)) + TIMEVALUE(MID(F459,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43941.507141203707</v>
       </c>
       <c r="B459">
@@ -20782,7 +20836,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="10">
-        <f>DATEVALUE(MID(F460,5,2) &amp; "-" &amp; LEFT(F460,3) &amp; "-" &amp; MID(F460,8,4)) + TIMEVALUE(MID(F460,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43944.463495370372</v>
       </c>
       <c r="B460">
@@ -20803,7 +20857,7 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="10">
-        <f>DATEVALUE(MID(F461,5,2) &amp; "-" &amp; LEFT(F461,3) &amp; "-" &amp; MID(F461,8,4)) + TIMEVALUE(MID(F461,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43948.430925925924</v>
       </c>
       <c r="B461">
@@ -20824,7 +20878,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="10">
-        <f>DATEVALUE(MID(F462,5,2) &amp; "-" &amp; LEFT(F462,3) &amp; "-" &amp; MID(F462,8,4)) + TIMEVALUE(MID(F462,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43949.450370370374</v>
       </c>
       <c r="B462">
@@ -20845,7 +20899,7 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="10">
-        <f>DATEVALUE(MID(F463,5,2) &amp; "-" &amp; LEFT(F463,3) &amp; "-" &amp; MID(F463,8,4)) + TIMEVALUE(MID(F463,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43950.519895833335</v>
       </c>
       <c r="B463">
@@ -20866,7 +20920,7 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="10">
-        <f>DATEVALUE(MID(F464,5,2) &amp; "-" &amp; LEFT(F464,3) &amp; "-" &amp; MID(F464,8,4)) + TIMEVALUE(MID(F464,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43952.470868055556</v>
       </c>
       <c r="B464">
@@ -20887,7 +20941,7 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="10">
-        <f>DATEVALUE(MID(F465,5,2) &amp; "-" &amp; LEFT(F465,3) &amp; "-" &amp; MID(F465,8,4)) + TIMEVALUE(MID(F465,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43955.450694444444</v>
       </c>
       <c r="B465">
@@ -20908,7 +20962,7 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="10">
-        <f>DATEVALUE(MID(F466,5,2) &amp; "-" &amp; LEFT(F466,3) &amp; "-" &amp; MID(F466,8,4)) + TIMEVALUE(MID(F466,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43956.506921296299</v>
       </c>
       <c r="B466">
@@ -20929,7 +20983,7 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="10">
-        <f>DATEVALUE(MID(F467,5,2) &amp; "-" &amp; LEFT(F467,3) &amp; "-" &amp; MID(F467,8,4)) + TIMEVALUE(MID(F467,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43957.423391203702</v>
       </c>
       <c r="B467">
@@ -20950,7 +21004,7 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="10">
-        <f>DATEVALUE(MID(F468,5,2) &amp; "-" &amp; LEFT(F468,3) &amp; "-" &amp; MID(F468,8,4)) + TIMEVALUE(MID(F468,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43958.437650462962</v>
       </c>
       <c r="B468">
@@ -20971,7 +21025,7 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="10">
-        <f>DATEVALUE(MID(F469,5,2) &amp; "-" &amp; LEFT(F469,3) &amp; "-" &amp; MID(F469,8,4)) + TIMEVALUE(MID(F469,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43960.443761574075</v>
       </c>
       <c r="B469">
@@ -20992,7 +21046,7 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="10">
-        <f>DATEVALUE(MID(F470,5,2) &amp; "-" &amp; LEFT(F470,3) &amp; "-" &amp; MID(F470,8,4)) + TIMEVALUE(MID(F470,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43961.446284722224</v>
       </c>
       <c r="B470">
@@ -21013,7 +21067,7 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="10">
-        <f>DATEVALUE(MID(F471,5,2) &amp; "-" &amp; LEFT(F471,3) &amp; "-" &amp; MID(F471,8,4)) + TIMEVALUE(MID(F471,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43962.421458333331</v>
       </c>
       <c r="B471">
@@ -21034,7 +21088,7 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="10">
-        <f>DATEVALUE(MID(F472,5,2) &amp; "-" &amp; LEFT(F472,3) &amp; "-" &amp; MID(F472,8,4)) + TIMEVALUE(MID(F472,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43963.4221412037</v>
       </c>
       <c r="B472">
@@ -21055,7 +21109,7 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="10">
-        <f>DATEVALUE(MID(F473,5,2) &amp; "-" &amp; LEFT(F473,3) &amp; "-" &amp; MID(F473,8,4)) + TIMEVALUE(MID(F473,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43986.415567129632</v>
       </c>
       <c r="B473">
@@ -21076,7 +21130,7 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="10">
-        <f>DATEVALUE(MID(F474,5,2) &amp; "-" &amp; LEFT(F474,3) &amp; "-" &amp; MID(F474,8,4)) + TIMEVALUE(MID(F474,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43993.414479166669</v>
       </c>
       <c r="B474">
@@ -21097,7 +21151,7 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="10">
-        <f>DATEVALUE(MID(F475,5,2) &amp; "-" &amp; LEFT(F475,3) &amp; "-" &amp; MID(F475,8,4)) + TIMEVALUE(MID(F475,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43996.470312500001</v>
       </c>
       <c r="B475">
@@ -21118,7 +21172,7 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="10">
-        <f>DATEVALUE(MID(F476,5,2) &amp; "-" &amp; LEFT(F476,3) &amp; "-" &amp; MID(F476,8,4)) + TIMEVALUE(MID(F476,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43996.472673611112</v>
       </c>
       <c r="B476">
@@ -21139,7 +21193,7 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="10">
-        <f>DATEVALUE(MID(F477,5,2) &amp; "-" &amp; LEFT(F477,3) &amp; "-" &amp; MID(F477,8,4)) + TIMEVALUE(MID(F477,13,11))</f>
+        <f t="shared" si="1"/>
         <v>43997.460821759261</v>
       </c>
       <c r="B477">
@@ -21160,7 +21214,7 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="10">
-        <f>DATEVALUE(MID(F478,5,2) &amp; "-" &amp; LEFT(F478,3) &amp; "-" &amp; MID(F478,8,4)) + TIMEVALUE(MID(F478,13,11))</f>
+        <f t="shared" si="1"/>
         <v>44004.430717592593</v>
       </c>
       <c r="B478">
@@ -21181,7 +21235,7 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="10">
-        <f>DATEVALUE(MID(F479,5,2) &amp; "-" &amp; LEFT(F479,3) &amp; "-" &amp; MID(F479,8,4)) + TIMEVALUE(MID(F479,13,11))</f>
+        <f t="shared" si="1"/>
         <v>44008.427210648151</v>
       </c>
       <c r="B479">
@@ -21202,7 +21256,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="10">
-        <f>DATEVALUE(MID(F480,5,2) &amp; "-" &amp; LEFT(F480,3) &amp; "-" &amp; MID(F480,8,4)) + TIMEVALUE(MID(F480,13,11))</f>
+        <f t="shared" ref="A480:A543" si="2">DATEVALUE(MID(F480,5,2) &amp; "-" &amp; LEFT(F480,3) &amp; "-" &amp; MID(F480,8,4)) + TIMEVALUE(MID(F480,13,11))</f>
         <v>44011.440509259257</v>
       </c>
       <c r="B480">
@@ -21223,7 +21277,7 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="10">
-        <f>DATEVALUE(MID(F481,5,2) &amp; "-" &amp; LEFT(F481,3) &amp; "-" &amp; MID(F481,8,4)) + TIMEVALUE(MID(F481,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44012.451666666668</v>
       </c>
       <c r="B481">
@@ -21244,7 +21298,7 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="10">
-        <f>DATEVALUE(MID(F482,5,2) &amp; "-" &amp; LEFT(F482,3) &amp; "-" &amp; MID(F482,8,4)) + TIMEVALUE(MID(F482,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44019.404745370368</v>
       </c>
       <c r="B482">
@@ -21265,7 +21319,7 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="10">
-        <f>DATEVALUE(MID(F483,5,2) &amp; "-" &amp; LEFT(F483,3) &amp; "-" &amp; MID(F483,8,4)) + TIMEVALUE(MID(F483,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44024.444988425923</v>
       </c>
       <c r="B483">
@@ -21286,7 +21340,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="10">
-        <f>DATEVALUE(MID(F484,5,2) &amp; "-" &amp; LEFT(F484,3) &amp; "-" &amp; MID(F484,8,4)) + TIMEVALUE(MID(F484,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44028.414467592593</v>
       </c>
       <c r="B484">
@@ -21307,7 +21361,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="10">
-        <f>DATEVALUE(MID(F485,5,2) &amp; "-" &amp; LEFT(F485,3) &amp; "-" &amp; MID(F485,8,4)) + TIMEVALUE(MID(F485,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44034.443726851852</v>
       </c>
       <c r="B485">
@@ -21328,7 +21382,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="10">
-        <f>DATEVALUE(MID(F486,5,2) &amp; "-" &amp; LEFT(F486,3) &amp; "-" &amp; MID(F486,8,4)) + TIMEVALUE(MID(F486,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44035.451770833337</v>
       </c>
       <c r="B486">
@@ -21349,7 +21403,7 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="10">
-        <f>DATEVALUE(MID(F487,5,2) &amp; "-" &amp; LEFT(F487,3) &amp; "-" &amp; MID(F487,8,4)) + TIMEVALUE(MID(F487,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44039.428923611114</v>
       </c>
       <c r="B487">
@@ -21370,7 +21424,7 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="10">
-        <f>DATEVALUE(MID(F488,5,2) &amp; "-" &amp; LEFT(F488,3) &amp; "-" &amp; MID(F488,8,4)) + TIMEVALUE(MID(F488,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44040.432442129626</v>
       </c>
       <c r="B488">
@@ -21391,7 +21445,7 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="10">
-        <f>DATEVALUE(MID(F489,5,2) &amp; "-" &amp; LEFT(F489,3) &amp; "-" &amp; MID(F489,8,4)) + TIMEVALUE(MID(F489,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44041.451331018521</v>
       </c>
       <c r="B489">
@@ -21412,7 +21466,7 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="10">
-        <f>DATEVALUE(MID(F490,5,2) &amp; "-" &amp; LEFT(F490,3) &amp; "-" &amp; MID(F490,8,4)) + TIMEVALUE(MID(F490,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44042.402268518519</v>
       </c>
       <c r="B490">
@@ -21433,7 +21487,7 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="10">
-        <f>DATEVALUE(MID(F491,5,2) &amp; "-" &amp; LEFT(F491,3) &amp; "-" &amp; MID(F491,8,4)) + TIMEVALUE(MID(F491,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44043.425243055557</v>
       </c>
       <c r="B491">
@@ -21454,7 +21508,7 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="10">
-        <f>DATEVALUE(MID(F492,5,2) &amp; "-" &amp; LEFT(F492,3) &amp; "-" &amp; MID(F492,8,4)) + TIMEVALUE(MID(F492,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44044.444687499999</v>
       </c>
       <c r="B492">
@@ -21475,7 +21529,7 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="10">
-        <f>DATEVALUE(MID(F493,5,2) &amp; "-" &amp; LEFT(F493,3) &amp; "-" &amp; MID(F493,8,4)) + TIMEVALUE(MID(F493,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44045.411921296298</v>
       </c>
       <c r="B493">
@@ -21496,7 +21550,7 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="10">
-        <f>DATEVALUE(MID(F494,5,2) &amp; "-" &amp; LEFT(F494,3) &amp; "-" &amp; MID(F494,8,4)) + TIMEVALUE(MID(F494,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44046.431400462963</v>
       </c>
       <c r="B494">
@@ -21517,7 +21571,7 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="10">
-        <f>DATEVALUE(MID(F495,5,2) &amp; "-" &amp; LEFT(F495,3) &amp; "-" &amp; MID(F495,8,4)) + TIMEVALUE(MID(F495,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44048.427465277775</v>
       </c>
       <c r="B495">
@@ -21538,7 +21592,7 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="10">
-        <f>DATEVALUE(MID(F496,5,2) &amp; "-" &amp; LEFT(F496,3) &amp; "-" &amp; MID(F496,8,4)) + TIMEVALUE(MID(F496,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44049.424467592595</v>
       </c>
       <c r="B496">
@@ -21559,7 +21613,7 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="10">
-        <f>DATEVALUE(MID(F497,5,2) &amp; "-" &amp; LEFT(F497,3) &amp; "-" &amp; MID(F497,8,4)) + TIMEVALUE(MID(F497,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44053.411550925928</v>
       </c>
       <c r="B497">
@@ -21580,7 +21634,7 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="10">
-        <f>DATEVALUE(MID(F498,5,2) &amp; "-" &amp; LEFT(F498,3) &amp; "-" &amp; MID(F498,8,4)) + TIMEVALUE(MID(F498,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44054.432870370372</v>
       </c>
       <c r="B498">
@@ -21601,7 +21655,7 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="10">
-        <f>DATEVALUE(MID(F499,5,2) &amp; "-" &amp; LEFT(F499,3) &amp; "-" &amp; MID(F499,8,4)) + TIMEVALUE(MID(F499,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44058.427476851852</v>
       </c>
       <c r="B499">
@@ -21622,7 +21676,7 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="10">
-        <f>DATEVALUE(MID(F500,5,2) &amp; "-" &amp; LEFT(F500,3) &amp; "-" &amp; MID(F500,8,4)) + TIMEVALUE(MID(F500,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44059.424502314818</v>
       </c>
       <c r="B500">
@@ -21643,7 +21697,7 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="10">
-        <f>DATEVALUE(MID(F501,5,2) &amp; "-" &amp; LEFT(F501,3) &amp; "-" &amp; MID(F501,8,4)) + TIMEVALUE(MID(F501,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44060.445925925924</v>
       </c>
       <c r="B501">
@@ -21664,7 +21718,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="10">
-        <f>DATEVALUE(MID(F502,5,2) &amp; "-" &amp; LEFT(F502,3) &amp; "-" &amp; MID(F502,8,4)) + TIMEVALUE(MID(F502,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44060.512511574074</v>
       </c>
       <c r="B502">
@@ -21685,7 +21739,7 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="10">
-        <f>DATEVALUE(MID(F503,5,2) &amp; "-" &amp; LEFT(F503,3) &amp; "-" &amp; MID(F503,8,4)) + TIMEVALUE(MID(F503,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44061.457650462966</v>
       </c>
       <c r="B503">
@@ -21706,7 +21760,7 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="10">
-        <f>DATEVALUE(MID(F504,5,2) &amp; "-" &amp; LEFT(F504,3) &amp; "-" &amp; MID(F504,8,4)) + TIMEVALUE(MID(F504,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44062.441203703704</v>
       </c>
       <c r="B504">
@@ -21727,7 +21781,7 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="10">
-        <f>DATEVALUE(MID(F505,5,2) &amp; "-" &amp; LEFT(F505,3) &amp; "-" &amp; MID(F505,8,4)) + TIMEVALUE(MID(F505,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44063.457546296297</v>
       </c>
       <c r="B505">
@@ -21748,7 +21802,7 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="10">
-        <f>DATEVALUE(MID(F506,5,2) &amp; "-" &amp; LEFT(F506,3) &amp; "-" &amp; MID(F506,8,4)) + TIMEVALUE(MID(F506,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44064.453958333332</v>
       </c>
       <c r="B506">
@@ -21769,7 +21823,7 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="10">
-        <f>DATEVALUE(MID(F507,5,2) &amp; "-" &amp; LEFT(F507,3) &amp; "-" &amp; MID(F507,8,4)) + TIMEVALUE(MID(F507,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44065.439398148148</v>
       </c>
       <c r="B507">
@@ -21790,7 +21844,7 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="10">
-        <f>DATEVALUE(MID(F508,5,2) &amp; "-" &amp; LEFT(F508,3) &amp; "-" &amp; MID(F508,8,4)) + TIMEVALUE(MID(F508,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44067.484861111108</v>
       </c>
       <c r="B508">
@@ -21811,7 +21865,7 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="10">
-        <f>DATEVALUE(MID(F509,5,2) &amp; "-" &amp; LEFT(F509,3) &amp; "-" &amp; MID(F509,8,4)) + TIMEVALUE(MID(F509,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44068.40384259259</v>
       </c>
       <c r="B509">
@@ -21832,7 +21886,7 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="10">
-        <f>DATEVALUE(MID(F510,5,2) &amp; "-" &amp; LEFT(F510,3) &amp; "-" &amp; MID(F510,8,4)) + TIMEVALUE(MID(F510,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44070.488680555558</v>
       </c>
       <c r="B510">
@@ -21853,7 +21907,7 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="10">
-        <f>DATEVALUE(MID(F511,5,2) &amp; "-" &amp; LEFT(F511,3) &amp; "-" &amp; MID(F511,8,4)) + TIMEVALUE(MID(F511,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44072.47347222222</v>
       </c>
       <c r="B511">
@@ -21874,7 +21928,7 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="10">
-        <f>DATEVALUE(MID(F512,5,2) &amp; "-" &amp; LEFT(F512,3) &amp; "-" &amp; MID(F512,8,4)) + TIMEVALUE(MID(F512,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44073.467372685183</v>
       </c>
       <c r="B512">
@@ -21895,7 +21949,7 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="10">
-        <f>DATEVALUE(MID(F513,5,2) &amp; "-" &amp; LEFT(F513,3) &amp; "-" &amp; MID(F513,8,4)) + TIMEVALUE(MID(F513,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44074.450879629629</v>
       </c>
       <c r="B513">
@@ -21916,7 +21970,7 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="10">
-        <f>DATEVALUE(MID(F514,5,2) &amp; "-" &amp; LEFT(F514,3) &amp; "-" &amp; MID(F514,8,4)) + TIMEVALUE(MID(F514,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44075.47892361111</v>
       </c>
       <c r="B514">
@@ -21937,7 +21991,7 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="10">
-        <f>DATEVALUE(MID(F515,5,2) &amp; "-" &amp; LEFT(F515,3) &amp; "-" &amp; MID(F515,8,4)) + TIMEVALUE(MID(F515,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44076.459270833337</v>
       </c>
       <c r="B515">
@@ -21958,7 +22012,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="10">
-        <f>DATEVALUE(MID(F516,5,2) &amp; "-" &amp; LEFT(F516,3) &amp; "-" &amp; MID(F516,8,4)) + TIMEVALUE(MID(F516,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44078.41815972222</v>
       </c>
       <c r="B516">
@@ -21979,7 +22033,7 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="10">
-        <f>DATEVALUE(MID(F517,5,2) &amp; "-" &amp; LEFT(F517,3) &amp; "-" &amp; MID(F517,8,4)) + TIMEVALUE(MID(F517,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44078.468680555554</v>
       </c>
       <c r="B517">
@@ -22000,7 +22054,7 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="10">
-        <f>DATEVALUE(MID(F518,5,2) &amp; "-" &amp; LEFT(F518,3) &amp; "-" &amp; MID(F518,8,4)) + TIMEVALUE(MID(F518,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44079.435694444444</v>
       </c>
       <c r="B518">
@@ -22021,7 +22075,7 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="10">
-        <f>DATEVALUE(MID(F519,5,2) &amp; "-" &amp; LEFT(F519,3) &amp; "-" &amp; MID(F519,8,4)) + TIMEVALUE(MID(F519,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44079.445543981485</v>
       </c>
       <c r="B519">
@@ -22042,7 +22096,7 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="10">
-        <f>DATEVALUE(MID(F520,5,2) &amp; "-" &amp; LEFT(F520,3) &amp; "-" &amp; MID(F520,8,4)) + TIMEVALUE(MID(F520,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44081.484270833331</v>
       </c>
       <c r="B520">
@@ -22063,7 +22117,7 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="10">
-        <f>DATEVALUE(MID(F521,5,2) &amp; "-" &amp; LEFT(F521,3) &amp; "-" &amp; MID(F521,8,4)) + TIMEVALUE(MID(F521,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44091.435624999998</v>
       </c>
       <c r="B521">
@@ -22084,7 +22138,7 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="10">
-        <f>DATEVALUE(MID(F522,5,2) &amp; "-" &amp; LEFT(F522,3) &amp; "-" &amp; MID(F522,8,4)) + TIMEVALUE(MID(F522,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44095.441018518519</v>
       </c>
       <c r="B522">
@@ -22105,7 +22159,7 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="10">
-        <f>DATEVALUE(MID(F523,5,2) &amp; "-" &amp; LEFT(F523,3) &amp; "-" &amp; MID(F523,8,4)) + TIMEVALUE(MID(F523,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44116.477824074071</v>
       </c>
       <c r="B523">
@@ -22126,7 +22180,7 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="10">
-        <f>DATEVALUE(MID(F524,5,2) &amp; "-" &amp; LEFT(F524,3) &amp; "-" &amp; MID(F524,8,4)) + TIMEVALUE(MID(F524,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44117.47047453704</v>
       </c>
       <c r="B524">
@@ -22147,7 +22201,7 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="10">
-        <f>DATEVALUE(MID(F525,5,2) &amp; "-" &amp; LEFT(F525,3) &amp; "-" &amp; MID(F525,8,4)) + TIMEVALUE(MID(F525,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44120.474895833337</v>
       </c>
       <c r="B525">
@@ -22168,7 +22222,7 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="10">
-        <f>DATEVALUE(MID(F526,5,2) &amp; "-" &amp; LEFT(F526,3) &amp; "-" &amp; MID(F526,8,4)) + TIMEVALUE(MID(F526,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44123.46769675926</v>
       </c>
       <c r="B526">
@@ -22189,7 +22243,7 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="10">
-        <f>DATEVALUE(MID(F527,5,2) &amp; "-" &amp; LEFT(F527,3) &amp; "-" &amp; MID(F527,8,4)) + TIMEVALUE(MID(F527,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44124.511388888888</v>
       </c>
       <c r="B527">
@@ -22210,7 +22264,7 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="10">
-        <f>DATEVALUE(MID(F528,5,2) &amp; "-" &amp; LEFT(F528,3) &amp; "-" &amp; MID(F528,8,4)) + TIMEVALUE(MID(F528,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44152.518993055557</v>
       </c>
       <c r="B528">
@@ -22231,7 +22285,7 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="10">
-        <f>DATEVALUE(MID(F529,5,2) &amp; "-" &amp; LEFT(F529,3) &amp; "-" &amp; MID(F529,8,4)) + TIMEVALUE(MID(F529,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44153.490324074075</v>
       </c>
       <c r="B529">
@@ -22252,7 +22306,7 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="10">
-        <f>DATEVALUE(MID(F530,5,2) &amp; "-" &amp; LEFT(F530,3) &amp; "-" &amp; MID(F530,8,4)) + TIMEVALUE(MID(F530,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44158.487870370373</v>
       </c>
       <c r="B530">
@@ -22273,7 +22327,7 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="10">
-        <f>DATEVALUE(MID(F531,5,2) &amp; "-" &amp; LEFT(F531,3) &amp; "-" &amp; MID(F531,8,4)) + TIMEVALUE(MID(F531,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44159.550081018519</v>
       </c>
       <c r="B531">
@@ -22294,7 +22348,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="10">
-        <f>DATEVALUE(MID(F532,5,2) &amp; "-" &amp; LEFT(F532,3) &amp; "-" &amp; MID(F532,8,4)) + TIMEVALUE(MID(F532,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44172.524525462963</v>
       </c>
       <c r="B532">
@@ -22315,7 +22369,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="10">
-        <f>DATEVALUE(MID(F533,5,2) &amp; "-" &amp; LEFT(F533,3) &amp; "-" &amp; MID(F533,8,4)) + TIMEVALUE(MID(F533,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44173.523032407407</v>
       </c>
       <c r="B533">
@@ -22336,7 +22390,7 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="10">
-        <f>DATEVALUE(MID(F534,5,2) &amp; "-" &amp; LEFT(F534,3) &amp; "-" &amp; MID(F534,8,4)) + TIMEVALUE(MID(F534,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44174.526412037034</v>
       </c>
       <c r="B534">
@@ -22357,7 +22411,7 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="10">
-        <f>DATEVALUE(MID(F535,5,2) &amp; "-" &amp; LEFT(F535,3) &amp; "-" &amp; MID(F535,8,4)) + TIMEVALUE(MID(F535,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44179.475405092591</v>
       </c>
       <c r="B535">
@@ -22378,7 +22432,7 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="10">
-        <f>DATEVALUE(MID(F536,5,2) &amp; "-" &amp; LEFT(F536,3) &amp; "-" &amp; MID(F536,8,4)) + TIMEVALUE(MID(F536,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44180.521168981482</v>
       </c>
       <c r="B536">
@@ -22399,7 +22453,7 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="10">
-        <f>DATEVALUE(MID(F537,5,2) &amp; "-" &amp; LEFT(F537,3) &amp; "-" &amp; MID(F537,8,4)) + TIMEVALUE(MID(F537,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44187.538738425923</v>
       </c>
       <c r="B537">
@@ -22420,7 +22474,7 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="10">
-        <f>DATEVALUE(MID(F538,5,2) &amp; "-" &amp; LEFT(F538,3) &amp; "-" &amp; MID(F538,8,4)) + TIMEVALUE(MID(F538,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44239.488009259258</v>
       </c>
       <c r="B538">
@@ -22441,7 +22495,7 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="10">
-        <f>DATEVALUE(MID(F539,5,2) &amp; "-" &amp; LEFT(F539,3) &amp; "-" &amp; MID(F539,8,4)) + TIMEVALUE(MID(F539,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44242.513275462959</v>
       </c>
       <c r="B539">
@@ -22462,7 +22516,7 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="10">
-        <f>DATEVALUE(MID(F540,5,2) &amp; "-" &amp; LEFT(F540,3) &amp; "-" &amp; MID(F540,8,4)) + TIMEVALUE(MID(F540,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44249.55259259259</v>
       </c>
       <c r="B540">
@@ -22483,7 +22537,7 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="10">
-        <f>DATEVALUE(MID(F541,5,2) &amp; "-" &amp; LEFT(F541,3) &amp; "-" &amp; MID(F541,8,4)) + TIMEVALUE(MID(F541,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44250.510752314818</v>
       </c>
       <c r="B541">
@@ -22504,7 +22558,7 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="10">
-        <f>DATEVALUE(MID(F542,5,2) &amp; "-" &amp; LEFT(F542,3) &amp; "-" &amp; MID(F542,8,4)) + TIMEVALUE(MID(F542,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44251.538321759261</v>
       </c>
       <c r="B542">
@@ -22525,7 +22579,7 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="10">
-        <f>DATEVALUE(MID(F543,5,2) &amp; "-" &amp; LEFT(F543,3) &amp; "-" &amp; MID(F543,8,4)) + TIMEVALUE(MID(F543,13,11))</f>
+        <f t="shared" si="2"/>
         <v>44252.518113425926</v>
       </c>
       <c r="B543">
@@ -22546,7 +22600,7 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="10">
-        <f>DATEVALUE(MID(F544,5,2) &amp; "-" &amp; LEFT(F544,3) &amp; "-" &amp; MID(F544,8,4)) + TIMEVALUE(MID(F544,13,11))</f>
+        <f t="shared" ref="A544:A607" si="3">DATEVALUE(MID(F544,5,2) &amp; "-" &amp; LEFT(F544,3) &amp; "-" &amp; MID(F544,8,4)) + TIMEVALUE(MID(F544,13,11))</f>
         <v>44256.508032407408</v>
       </c>
       <c r="B544">
@@ -22567,7 +22621,7 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="10">
-        <f>DATEVALUE(MID(F545,5,2) &amp; "-" &amp; LEFT(F545,3) &amp; "-" &amp; MID(F545,8,4)) + TIMEVALUE(MID(F545,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44257.527499999997</v>
       </c>
       <c r="B545">
@@ -22588,7 +22642,7 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="10">
-        <f>DATEVALUE(MID(F546,5,2) &amp; "-" &amp; LEFT(F546,3) &amp; "-" &amp; MID(F546,8,4)) + TIMEVALUE(MID(F546,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44258.560949074075</v>
       </c>
       <c r="B546">
@@ -22609,7 +22663,7 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="10">
-        <f>DATEVALUE(MID(F547,5,2) &amp; "-" &amp; LEFT(F547,3) &amp; "-" &amp; MID(F547,8,4)) + TIMEVALUE(MID(F547,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44259.548530092594</v>
       </c>
       <c r="B547">
@@ -22630,7 +22684,7 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="10">
-        <f>DATEVALUE(MID(F548,5,2) &amp; "-" &amp; LEFT(F548,3) &amp; "-" &amp; MID(F548,8,4)) + TIMEVALUE(MID(F548,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44259.555127314816</v>
       </c>
       <c r="B548">
@@ -22651,7 +22705,7 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="10">
-        <f>DATEVALUE(MID(F549,5,2) &amp; "-" &amp; LEFT(F549,3) &amp; "-" &amp; MID(F549,8,4)) + TIMEVALUE(MID(F549,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44260.501354166663</v>
       </c>
       <c r="B549">
@@ -22672,7 +22726,7 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="10">
-        <f>DATEVALUE(MID(F550,5,2) &amp; "-" &amp; LEFT(F550,3) &amp; "-" &amp; MID(F550,8,4)) + TIMEVALUE(MID(F550,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44263.525335648148</v>
       </c>
       <c r="B550">
@@ -22693,7 +22747,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="10">
-        <f>DATEVALUE(MID(F551,5,2) &amp; "-" &amp; LEFT(F551,3) &amp; "-" &amp; MID(F551,8,4)) + TIMEVALUE(MID(F551,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44264.515821759262</v>
       </c>
       <c r="B551">
@@ -22714,7 +22768,7 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="10">
-        <f>DATEVALUE(MID(F552,5,2) &amp; "-" &amp; LEFT(F552,3) &amp; "-" &amp; MID(F552,8,4)) + TIMEVALUE(MID(F552,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44265.52752314815</v>
       </c>
       <c r="B552">
@@ -22735,7 +22789,7 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="10">
-        <f>DATEVALUE(MID(F553,5,2) &amp; "-" &amp; LEFT(F553,3) &amp; "-" &amp; MID(F553,8,4)) + TIMEVALUE(MID(F553,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44266.471261574072</v>
       </c>
       <c r="B553">
@@ -22756,7 +22810,7 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="10">
-        <f>DATEVALUE(MID(F554,5,2) &amp; "-" &amp; LEFT(F554,3) &amp; "-" &amp; MID(F554,8,4)) + TIMEVALUE(MID(F554,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44270.474965277775</v>
       </c>
       <c r="B554">
@@ -22777,7 +22831,7 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="10">
-        <f>DATEVALUE(MID(F555,5,2) &amp; "-" &amp; LEFT(F555,3) &amp; "-" &amp; MID(F555,8,4)) + TIMEVALUE(MID(F555,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44272.464166666665</v>
       </c>
       <c r="B555">
@@ -22798,7 +22852,7 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="10">
-        <f>DATEVALUE(MID(F556,5,2) &amp; "-" &amp; LEFT(F556,3) &amp; "-" &amp; MID(F556,8,4)) + TIMEVALUE(MID(F556,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44274.467962962961</v>
       </c>
       <c r="B556">
@@ -22819,7 +22873,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="10">
-        <f>DATEVALUE(MID(F557,5,2) &amp; "-" &amp; LEFT(F557,3) &amp; "-" &amp; MID(F557,8,4)) + TIMEVALUE(MID(F557,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44275.504490740743</v>
       </c>
       <c r="B557">
@@ -22840,7 +22894,7 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="10">
-        <f>DATEVALUE(MID(F558,5,2) &amp; "-" &amp; LEFT(F558,3) &amp; "-" &amp; MID(F558,8,4)) + TIMEVALUE(MID(F558,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44276.472071759257</v>
       </c>
       <c r="B558">
@@ -22861,7 +22915,7 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="10">
-        <f>DATEVALUE(MID(F559,5,2) &amp; "-" &amp; LEFT(F559,3) &amp; "-" &amp; MID(F559,8,4)) + TIMEVALUE(MID(F559,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44281.513136574074</v>
       </c>
       <c r="B559">
@@ -22882,7 +22936,7 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="10">
-        <f>DATEVALUE(MID(F560,5,2) &amp; "-" &amp; LEFT(F560,3) &amp; "-" &amp; MID(F560,8,4)) + TIMEVALUE(MID(F560,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44284.503738425927</v>
       </c>
       <c r="B560">
@@ -22903,7 +22957,7 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="10">
-        <f>DATEVALUE(MID(F561,5,2) &amp; "-" &amp; LEFT(F561,3) &amp; "-" &amp; MID(F561,8,4)) + TIMEVALUE(MID(F561,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44285.47283564815</v>
       </c>
       <c r="B561">
@@ -22924,7 +22978,7 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="10">
-        <f>DATEVALUE(MID(F562,5,2) &amp; "-" &amp; LEFT(F562,3) &amp; "-" &amp; MID(F562,8,4)) + TIMEVALUE(MID(F562,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44286.495879629627</v>
       </c>
       <c r="B562">
@@ -22945,7 +22999,7 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="10">
-        <f>DATEVALUE(MID(F563,5,2) &amp; "-" &amp; LEFT(F563,3) &amp; "-" &amp; MID(F563,8,4)) + TIMEVALUE(MID(F563,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44287.432673611111</v>
       </c>
       <c r="B563">
@@ -22966,7 +23020,7 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="10">
-        <f>DATEVALUE(MID(F564,5,2) &amp; "-" &amp; LEFT(F564,3) &amp; "-" &amp; MID(F564,8,4)) + TIMEVALUE(MID(F564,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44291.454768518517</v>
       </c>
       <c r="B564">
@@ -22987,7 +23041,7 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="10">
-        <f>DATEVALUE(MID(F565,5,2) &amp; "-" &amp; LEFT(F565,3) &amp; "-" &amp; MID(F565,8,4)) + TIMEVALUE(MID(F565,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44292.486226851855</v>
       </c>
       <c r="B565">
@@ -23008,7 +23062,7 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="10">
-        <f>DATEVALUE(MID(F566,5,2) &amp; "-" &amp; LEFT(F566,3) &amp; "-" &amp; MID(F566,8,4)) + TIMEVALUE(MID(F566,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44293.478796296295</v>
       </c>
       <c r="B566">
@@ -23029,7 +23083,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="10">
-        <f>DATEVALUE(MID(F567,5,2) &amp; "-" &amp; LEFT(F567,3) &amp; "-" &amp; MID(F567,8,4)) + TIMEVALUE(MID(F567,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44298.47415509259</v>
       </c>
       <c r="B567">
@@ -23050,7 +23104,7 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="10">
-        <f>DATEVALUE(MID(F568,5,2) &amp; "-" &amp; LEFT(F568,3) &amp; "-" &amp; MID(F568,8,4)) + TIMEVALUE(MID(F568,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44299.484861111108</v>
       </c>
       <c r="B568">
@@ -23071,7 +23125,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="10">
-        <f>DATEVALUE(MID(F569,5,2) &amp; "-" &amp; LEFT(F569,3) &amp; "-" &amp; MID(F569,8,4)) + TIMEVALUE(MID(F569,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44301.452592592592</v>
       </c>
       <c r="B569">
@@ -23092,7 +23146,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="10">
-        <f>DATEVALUE(MID(F570,5,2) &amp; "-" &amp; LEFT(F570,3) &amp; "-" &amp; MID(F570,8,4)) + TIMEVALUE(MID(F570,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44302.443842592591</v>
       </c>
       <c r="B570">
@@ -23113,7 +23167,7 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="10">
-        <f>DATEVALUE(MID(F571,5,2) &amp; "-" &amp; LEFT(F571,3) &amp; "-" &amp; MID(F571,8,4)) + TIMEVALUE(MID(F571,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44313.422453703701</v>
       </c>
       <c r="B571">
@@ -23134,7 +23188,7 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="10">
-        <f>DATEVALUE(MID(F572,5,2) &amp; "-" &amp; LEFT(F572,3) &amp; "-" &amp; MID(F572,8,4)) + TIMEVALUE(MID(F572,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44316.42564814815</v>
       </c>
       <c r="B572">
@@ -23155,7 +23209,7 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="10">
-        <f>DATEVALUE(MID(F573,5,2) &amp; "-" &amp; LEFT(F573,3) &amp; "-" &amp; MID(F573,8,4)) + TIMEVALUE(MID(F573,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44319.486180555556</v>
       </c>
       <c r="B573">
@@ -23176,7 +23230,7 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="10">
-        <f>DATEVALUE(MID(F574,5,2) &amp; "-" &amp; LEFT(F574,3) &amp; "-" &amp; MID(F574,8,4)) + TIMEVALUE(MID(F574,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44326.481932870367</v>
       </c>
       <c r="B574">
@@ -23197,7 +23251,7 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="10">
-        <f>DATEVALUE(MID(F575,5,2) &amp; "-" &amp; LEFT(F575,3) &amp; "-" &amp; MID(F575,8,4)) + TIMEVALUE(MID(F575,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44327.493587962963</v>
       </c>
       <c r="B575">
@@ -23218,7 +23272,7 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="10">
-        <f>DATEVALUE(MID(F576,5,2) &amp; "-" &amp; LEFT(F576,3) &amp; "-" &amp; MID(F576,8,4)) + TIMEVALUE(MID(F576,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44334.475624999999</v>
       </c>
       <c r="B576">
@@ -23239,7 +23293,7 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="10">
-        <f>DATEVALUE(MID(F577,5,2) &amp; "-" &amp; LEFT(F577,3) &amp; "-" &amp; MID(F577,8,4)) + TIMEVALUE(MID(F577,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44336.485798611109</v>
       </c>
       <c r="B577">
@@ -23260,7 +23314,7 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="10">
-        <f>DATEVALUE(MID(F578,5,2) &amp; "-" &amp; LEFT(F578,3) &amp; "-" &amp; MID(F578,8,4)) + TIMEVALUE(MID(F578,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44337.435648148145</v>
       </c>
       <c r="B578">
@@ -23281,7 +23335,7 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="10">
-        <f>DATEVALUE(MID(F579,5,2) &amp; "-" &amp; LEFT(F579,3) &amp; "-" &amp; MID(F579,8,4)) + TIMEVALUE(MID(F579,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44338.442337962966</v>
       </c>
       <c r="B579">
@@ -23302,7 +23356,7 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="10">
-        <f>DATEVALUE(MID(F580,5,2) &amp; "-" &amp; LEFT(F580,3) &amp; "-" &amp; MID(F580,8,4)) + TIMEVALUE(MID(F580,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44339.442777777775</v>
       </c>
       <c r="B580">
@@ -23323,7 +23377,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="10">
-        <f>DATEVALUE(MID(F581,5,2) &amp; "-" &amp; LEFT(F581,3) &amp; "-" &amp; MID(F581,8,4)) + TIMEVALUE(MID(F581,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44343.475925925923</v>
       </c>
       <c r="B581">
@@ -23344,7 +23398,7 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="10">
-        <f>DATEVALUE(MID(F582,5,2) &amp; "-" &amp; LEFT(F582,3) &amp; "-" &amp; MID(F582,8,4)) + TIMEVALUE(MID(F582,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44353.478148148148</v>
       </c>
       <c r="B582">
@@ -23365,7 +23419,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="10">
-        <f>DATEVALUE(MID(F583,5,2) &amp; "-" &amp; LEFT(F583,3) &amp; "-" &amp; MID(F583,8,4)) + TIMEVALUE(MID(F583,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44358.469293981485</v>
       </c>
       <c r="B583">
@@ -23386,7 +23440,7 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="10">
-        <f>DATEVALUE(MID(F584,5,2) &amp; "-" &amp; LEFT(F584,3) &amp; "-" &amp; MID(F584,8,4)) + TIMEVALUE(MID(F584,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44364.460347222222</v>
       </c>
       <c r="B584">
@@ -23407,7 +23461,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="10">
-        <f>DATEVALUE(MID(F585,5,2) &amp; "-" &amp; LEFT(F585,3) &amp; "-" &amp; MID(F585,8,4)) + TIMEVALUE(MID(F585,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44365.470266203702</v>
       </c>
       <c r="B585">
@@ -23428,7 +23482,7 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="10">
-        <f>DATEVALUE(MID(F586,5,2) &amp; "-" &amp; LEFT(F586,3) &amp; "-" &amp; MID(F586,8,4)) + TIMEVALUE(MID(F586,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44367.468298611115</v>
       </c>
       <c r="B586">
@@ -23449,7 +23503,7 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="10">
-        <f>DATEVALUE(MID(F587,5,2) &amp; "-" &amp; LEFT(F587,3) &amp; "-" &amp; MID(F587,8,4)) + TIMEVALUE(MID(F587,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44370.424780092595</v>
       </c>
       <c r="B587">
@@ -23470,7 +23524,7 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="10">
-        <f>DATEVALUE(MID(F588,5,2) &amp; "-" &amp; LEFT(F588,3) &amp; "-" &amp; MID(F588,8,4)) + TIMEVALUE(MID(F588,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44372.462233796294</v>
       </c>
       <c r="B588">
@@ -23491,7 +23545,7 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="10">
-        <f>DATEVALUE(MID(F589,5,2) &amp; "-" &amp; LEFT(F589,3) &amp; "-" &amp; MID(F589,8,4)) + TIMEVALUE(MID(F589,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44374.485925925925</v>
       </c>
       <c r="B589">
@@ -23512,7 +23566,7 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="10">
-        <f>DATEVALUE(MID(F590,5,2) &amp; "-" &amp; LEFT(F590,3) &amp; "-" &amp; MID(F590,8,4)) + TIMEVALUE(MID(F590,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44379.427523148152</v>
       </c>
       <c r="B590">
@@ -23533,7 +23587,7 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="10">
-        <f>DATEVALUE(MID(F591,5,2) &amp; "-" &amp; LEFT(F591,3) &amp; "-" &amp; MID(F591,8,4)) + TIMEVALUE(MID(F591,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44381.4846412037</v>
       </c>
       <c r="B591">
@@ -23554,7 +23608,7 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="10">
-        <f>DATEVALUE(MID(F592,5,2) &amp; "-" &amp; LEFT(F592,3) &amp; "-" &amp; MID(F592,8,4)) + TIMEVALUE(MID(F592,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44382.423136574071</v>
       </c>
       <c r="B592">
@@ -23575,7 +23629,7 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="10">
-        <f>DATEVALUE(MID(F593,5,2) &amp; "-" &amp; LEFT(F593,3) &amp; "-" &amp; MID(F593,8,4)) + TIMEVALUE(MID(F593,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44383.423356481479</v>
       </c>
       <c r="B593">
@@ -23596,7 +23650,7 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="10">
-        <f>DATEVALUE(MID(F594,5,2) &amp; "-" &amp; LEFT(F594,3) &amp; "-" &amp; MID(F594,8,4)) + TIMEVALUE(MID(F594,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44383.564872685187</v>
       </c>
       <c r="B594">
@@ -23617,7 +23671,7 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="10">
-        <f>DATEVALUE(MID(F595,5,2) &amp; "-" &amp; LEFT(F595,3) &amp; "-" &amp; MID(F595,8,4)) + TIMEVALUE(MID(F595,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44384.397662037038</v>
       </c>
       <c r="B595">
@@ -23638,7 +23692,7 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="10">
-        <f>DATEVALUE(MID(F596,5,2) &amp; "-" &amp; LEFT(F596,3) &amp; "-" &amp; MID(F596,8,4)) + TIMEVALUE(MID(F596,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44385.441435185188</v>
       </c>
       <c r="B596">
@@ -23659,7 +23713,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="10">
-        <f>DATEVALUE(MID(F597,5,2) &amp; "-" &amp; LEFT(F597,3) &amp; "-" &amp; MID(F597,8,4)) + TIMEVALUE(MID(F597,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44386.438159722224</v>
       </c>
       <c r="B597">
@@ -23680,7 +23734,7 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="10">
-        <f>DATEVALUE(MID(F598,5,2) &amp; "-" &amp; LEFT(F598,3) &amp; "-" &amp; MID(F598,8,4)) + TIMEVALUE(MID(F598,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44389.453831018516</v>
       </c>
       <c r="B598">
@@ -23701,7 +23755,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="10">
-        <f>DATEVALUE(MID(F599,5,2) &amp; "-" &amp; LEFT(F599,3) &amp; "-" &amp; MID(F599,8,4)) + TIMEVALUE(MID(F599,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44390.402789351851</v>
       </c>
       <c r="B599">
@@ -23722,7 +23776,7 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="10">
-        <f>DATEVALUE(MID(F600,5,2) &amp; "-" &amp; LEFT(F600,3) &amp; "-" &amp; MID(F600,8,4)) + TIMEVALUE(MID(F600,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44392.439502314817</v>
       </c>
       <c r="B600">
@@ -23743,7 +23797,7 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="10">
-        <f>DATEVALUE(MID(F601,5,2) &amp; "-" &amp; LEFT(F601,3) &amp; "-" &amp; MID(F601,8,4)) + TIMEVALUE(MID(F601,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44393.474664351852</v>
       </c>
       <c r="B601">
@@ -23764,7 +23818,7 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="10">
-        <f>DATEVALUE(MID(F602,5,2) &amp; "-" &amp; LEFT(F602,3) &amp; "-" &amp; MID(F602,8,4)) + TIMEVALUE(MID(F602,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44396.452361111114</v>
       </c>
       <c r="B602">
@@ -23785,7 +23839,7 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="10">
-        <f>DATEVALUE(MID(F603,5,2) &amp; "-" &amp; LEFT(F603,3) &amp; "-" &amp; MID(F603,8,4)) + TIMEVALUE(MID(F603,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44399.473935185182</v>
       </c>
       <c r="B603">
@@ -23806,7 +23860,7 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="10">
-        <f>DATEVALUE(MID(F604,5,2) &amp; "-" &amp; LEFT(F604,3) &amp; "-" &amp; MID(F604,8,4)) + TIMEVALUE(MID(F604,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44400.438900462963</v>
       </c>
       <c r="B604">
@@ -23827,7 +23881,7 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="10">
-        <f>DATEVALUE(MID(F605,5,2) &amp; "-" &amp; LEFT(F605,3) &amp; "-" &amp; MID(F605,8,4)) + TIMEVALUE(MID(F605,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44403.428229166668</v>
       </c>
       <c r="B605">
@@ -23848,7 +23902,7 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="10">
-        <f>DATEVALUE(MID(F606,5,2) &amp; "-" &amp; LEFT(F606,3) &amp; "-" &amp; MID(F606,8,4)) + TIMEVALUE(MID(F606,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44404.440300925926</v>
       </c>
       <c r="B606">
@@ -23869,7 +23923,7 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="10">
-        <f>DATEVALUE(MID(F607,5,2) &amp; "-" &amp; LEFT(F607,3) &amp; "-" &amp; MID(F607,8,4)) + TIMEVALUE(MID(F607,13,11))</f>
+        <f t="shared" si="3"/>
         <v>44405.449016203704</v>
       </c>
       <c r="B607">
@@ -23890,7 +23944,7 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="10">
-        <f>DATEVALUE(MID(F608,5,2) &amp; "-" &amp; LEFT(F608,3) &amp; "-" &amp; MID(F608,8,4)) + TIMEVALUE(MID(F608,13,11))</f>
+        <f t="shared" ref="A608:A671" si="4">DATEVALUE(MID(F608,5,2) &amp; "-" &amp; LEFT(F608,3) &amp; "-" &amp; MID(F608,8,4)) + TIMEVALUE(MID(F608,13,11))</f>
         <v>44406.426168981481</v>
       </c>
       <c r="B608">
@@ -23911,7 +23965,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="10">
-        <f>DATEVALUE(MID(F609,5,2) &amp; "-" &amp; LEFT(F609,3) &amp; "-" &amp; MID(F609,8,4)) + TIMEVALUE(MID(F609,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44408.497662037036</v>
       </c>
       <c r="B609">
@@ -23932,7 +23986,7 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="10">
-        <f>DATEVALUE(MID(F610,5,2) &amp; "-" &amp; LEFT(F610,3) &amp; "-" &amp; MID(F610,8,4)) + TIMEVALUE(MID(F610,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44409.561354166668</v>
       </c>
       <c r="B610">
@@ -23953,7 +24007,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="10">
-        <f>DATEVALUE(MID(F611,5,2) &amp; "-" &amp; LEFT(F611,3) &amp; "-" &amp; MID(F611,8,4)) + TIMEVALUE(MID(F611,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44410.465983796297</v>
       </c>
       <c r="B611">
@@ -23974,7 +24028,7 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="10">
-        <f>DATEVALUE(MID(F612,5,2) &amp; "-" &amp; LEFT(F612,3) &amp; "-" &amp; MID(F612,8,4)) + TIMEVALUE(MID(F612,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44411.437615740739</v>
       </c>
       <c r="B612">
@@ -23995,7 +24049,7 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="10">
-        <f>DATEVALUE(MID(F613,5,2) &amp; "-" &amp; LEFT(F613,3) &amp; "-" &amp; MID(F613,8,4)) + TIMEVALUE(MID(F613,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44413.501099537039</v>
       </c>
       <c r="B613">
@@ -24016,7 +24070,7 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="10">
-        <f>DATEVALUE(MID(F614,5,2) &amp; "-" &amp; LEFT(F614,3) &amp; "-" &amp; MID(F614,8,4)) + TIMEVALUE(MID(F614,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44414.563067129631</v>
       </c>
       <c r="B614">
@@ -24037,7 +24091,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="10">
-        <f>DATEVALUE(MID(F615,5,2) &amp; "-" &amp; LEFT(F615,3) &amp; "-" &amp; MID(F615,8,4)) + TIMEVALUE(MID(F615,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44419.444363425922</v>
       </c>
       <c r="B615">
@@ -24058,7 +24112,7 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="10">
-        <f>DATEVALUE(MID(F616,5,2) &amp; "-" &amp; LEFT(F616,3) &amp; "-" &amp; MID(F616,8,4)) + TIMEVALUE(MID(F616,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44421.474016203705</v>
       </c>
       <c r="B616">
@@ -24079,7 +24133,7 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="10">
-        <f>DATEVALUE(MID(F617,5,2) &amp; "-" &amp; LEFT(F617,3) &amp; "-" &amp; MID(F617,8,4)) + TIMEVALUE(MID(F617,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44422.510266203702</v>
       </c>
       <c r="B617">
@@ -24100,7 +24154,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="10">
-        <f>DATEVALUE(MID(F618,5,2) &amp; "-" &amp; LEFT(F618,3) &amp; "-" &amp; MID(F618,8,4)) + TIMEVALUE(MID(F618,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44424.456435185188</v>
       </c>
       <c r="B618">
@@ -24121,7 +24175,7 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="10">
-        <f>DATEVALUE(MID(F619,5,2) &amp; "-" &amp; LEFT(F619,3) &amp; "-" &amp; MID(F619,8,4)) + TIMEVALUE(MID(F619,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44432.486261574071</v>
       </c>
       <c r="B619">
@@ -24142,7 +24196,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="10">
-        <f>DATEVALUE(MID(F620,5,2) &amp; "-" &amp; LEFT(F620,3) &amp; "-" &amp; MID(F620,8,4)) + TIMEVALUE(MID(F620,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44433.456365740742</v>
       </c>
       <c r="B620">
@@ -24163,7 +24217,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="10">
-        <f>DATEVALUE(MID(F621,5,2) &amp; "-" &amp; LEFT(F621,3) &amp; "-" &amp; MID(F621,8,4)) + TIMEVALUE(MID(F621,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44435.483541666668</v>
       </c>
       <c r="B621">
@@ -24184,7 +24238,7 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="10">
-        <f>DATEVALUE(MID(F622,5,2) &amp; "-" &amp; LEFT(F622,3) &amp; "-" &amp; MID(F622,8,4)) + TIMEVALUE(MID(F622,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44435.549814814818</v>
       </c>
       <c r="B622">
@@ -24205,7 +24259,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="10">
-        <f>DATEVALUE(MID(F623,5,2) &amp; "-" &amp; LEFT(F623,3) &amp; "-" &amp; MID(F623,8,4)) + TIMEVALUE(MID(F623,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44440.487638888888</v>
       </c>
       <c r="B623">
@@ -24226,7 +24280,7 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="10">
-        <f>DATEVALUE(MID(F624,5,2) &amp; "-" &amp; LEFT(F624,3) &amp; "-" &amp; MID(F624,8,4)) + TIMEVALUE(MID(F624,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44446.469571759262</v>
       </c>
       <c r="B624">
@@ -24247,7 +24301,7 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="10">
-        <f>DATEVALUE(MID(F625,5,2) &amp; "-" &amp; LEFT(F625,3) &amp; "-" &amp; MID(F625,8,4)) + TIMEVALUE(MID(F625,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44447.460185185184</v>
       </c>
       <c r="B625">
@@ -24268,7 +24322,7 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="10">
-        <f>DATEVALUE(MID(F626,5,2) &amp; "-" &amp; LEFT(F626,3) &amp; "-" &amp; MID(F626,8,4)) + TIMEVALUE(MID(F626,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44448.490532407406</v>
       </c>
       <c r="B626">
@@ -24289,7 +24343,7 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="10">
-        <f>DATEVALUE(MID(F627,5,2) &amp; "-" &amp; LEFT(F627,3) &amp; "-" &amp; MID(F627,8,4)) + TIMEVALUE(MID(F627,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44449.501423611109</v>
       </c>
       <c r="B627">
@@ -24310,7 +24364,7 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="10">
-        <f>DATEVALUE(MID(F628,5,2) &amp; "-" &amp; LEFT(F628,3) &amp; "-" &amp; MID(F628,8,4)) + TIMEVALUE(MID(F628,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44451.505925925929</v>
       </c>
       <c r="B628">
@@ -24331,7 +24385,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="10">
-        <f>DATEVALUE(MID(F629,5,2) &amp; "-" &amp; LEFT(F629,3) &amp; "-" &amp; MID(F629,8,4)) + TIMEVALUE(MID(F629,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44452.466099537036</v>
       </c>
       <c r="B629">
@@ -24352,7 +24406,7 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="10">
-        <f>DATEVALUE(MID(F630,5,2) &amp; "-" &amp; LEFT(F630,3) &amp; "-" &amp; MID(F630,8,4)) + TIMEVALUE(MID(F630,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44453.470567129632</v>
       </c>
       <c r="B630">
@@ -24373,7 +24427,7 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="10">
-        <f>DATEVALUE(MID(F631,5,2) &amp; "-" &amp; LEFT(F631,3) &amp; "-" &amp; MID(F631,8,4)) + TIMEVALUE(MID(F631,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44454.476817129631</v>
       </c>
       <c r="B631">
@@ -24394,7 +24448,7 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="10">
-        <f>DATEVALUE(MID(F632,5,2) &amp; "-" &amp; LEFT(F632,3) &amp; "-" &amp; MID(F632,8,4)) + TIMEVALUE(MID(F632,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44455.47074074074</v>
       </c>
       <c r="B632">
@@ -24415,7 +24469,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="10">
-        <f>DATEVALUE(MID(F633,5,2) &amp; "-" &amp; LEFT(F633,3) &amp; "-" &amp; MID(F633,8,4)) + TIMEVALUE(MID(F633,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44456.466400462959</v>
       </c>
       <c r="B633">
@@ -24436,7 +24490,7 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="10">
-        <f>DATEVALUE(MID(F634,5,2) &amp; "-" &amp; LEFT(F634,3) &amp; "-" &amp; MID(F634,8,4)) + TIMEVALUE(MID(F634,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44457.514861111114</v>
       </c>
       <c r="B634">
@@ -24457,7 +24511,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="10">
-        <f>DATEVALUE(MID(F635,5,2) &amp; "-" &amp; LEFT(F635,3) &amp; "-" &amp; MID(F635,8,4)) + TIMEVALUE(MID(F635,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44458.459328703706</v>
       </c>
       <c r="B635">
@@ -24478,7 +24532,7 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="10">
-        <f>DATEVALUE(MID(F636,5,2) &amp; "-" &amp; LEFT(F636,3) &amp; "-" &amp; MID(F636,8,4)) + TIMEVALUE(MID(F636,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44459.451377314814</v>
       </c>
       <c r="B636">
@@ -24499,7 +24553,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="10">
-        <f>DATEVALUE(MID(F637,5,2) &amp; "-" &amp; LEFT(F637,3) &amp; "-" &amp; MID(F637,8,4)) + TIMEVALUE(MID(F637,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44461.477534722224</v>
       </c>
       <c r="B637">
@@ -24520,7 +24574,7 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="10">
-        <f>DATEVALUE(MID(F638,5,2) &amp; "-" &amp; LEFT(F638,3) &amp; "-" &amp; MID(F638,8,4)) + TIMEVALUE(MID(F638,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44473.476712962962</v>
       </c>
       <c r="B638">
@@ -24541,7 +24595,7 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="10">
-        <f>DATEVALUE(MID(F639,5,2) &amp; "-" &amp; LEFT(F639,3) &amp; "-" &amp; MID(F639,8,4)) + TIMEVALUE(MID(F639,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44496.453611111108</v>
       </c>
       <c r="B639">
@@ -24562,7 +24616,7 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="10">
-        <f>DATEVALUE(MID(F640,5,2) &amp; "-" &amp; LEFT(F640,3) &amp; "-" &amp; MID(F640,8,4)) + TIMEVALUE(MID(F640,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44497.455312500002</v>
       </c>
       <c r="B640">
@@ -24583,7 +24637,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="10">
-        <f>DATEVALUE(MID(F641,5,2) &amp; "-" &amp; LEFT(F641,3) &amp; "-" &amp; MID(F641,8,4)) + TIMEVALUE(MID(F641,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44498.43005787037</v>
       </c>
       <c r="B641">
@@ -24604,7 +24658,7 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="10">
-        <f>DATEVALUE(MID(F642,5,2) &amp; "-" &amp; LEFT(F642,3) &amp; "-" &amp; MID(F642,8,4)) + TIMEVALUE(MID(F642,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44500.440995370373</v>
       </c>
       <c r="B642">
@@ -24625,7 +24679,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="10">
-        <f>DATEVALUE(MID(F643,5,2) &amp; "-" &amp; LEFT(F643,3) &amp; "-" &amp; MID(F643,8,4)) + TIMEVALUE(MID(F643,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44501.447870370372</v>
       </c>
       <c r="B643">
@@ -24646,7 +24700,7 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="10">
-        <f>DATEVALUE(MID(F644,5,2) &amp; "-" &amp; LEFT(F644,3) &amp; "-" &amp; MID(F644,8,4)) + TIMEVALUE(MID(F644,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44502.485798611109</v>
       </c>
       <c r="B644">
@@ -24667,7 +24721,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="10">
-        <f>DATEVALUE(MID(F645,5,2) &amp; "-" &amp; LEFT(F645,3) &amp; "-" &amp; MID(F645,8,4)) + TIMEVALUE(MID(F645,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44503.451238425929</v>
       </c>
       <c r="B645">
@@ -24688,7 +24742,7 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="10">
-        <f>DATEVALUE(MID(F646,5,2) &amp; "-" &amp; LEFT(F646,3) &amp; "-" &amp; MID(F646,8,4)) + TIMEVALUE(MID(F646,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44504.448634259257</v>
       </c>
       <c r="B646">
@@ -24709,7 +24763,7 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="10">
-        <f>DATEVALUE(MID(F647,5,2) &amp; "-" &amp; LEFT(F647,3) &amp; "-" &amp; MID(F647,8,4)) + TIMEVALUE(MID(F647,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44505.487650462965</v>
       </c>
       <c r="B647">
@@ -24730,7 +24784,7 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="10">
-        <f>DATEVALUE(MID(F648,5,2) &amp; "-" &amp; LEFT(F648,3) &amp; "-" &amp; MID(F648,8,4)) + TIMEVALUE(MID(F648,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44506.441493055558</v>
       </c>
       <c r="B648">
@@ -24751,7 +24805,7 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="10">
-        <f>DATEVALUE(MID(F649,5,2) &amp; "-" &amp; LEFT(F649,3) &amp; "-" &amp; MID(F649,8,4)) + TIMEVALUE(MID(F649,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44507.492604166669</v>
       </c>
       <c r="B649">
@@ -24772,7 +24826,7 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="10">
-        <f>DATEVALUE(MID(F650,5,2) &amp; "-" &amp; LEFT(F650,3) &amp; "-" &amp; MID(F650,8,4)) + TIMEVALUE(MID(F650,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44508.463483796295</v>
       </c>
       <c r="B650">
@@ -24793,7 +24847,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="10">
-        <f>DATEVALUE(MID(F651,5,2) &amp; "-" &amp; LEFT(F651,3) &amp; "-" &amp; MID(F651,8,4)) + TIMEVALUE(MID(F651,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44509.490243055552</v>
       </c>
       <c r="B651">
@@ -24814,7 +24868,7 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="10">
-        <f>DATEVALUE(MID(F652,5,2) &amp; "-" &amp; LEFT(F652,3) &amp; "-" &amp; MID(F652,8,4)) + TIMEVALUE(MID(F652,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44510.473263888889</v>
       </c>
       <c r="B652">
@@ -24835,7 +24889,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="10">
-        <f>DATEVALUE(MID(F653,5,2) &amp; "-" &amp; LEFT(F653,3) &amp; "-" &amp; MID(F653,8,4)) + TIMEVALUE(MID(F653,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44511.483900462961</v>
       </c>
       <c r="B653">
@@ -24856,7 +24910,7 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="10">
-        <f>DATEVALUE(MID(F654,5,2) &amp; "-" &amp; LEFT(F654,3) &amp; "-" &amp; MID(F654,8,4)) + TIMEVALUE(MID(F654,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44512.506261574075</v>
       </c>
       <c r="B654">
@@ -24877,7 +24931,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="10">
-        <f>DATEVALUE(MID(F655,5,2) &amp; "-" &amp; LEFT(F655,3) &amp; "-" &amp; MID(F655,8,4)) + TIMEVALUE(MID(F655,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44512.530451388891</v>
       </c>
       <c r="B655">
@@ -24898,7 +24952,7 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="10">
-        <f>DATEVALUE(MID(F656,5,2) &amp; "-" &amp; LEFT(F656,3) &amp; "-" &amp; MID(F656,8,4)) + TIMEVALUE(MID(F656,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44513.635682870372</v>
       </c>
       <c r="B656">
@@ -24919,7 +24973,7 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="10">
-        <f>DATEVALUE(MID(F657,5,2) &amp; "-" &amp; LEFT(F657,3) &amp; "-" &amp; MID(F657,8,4)) + TIMEVALUE(MID(F657,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44514.480810185189</v>
       </c>
       <c r="B657">
@@ -24940,7 +24994,7 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="10">
-        <f>DATEVALUE(MID(F658,5,2) &amp; "-" &amp; LEFT(F658,3) &amp; "-" &amp; MID(F658,8,4)) + TIMEVALUE(MID(F658,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44515.495324074072</v>
       </c>
       <c r="B658">
@@ -24961,7 +25015,7 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="10">
-        <f>DATEVALUE(MID(F659,5,2) &amp; "-" &amp; LEFT(F659,3) &amp; "-" &amp; MID(F659,8,4)) + TIMEVALUE(MID(F659,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44516.486770833333</v>
       </c>
       <c r="B659">
@@ -24982,7 +25036,7 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="10">
-        <f>DATEVALUE(MID(F660,5,2) &amp; "-" &amp; LEFT(F660,3) &amp; "-" &amp; MID(F660,8,4)) + TIMEVALUE(MID(F660,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44517.525405092594</v>
       </c>
       <c r="B660">
@@ -25003,7 +25057,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="10">
-        <f>DATEVALUE(MID(F661,5,2) &amp; "-" &amp; LEFT(F661,3) &amp; "-" &amp; MID(F661,8,4)) + TIMEVALUE(MID(F661,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44518.508831018517</v>
       </c>
       <c r="B661">
@@ -25024,7 +25078,7 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="10">
-        <f>DATEVALUE(MID(F662,5,2) &amp; "-" &amp; LEFT(F662,3) &amp; "-" &amp; MID(F662,8,4)) + TIMEVALUE(MID(F662,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44519.506909722222</v>
       </c>
       <c r="B662">
@@ -25045,7 +25099,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="10">
-        <f>DATEVALUE(MID(F663,5,2) &amp; "-" &amp; LEFT(F663,3) &amp; "-" &amp; MID(F663,8,4)) + TIMEVALUE(MID(F663,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44520.549120370371</v>
       </c>
       <c r="B663">
@@ -25066,7 +25120,7 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="10">
-        <f>DATEVALUE(MID(F664,5,2) &amp; "-" &amp; LEFT(F664,3) &amp; "-" &amp; MID(F664,8,4)) + TIMEVALUE(MID(F664,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44521.51699074074</v>
       </c>
       <c r="B664">
@@ -25087,7 +25141,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="10">
-        <f>DATEVALUE(MID(F665,5,2) &amp; "-" &amp; LEFT(F665,3) &amp; "-" &amp; MID(F665,8,4)) + TIMEVALUE(MID(F665,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44522.504965277774</v>
       </c>
       <c r="B665">
@@ -25108,7 +25162,7 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="10">
-        <f>DATEVALUE(MID(F666,5,2) &amp; "-" &amp; LEFT(F666,3) &amp; "-" &amp; MID(F666,8,4)) + TIMEVALUE(MID(F666,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44523.493090277778</v>
       </c>
       <c r="B666">
@@ -25129,7 +25183,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="10">
-        <f>DATEVALUE(MID(F667,5,2) &amp; "-" &amp; LEFT(F667,3) &amp; "-" &amp; MID(F667,8,4)) + TIMEVALUE(MID(F667,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44526.536516203705</v>
       </c>
       <c r="B667">
@@ -25150,7 +25204,7 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="10">
-        <f>DATEVALUE(MID(F668,5,2) &amp; "-" &amp; LEFT(F668,3) &amp; "-" &amp; MID(F668,8,4)) + TIMEVALUE(MID(F668,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44528.495196759257</v>
       </c>
       <c r="B668">
@@ -25171,7 +25225,7 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="10">
-        <f>DATEVALUE(MID(F669,5,2) &amp; "-" &amp; LEFT(F669,3) &amp; "-" &amp; MID(F669,8,4)) + TIMEVALUE(MID(F669,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44530.449004629627</v>
       </c>
       <c r="B669">
@@ -25192,7 +25246,7 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="10">
-        <f>DATEVALUE(MID(F670,5,2) &amp; "-" &amp; LEFT(F670,3) &amp; "-" &amp; MID(F670,8,4)) + TIMEVALUE(MID(F670,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44531.4528125</v>
       </c>
       <c r="B670">
@@ -25213,7 +25267,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="10">
-        <f>DATEVALUE(MID(F671,5,2) &amp; "-" &amp; LEFT(F671,3) &amp; "-" &amp; MID(F671,8,4)) + TIMEVALUE(MID(F671,13,11))</f>
+        <f t="shared" si="4"/>
         <v>44532.499976851854</v>
       </c>
       <c r="B671">
@@ -25234,7 +25288,7 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="10">
-        <f>DATEVALUE(MID(F672,5,2) &amp; "-" &amp; LEFT(F672,3) &amp; "-" &amp; MID(F672,8,4)) + TIMEVALUE(MID(F672,13,11))</f>
+        <f t="shared" ref="A672:A735" si="5">DATEVALUE(MID(F672,5,2) &amp; "-" &amp; LEFT(F672,3) &amp; "-" &amp; MID(F672,8,4)) + TIMEVALUE(MID(F672,13,11))</f>
         <v>44533.487210648149</v>
       </c>
       <c r="B672">
@@ -25255,7 +25309,7 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="10">
-        <f>DATEVALUE(MID(F673,5,2) &amp; "-" &amp; LEFT(F673,3) &amp; "-" &amp; MID(F673,8,4)) + TIMEVALUE(MID(F673,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44535.534907407404</v>
       </c>
       <c r="B673">
@@ -25276,7 +25330,7 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="10">
-        <f>DATEVALUE(MID(F674,5,2) &amp; "-" &amp; LEFT(F674,3) &amp; "-" &amp; MID(F674,8,4)) + TIMEVALUE(MID(F674,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44536.50613425926</v>
       </c>
       <c r="B674">
@@ -25297,7 +25351,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="10">
-        <f>DATEVALUE(MID(F675,5,2) &amp; "-" &amp; LEFT(F675,3) &amp; "-" &amp; MID(F675,8,4)) + TIMEVALUE(MID(F675,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44537.447766203702</v>
       </c>
       <c r="B675">
@@ -25318,7 +25372,7 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="10">
-        <f>DATEVALUE(MID(F676,5,2) &amp; "-" &amp; LEFT(F676,3) &amp; "-" &amp; MID(F676,8,4)) + TIMEVALUE(MID(F676,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44538.504374999997</v>
       </c>
       <c r="B676">
@@ -25339,7 +25393,7 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="10">
-        <f>DATEVALUE(MID(F677,5,2) &amp; "-" &amp; LEFT(F677,3) &amp; "-" &amp; MID(F677,8,4)) + TIMEVALUE(MID(F677,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44550.466423611113</v>
       </c>
       <c r="B677">
@@ -25360,7 +25414,7 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="10">
-        <f>DATEVALUE(MID(F678,5,2) &amp; "-" &amp; LEFT(F678,3) &amp; "-" &amp; MID(F678,8,4)) + TIMEVALUE(MID(F678,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44551.481006944443</v>
       </c>
       <c r="B678">
@@ -25381,7 +25435,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="10">
-        <f>DATEVALUE(MID(F679,5,2) &amp; "-" &amp; LEFT(F679,3) &amp; "-" &amp; MID(F679,8,4)) + TIMEVALUE(MID(F679,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44565.143692129626</v>
       </c>
       <c r="B679">
@@ -25402,7 +25456,7 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="10">
-        <f>DATEVALUE(MID(F680,5,2) &amp; "-" &amp; LEFT(F680,3) &amp; "-" &amp; MID(F680,8,4)) + TIMEVALUE(MID(F680,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44566.162916666668</v>
       </c>
       <c r="B680">
@@ -25423,7 +25477,7 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="10">
-        <f>DATEVALUE(MID(F681,5,2) &amp; "-" &amp; LEFT(F681,3) &amp; "-" &amp; MID(F681,8,4)) + TIMEVALUE(MID(F681,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44566.559571759259</v>
       </c>
       <c r="B681">
@@ -25444,7 +25498,7 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="10">
-        <f>DATEVALUE(MID(F682,5,2) &amp; "-" &amp; LEFT(F682,3) &amp; "-" &amp; MID(F682,8,4)) + TIMEVALUE(MID(F682,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44569.607673611114</v>
       </c>
       <c r="B682">
@@ -25465,7 +25519,7 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="10">
-        <f>DATEVALUE(MID(F683,5,2) &amp; "-" &amp; LEFT(F683,3) &amp; "-" &amp; MID(F683,8,4)) + TIMEVALUE(MID(F683,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44570.591203703705</v>
       </c>
       <c r="B683">
@@ -25486,7 +25540,7 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="10">
-        <f>DATEVALUE(MID(F684,5,2) &amp; "-" &amp; LEFT(F684,3) &amp; "-" &amp; MID(F684,8,4)) + TIMEVALUE(MID(F684,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44571.52239583333</v>
       </c>
       <c r="B684">
@@ -25507,7 +25561,7 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="10">
-        <f>DATEVALUE(MID(F685,5,2) &amp; "-" &amp; LEFT(F685,3) &amp; "-" &amp; MID(F685,8,4)) + TIMEVALUE(MID(F685,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44572.519363425927</v>
       </c>
       <c r="B685">
@@ -25528,7 +25582,7 @@
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="10">
-        <f>DATEVALUE(MID(F686,5,2) &amp; "-" &amp; LEFT(F686,3) &amp; "-" &amp; MID(F686,8,4)) + TIMEVALUE(MID(F686,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44573.543055555558</v>
       </c>
       <c r="B686">
@@ -25549,7 +25603,7 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="10">
-        <f>DATEVALUE(MID(F687,5,2) &amp; "-" &amp; LEFT(F687,3) &amp; "-" &amp; MID(F687,8,4)) + TIMEVALUE(MID(F687,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44574.519155092596</v>
       </c>
       <c r="B687">
@@ -25570,7 +25624,7 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="10">
-        <f>DATEVALUE(MID(F688,5,2) &amp; "-" &amp; LEFT(F688,3) &amp; "-" &amp; MID(F688,8,4)) + TIMEVALUE(MID(F688,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44575.511481481481</v>
       </c>
       <c r="B688">
@@ -25591,7 +25645,7 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="10">
-        <f>DATEVALUE(MID(F689,5,2) &amp; "-" &amp; LEFT(F689,3) &amp; "-" &amp; MID(F689,8,4)) + TIMEVALUE(MID(F689,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44576.522997685184</v>
       </c>
       <c r="B689">
@@ -25612,7 +25666,7 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="10">
-        <f>DATEVALUE(MID(F690,5,2) &amp; "-" &amp; LEFT(F690,3) &amp; "-" &amp; MID(F690,8,4)) + TIMEVALUE(MID(F690,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44577.528587962966</v>
       </c>
       <c r="B690">
@@ -25633,7 +25687,7 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="10">
-        <f>DATEVALUE(MID(F691,5,2) &amp; "-" &amp; LEFT(F691,3) &amp; "-" &amp; MID(F691,8,4)) + TIMEVALUE(MID(F691,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44578.516493055555</v>
       </c>
       <c r="B691">
@@ -25654,7 +25708,7 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="10">
-        <f>DATEVALUE(MID(F692,5,2) &amp; "-" &amp; LEFT(F692,3) &amp; "-" &amp; MID(F692,8,4)) + TIMEVALUE(MID(F692,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44579.524328703701</v>
       </c>
       <c r="B692">
@@ -25675,7 +25729,7 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="10">
-        <f>DATEVALUE(MID(F693,5,2) &amp; "-" &amp; LEFT(F693,3) &amp; "-" &amp; MID(F693,8,4)) + TIMEVALUE(MID(F693,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44580.469988425924</v>
       </c>
       <c r="B693">
@@ -25696,7 +25750,7 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="10">
-        <f>DATEVALUE(MID(F694,5,2) &amp; "-" &amp; LEFT(F694,3) &amp; "-" &amp; MID(F694,8,4)) + TIMEVALUE(MID(F694,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44581.491712962961</v>
       </c>
       <c r="B694">
@@ -25717,7 +25771,7 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="10">
-        <f>DATEVALUE(MID(F695,5,2) &amp; "-" &amp; LEFT(F695,3) &amp; "-" &amp; MID(F695,8,4)) + TIMEVALUE(MID(F695,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44582.49291666667</v>
       </c>
       <c r="B695">
@@ -25738,7 +25792,7 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="10">
-        <f>DATEVALUE(MID(F696,5,2) &amp; "-" &amp; LEFT(F696,3) &amp; "-" &amp; MID(F696,8,4)) + TIMEVALUE(MID(F696,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44586.48578703704</v>
       </c>
       <c r="B696">
@@ -25759,7 +25813,7 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="10">
-        <f>DATEVALUE(MID(F697,5,2) &amp; "-" &amp; LEFT(F697,3) &amp; "-" &amp; MID(F697,8,4)) + TIMEVALUE(MID(F697,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44587.487673611111</v>
       </c>
       <c r="B697">
@@ -25780,7 +25834,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="10">
-        <f>DATEVALUE(MID(F698,5,2) &amp; "-" &amp; LEFT(F698,3) &amp; "-" &amp; MID(F698,8,4)) + TIMEVALUE(MID(F698,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44588.523263888892</v>
       </c>
       <c r="B698">
@@ -25801,7 +25855,7 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="10">
-        <f>DATEVALUE(MID(F699,5,2) &amp; "-" &amp; LEFT(F699,3) &amp; "-" &amp; MID(F699,8,4)) + TIMEVALUE(MID(F699,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44589.441099537034</v>
       </c>
       <c r="B699">
@@ -25822,7 +25876,7 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="10">
-        <f>DATEVALUE(MID(F700,5,2) &amp; "-" &amp; LEFT(F700,3) &amp; "-" &amp; MID(F700,8,4)) + TIMEVALUE(MID(F700,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44591.517696759256</v>
       </c>
       <c r="B700">
@@ -25843,7 +25897,7 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="10">
-        <f>DATEVALUE(MID(F701,5,2) &amp; "-" &amp; LEFT(F701,3) &amp; "-" &amp; MID(F701,8,4)) + TIMEVALUE(MID(F701,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44592.467638888891</v>
       </c>
       <c r="B701">
@@ -25864,7 +25918,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="10">
-        <f>DATEVALUE(MID(F702,5,2) &amp; "-" &amp; LEFT(F702,3) &amp; "-" &amp; MID(F702,8,4)) + TIMEVALUE(MID(F702,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44593.464062500003</v>
       </c>
       <c r="B702">
@@ -25885,7 +25939,7 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="10">
-        <f>DATEVALUE(MID(F703,5,2) &amp; "-" &amp; LEFT(F703,3) &amp; "-" &amp; MID(F703,8,4)) + TIMEVALUE(MID(F703,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44595.496261574073</v>
       </c>
       <c r="B703">
@@ -25906,7 +25960,7 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="10">
-        <f>DATEVALUE(MID(F704,5,2) &amp; "-" &amp; LEFT(F704,3) &amp; "-" &amp; MID(F704,8,4)) + TIMEVALUE(MID(F704,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44596.492754629631</v>
       </c>
       <c r="B704">
@@ -25927,7 +25981,7 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="10">
-        <f>DATEVALUE(MID(F705,5,2) &amp; "-" &amp; LEFT(F705,3) &amp; "-" &amp; MID(F705,8,4)) + TIMEVALUE(MID(F705,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44597.532175925924</v>
       </c>
       <c r="B705">
@@ -25948,7 +26002,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="10">
-        <f>DATEVALUE(MID(F706,5,2) &amp; "-" &amp; LEFT(F706,3) &amp; "-" &amp; MID(F706,8,4)) + TIMEVALUE(MID(F706,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44598.510358796295</v>
       </c>
       <c r="B706">
@@ -25969,7 +26023,7 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707" s="10">
-        <f>DATEVALUE(MID(F707,5,2) &amp; "-" &amp; LEFT(F707,3) &amp; "-" &amp; MID(F707,8,4)) + TIMEVALUE(MID(F707,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44599.463958333334</v>
       </c>
       <c r="B707">
@@ -25990,7 +26044,7 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708" s="10">
-        <f>DATEVALUE(MID(F708,5,2) &amp; "-" &amp; LEFT(F708,3) &amp; "-" &amp; MID(F708,8,4)) + TIMEVALUE(MID(F708,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44602.514525462961</v>
       </c>
       <c r="B708">
@@ -26011,7 +26065,7 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="10">
-        <f>DATEVALUE(MID(F709,5,2) &amp; "-" &amp; LEFT(F709,3) &amp; "-" &amp; MID(F709,8,4)) + TIMEVALUE(MID(F709,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44603.46769675926</v>
       </c>
       <c r="B709">
@@ -26032,7 +26086,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="10">
-        <f>DATEVALUE(MID(F710,5,2) &amp; "-" &amp; LEFT(F710,3) &amp; "-" &amp; MID(F710,8,4)) + TIMEVALUE(MID(F710,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44608.481944444444</v>
       </c>
       <c r="B710">
@@ -26053,7 +26107,7 @@
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A711" s="10">
-        <f>DATEVALUE(MID(F711,5,2) &amp; "-" &amp; LEFT(F711,3) &amp; "-" &amp; MID(F711,8,4)) + TIMEVALUE(MID(F711,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44609.532465277778</v>
       </c>
       <c r="B711">
@@ -26074,7 +26128,7 @@
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A712" s="10">
-        <f>DATEVALUE(MID(F712,5,2) &amp; "-" &amp; LEFT(F712,3) &amp; "-" &amp; MID(F712,8,4)) + TIMEVALUE(MID(F712,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44611.559537037036</v>
       </c>
       <c r="B712">
@@ -26095,7 +26149,7 @@
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713" s="10">
-        <f>DATEVALUE(MID(F713,5,2) &amp; "-" &amp; LEFT(F713,3) &amp; "-" &amp; MID(F713,8,4)) + TIMEVALUE(MID(F713,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44613.483113425929</v>
       </c>
       <c r="B713">
@@ -26116,7 +26170,7 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A714" s="10">
-        <f>DATEVALUE(MID(F714,5,2) &amp; "-" &amp; LEFT(F714,3) &amp; "-" &amp; MID(F714,8,4)) + TIMEVALUE(MID(F714,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44614.461597222224</v>
       </c>
       <c r="B714">
@@ -26137,7 +26191,7 @@
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A715" s="10">
-        <f>DATEVALUE(MID(F715,5,2) &amp; "-" &amp; LEFT(F715,3) &amp; "-" &amp; MID(F715,8,4)) + TIMEVALUE(MID(F715,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44616.500671296293</v>
       </c>
       <c r="B715">
@@ -26158,7 +26212,7 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A716" s="10">
-        <f>DATEVALUE(MID(F716,5,2) &amp; "-" &amp; LEFT(F716,3) &amp; "-" &amp; MID(F716,8,4)) + TIMEVALUE(MID(F716,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44616.570104166669</v>
       </c>
       <c r="B716">
@@ -26179,7 +26233,7 @@
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A717" s="10">
-        <f>DATEVALUE(MID(F717,5,2) &amp; "-" &amp; LEFT(F717,3) &amp; "-" &amp; MID(F717,8,4)) + TIMEVALUE(MID(F717,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44620.516597222224</v>
       </c>
       <c r="B717">
@@ -26200,7 +26254,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A718" s="10">
-        <f>DATEVALUE(MID(F718,5,2) &amp; "-" &amp; LEFT(F718,3) &amp; "-" &amp; MID(F718,8,4)) + TIMEVALUE(MID(F718,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44623.466562499998</v>
       </c>
       <c r="B718">
@@ -26221,7 +26275,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A719" s="10">
-        <f>DATEVALUE(MID(F719,5,2) &amp; "-" &amp; LEFT(F719,3) &amp; "-" &amp; MID(F719,8,4)) + TIMEVALUE(MID(F719,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44628.524918981479</v>
       </c>
       <c r="B719">
@@ -26242,7 +26296,7 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A720" s="10">
-        <f>DATEVALUE(MID(F720,5,2) &amp; "-" &amp; LEFT(F720,3) &amp; "-" &amp; MID(F720,8,4)) + TIMEVALUE(MID(F720,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44629.504004629627</v>
       </c>
       <c r="B720">
@@ -26263,7 +26317,7 @@
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A721" s="10">
-        <f>DATEVALUE(MID(F721,5,2) &amp; "-" &amp; LEFT(F721,3) &amp; "-" &amp; MID(F721,8,4)) + TIMEVALUE(MID(F721,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44646.545624999999</v>
       </c>
       <c r="B721">
@@ -26284,7 +26338,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A722" s="10">
-        <f>DATEVALUE(MID(F722,5,2) &amp; "-" &amp; LEFT(F722,3) &amp; "-" &amp; MID(F722,8,4)) + TIMEVALUE(MID(F722,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44647.479062500002</v>
       </c>
       <c r="B722">
@@ -26305,7 +26359,7 @@
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A723" s="10">
-        <f>DATEVALUE(MID(F723,5,2) &amp; "-" &amp; LEFT(F723,3) &amp; "-" &amp; MID(F723,8,4)) + TIMEVALUE(MID(F723,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44648.461296296293</v>
       </c>
       <c r="B723">
@@ -26326,7 +26380,7 @@
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A724" s="10">
-        <f>DATEVALUE(MID(F724,5,2) &amp; "-" &amp; LEFT(F724,3) &amp; "-" &amp; MID(F724,8,4)) + TIMEVALUE(MID(F724,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44649.444687499999</v>
       </c>
       <c r="B724">
@@ -26347,7 +26401,7 @@
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A725" s="10">
-        <f>DATEVALUE(MID(F725,5,2) &amp; "-" &amp; LEFT(F725,3) &amp; "-" &amp; MID(F725,8,4)) + TIMEVALUE(MID(F725,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44650.459988425922</v>
       </c>
       <c r="B725">
@@ -26368,7 +26422,7 @@
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A726" s="10">
-        <f>DATEVALUE(MID(F726,5,2) &amp; "-" &amp; LEFT(F726,3) &amp; "-" &amp; MID(F726,8,4)) + TIMEVALUE(MID(F726,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44651.451747685183</v>
       </c>
       <c r="B726">
@@ -26389,7 +26443,7 @@
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A727" s="10">
-        <f>DATEVALUE(MID(F727,5,2) &amp; "-" &amp; LEFT(F727,3) &amp; "-" &amp; MID(F727,8,4)) + TIMEVALUE(MID(F727,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44655.45584490741</v>
       </c>
       <c r="B727">
@@ -26410,7 +26464,7 @@
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A728" s="10">
-        <f>DATEVALUE(MID(F728,5,2) &amp; "-" &amp; LEFT(F728,3) &amp; "-" &amp; MID(F728,8,4)) + TIMEVALUE(MID(F728,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44656.487604166665</v>
       </c>
       <c r="B728">
@@ -26431,7 +26485,7 @@
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A729" s="10">
-        <f>DATEVALUE(MID(F729,5,2) &amp; "-" &amp; LEFT(F729,3) &amp; "-" &amp; MID(F729,8,4)) + TIMEVALUE(MID(F729,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44657.520983796298</v>
       </c>
       <c r="B729">
@@ -26452,7 +26506,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A730" s="10">
-        <f>DATEVALUE(MID(F730,5,2) &amp; "-" &amp; LEFT(F730,3) &amp; "-" &amp; MID(F730,8,4)) + TIMEVALUE(MID(F730,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44658.469467592593</v>
       </c>
       <c r="B730">
@@ -26473,7 +26527,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A731" s="10">
-        <f>DATEVALUE(MID(F731,5,2) &amp; "-" &amp; LEFT(F731,3) &amp; "-" &amp; MID(F731,8,4)) + TIMEVALUE(MID(F731,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44659.45103009259</v>
       </c>
       <c r="B731">
@@ -26494,7 +26548,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A732" s="10">
-        <f>DATEVALUE(MID(F732,5,2) &amp; "-" &amp; LEFT(F732,3) &amp; "-" &amp; MID(F732,8,4)) + TIMEVALUE(MID(F732,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44660.495891203704</v>
       </c>
       <c r="B732">
@@ -26515,7 +26569,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A733" s="10">
-        <f>DATEVALUE(MID(F733,5,2) &amp; "-" &amp; LEFT(F733,3) &amp; "-" &amp; MID(F733,8,4)) + TIMEVALUE(MID(F733,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44662.453912037039</v>
       </c>
       <c r="B733">
@@ -26536,7 +26590,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A734" s="10">
-        <f>DATEVALUE(MID(F734,5,2) &amp; "-" &amp; LEFT(F734,3) &amp; "-" &amp; MID(F734,8,4)) + TIMEVALUE(MID(F734,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44663.420034722221</v>
       </c>
       <c r="B734">
@@ -26557,7 +26611,7 @@
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A735" s="10">
-        <f>DATEVALUE(MID(F735,5,2) &amp; "-" &amp; LEFT(F735,3) &amp; "-" &amp; MID(F735,8,4)) + TIMEVALUE(MID(F735,13,11))</f>
+        <f t="shared" si="5"/>
         <v>44664.452141203707</v>
       </c>
       <c r="B735">
@@ -26578,7 +26632,7 @@
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A736" s="10">
-        <f>DATEVALUE(MID(F736,5,2) &amp; "-" &amp; LEFT(F736,3) &amp; "-" &amp; MID(F736,8,4)) + TIMEVALUE(MID(F736,13,11))</f>
+        <f t="shared" ref="A736:A799" si="6">DATEVALUE(MID(F736,5,2) &amp; "-" &amp; LEFT(F736,3) &amp; "-" &amp; MID(F736,8,4)) + TIMEVALUE(MID(F736,13,11))</f>
         <v>44665.42083333333</v>
       </c>
       <c r="B736">
@@ -26599,7 +26653,7 @@
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A737" s="10">
-        <f>DATEVALUE(MID(F737,5,2) &amp; "-" &amp; LEFT(F737,3) &amp; "-" &amp; MID(F737,8,4)) + TIMEVALUE(MID(F737,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44666.420023148145</v>
       </c>
       <c r="B737">
@@ -26620,7 +26674,7 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A738" s="10">
-        <f>DATEVALUE(MID(F738,5,2) &amp; "-" &amp; LEFT(F738,3) &amp; "-" &amp; MID(F738,8,4)) + TIMEVALUE(MID(F738,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44667.474629629629</v>
       </c>
       <c r="B738">
@@ -26641,7 +26695,7 @@
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A739" s="10">
-        <f>DATEVALUE(MID(F739,5,2) &amp; "-" &amp; LEFT(F739,3) &amp; "-" &amp; MID(F739,8,4)) + TIMEVALUE(MID(F739,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44668.449884259258</v>
       </c>
       <c r="B739">
@@ -26662,7 +26716,7 @@
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A740" s="10">
-        <f>DATEVALUE(MID(F740,5,2) &amp; "-" &amp; LEFT(F740,3) &amp; "-" &amp; MID(F740,8,4)) + TIMEVALUE(MID(F740,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44669.447916666664</v>
       </c>
       <c r="B740">
@@ -26683,7 +26737,7 @@
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A741" s="10">
-        <f>DATEVALUE(MID(F741,5,2) &amp; "-" &amp; LEFT(F741,3) &amp; "-" &amp; MID(F741,8,4)) + TIMEVALUE(MID(F741,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44670.485219907408</v>
       </c>
       <c r="B741">
@@ -26704,7 +26758,7 @@
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A742" s="10">
-        <f>DATEVALUE(MID(F742,5,2) &amp; "-" &amp; LEFT(F742,3) &amp; "-" &amp; MID(F742,8,4)) + TIMEVALUE(MID(F742,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44671.476782407408</v>
       </c>
       <c r="B742">
@@ -26725,7 +26779,7 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A743" s="10">
-        <f>DATEVALUE(MID(F743,5,2) &amp; "-" &amp; LEFT(F743,3) &amp; "-" &amp; MID(F743,8,4)) + TIMEVALUE(MID(F743,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44676.500937500001</v>
       </c>
       <c r="B743">
@@ -26746,7 +26800,7 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A744" s="10">
-        <f>DATEVALUE(MID(F744,5,2) &amp; "-" &amp; LEFT(F744,3) &amp; "-" &amp; MID(F744,8,4)) + TIMEVALUE(MID(F744,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44677.416331018518</v>
       </c>
       <c r="B744">
@@ -26767,7 +26821,7 @@
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A745" s="10">
-        <f>DATEVALUE(MID(F745,5,2) &amp; "-" &amp; LEFT(F745,3) &amp; "-" &amp; MID(F745,8,4)) + TIMEVALUE(MID(F745,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44678.463599537034</v>
       </c>
       <c r="B745">
@@ -26788,7 +26842,7 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A746" s="10">
-        <f>DATEVALUE(MID(F746,5,2) &amp; "-" &amp; LEFT(F746,3) &amp; "-" &amp; MID(F746,8,4)) + TIMEVALUE(MID(F746,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44679.442800925928</v>
       </c>
       <c r="B746">
@@ -26809,7 +26863,7 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747" s="10">
-        <f>DATEVALUE(MID(F747,5,2) &amp; "-" &amp; LEFT(F747,3) &amp; "-" &amp; MID(F747,8,4)) + TIMEVALUE(MID(F747,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44686.452013888891</v>
       </c>
       <c r="B747">
@@ -26830,7 +26884,7 @@
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A748" s="10">
-        <f>DATEVALUE(MID(F748,5,2) &amp; "-" &amp; LEFT(F748,3) &amp; "-" &amp; MID(F748,8,4)) + TIMEVALUE(MID(F748,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44687.46733796296</v>
       </c>
       <c r="B748">
@@ -26851,7 +26905,7 @@
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A749" s="10">
-        <f>DATEVALUE(MID(F749,5,2) &amp; "-" &amp; LEFT(F749,3) &amp; "-" &amp; MID(F749,8,4)) + TIMEVALUE(MID(F749,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44688.386886574073</v>
       </c>
       <c r="B749">
@@ -26872,7 +26926,7 @@
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A750" s="10">
-        <f>DATEVALUE(MID(F750,5,2) &amp; "-" &amp; LEFT(F750,3) &amp; "-" &amp; MID(F750,8,4)) + TIMEVALUE(MID(F750,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44689.482060185182</v>
       </c>
       <c r="B750">
@@ -26893,7 +26947,7 @@
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A751" s="10">
-        <f>DATEVALUE(MID(F751,5,2) &amp; "-" &amp; LEFT(F751,3) &amp; "-" &amp; MID(F751,8,4)) + TIMEVALUE(MID(F751,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44690.40792824074</v>
       </c>
       <c r="B751">
@@ -26914,7 +26968,7 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A752" s="10">
-        <f>DATEVALUE(MID(F752,5,2) &amp; "-" &amp; LEFT(F752,3) &amp; "-" &amp; MID(F752,8,4)) + TIMEVALUE(MID(F752,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44691.451111111113</v>
       </c>
       <c r="B752">
@@ -26935,7 +26989,7 @@
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A753" s="10">
-        <f>DATEVALUE(MID(F753,5,2) &amp; "-" &amp; LEFT(F753,3) &amp; "-" &amp; MID(F753,8,4)) + TIMEVALUE(MID(F753,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44692.466249999998</v>
       </c>
       <c r="B753">
@@ -26956,7 +27010,7 @@
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A754" s="10">
-        <f>DATEVALUE(MID(F754,5,2) &amp; "-" &amp; LEFT(F754,3) &amp; "-" &amp; MID(F754,8,4)) + TIMEVALUE(MID(F754,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44693.451805555553</v>
       </c>
       <c r="B754">
@@ -26977,7 +27031,7 @@
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A755" s="10">
-        <f>DATEVALUE(MID(F755,5,2) &amp; "-" &amp; LEFT(F755,3) &amp; "-" &amp; MID(F755,8,4)) + TIMEVALUE(MID(F755,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44694.437407407408</v>
       </c>
       <c r="B755">
@@ -26998,7 +27052,7 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A756" s="10">
-        <f>DATEVALUE(MID(F756,5,2) &amp; "-" &amp; LEFT(F756,3) &amp; "-" &amp; MID(F756,8,4)) + TIMEVALUE(MID(F756,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44694.509386574071</v>
       </c>
       <c r="B756">
@@ -27019,7 +27073,7 @@
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A757" s="10">
-        <f>DATEVALUE(MID(F757,5,2) &amp; "-" &amp; LEFT(F757,3) &amp; "-" &amp; MID(F757,8,4)) + TIMEVALUE(MID(F757,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44695.429791666669</v>
       </c>
       <c r="B757">
@@ -27040,7 +27094,7 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A758" s="10">
-        <f>DATEVALUE(MID(F758,5,2) &amp; "-" &amp; LEFT(F758,3) &amp; "-" &amp; MID(F758,8,4)) + TIMEVALUE(MID(F758,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44696.455960648149</v>
       </c>
       <c r="B758">
@@ -27061,7 +27115,7 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A759" s="10">
-        <f>DATEVALUE(MID(F759,5,2) &amp; "-" &amp; LEFT(F759,3) &amp; "-" &amp; MID(F759,8,4)) + TIMEVALUE(MID(F759,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44697.424722222226</v>
       </c>
       <c r="B759">
@@ -27082,7 +27136,7 @@
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A760" s="10">
-        <f>DATEVALUE(MID(F760,5,2) &amp; "-" &amp; LEFT(F760,3) &amp; "-" &amp; MID(F760,8,4)) + TIMEVALUE(MID(F760,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44698.416226851848</v>
       </c>
       <c r="B760">
@@ -27103,7 +27157,7 @@
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A761" s="10">
-        <f>DATEVALUE(MID(F761,5,2) &amp; "-" &amp; LEFT(F761,3) &amp; "-" &amp; MID(F761,8,4)) + TIMEVALUE(MID(F761,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44699.462500000001</v>
       </c>
       <c r="B761">
@@ -27124,7 +27178,7 @@
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A762" s="10">
-        <f>DATEVALUE(MID(F762,5,2) &amp; "-" &amp; LEFT(F762,3) &amp; "-" &amp; MID(F762,8,4)) + TIMEVALUE(MID(F762,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44700.421851851854</v>
       </c>
       <c r="B762">
@@ -27145,7 +27199,7 @@
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A763" s="10">
-        <f>DATEVALUE(MID(F763,5,2) &amp; "-" &amp; LEFT(F763,3) &amp; "-" &amp; MID(F763,8,4)) + TIMEVALUE(MID(F763,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44701.459374999999</v>
       </c>
       <c r="B763">
@@ -27166,7 +27220,7 @@
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A764" s="10">
-        <f>DATEVALUE(MID(F764,5,2) &amp; "-" &amp; LEFT(F764,3) &amp; "-" &amp; MID(F764,8,4)) + TIMEVALUE(MID(F764,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44702.489120370374</v>
       </c>
       <c r="B764">
@@ -27187,7 +27241,7 @@
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A765" s="10">
-        <f>DATEVALUE(MID(F765,5,2) &amp; "-" &amp; LEFT(F765,3) &amp; "-" &amp; MID(F765,8,4)) + TIMEVALUE(MID(F765,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44703.454282407409</v>
       </c>
       <c r="B765">
@@ -27208,7 +27262,7 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A766" s="10">
-        <f>DATEVALUE(MID(F766,5,2) &amp; "-" &amp; LEFT(F766,3) &amp; "-" &amp; MID(F766,8,4)) + TIMEVALUE(MID(F766,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44704.447291666664</v>
       </c>
       <c r="B766">
@@ -27229,7 +27283,7 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A767" s="10">
-        <f>DATEVALUE(MID(F767,5,2) &amp; "-" &amp; LEFT(F767,3) &amp; "-" &amp; MID(F767,8,4)) + TIMEVALUE(MID(F767,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44705.457812499997</v>
       </c>
       <c r="B767">
@@ -27250,7 +27304,7 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A768" s="10">
-        <f>DATEVALUE(MID(F768,5,2) &amp; "-" &amp; LEFT(F768,3) &amp; "-" &amp; MID(F768,8,4)) + TIMEVALUE(MID(F768,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44706.465370370373</v>
       </c>
       <c r="B768">
@@ -27271,7 +27325,7 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A769" s="10">
-        <f>DATEVALUE(MID(F769,5,2) &amp; "-" &amp; LEFT(F769,3) &amp; "-" &amp; MID(F769,8,4)) + TIMEVALUE(MID(F769,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44707.477094907408</v>
       </c>
       <c r="B769">
@@ -27292,7 +27346,7 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A770" s="10">
-        <f>DATEVALUE(MID(F770,5,2) &amp; "-" &amp; LEFT(F770,3) &amp; "-" &amp; MID(F770,8,4)) + TIMEVALUE(MID(F770,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44708.415648148148</v>
       </c>
       <c r="B770">
@@ -27313,7 +27367,7 @@
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A771" s="10">
-        <f>DATEVALUE(MID(F771,5,2) &amp; "-" &amp; LEFT(F771,3) &amp; "-" &amp; MID(F771,8,4)) + TIMEVALUE(MID(F771,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44709.475983796299</v>
       </c>
       <c r="B771">
@@ -27334,7 +27388,7 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A772" s="10">
-        <f>DATEVALUE(MID(F772,5,2) &amp; "-" &amp; LEFT(F772,3) &amp; "-" &amp; MID(F772,8,4)) + TIMEVALUE(MID(F772,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44710.464733796296</v>
       </c>
       <c r="B772">
@@ -27355,7 +27409,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A773" s="10">
-        <f>DATEVALUE(MID(F773,5,2) &amp; "-" &amp; LEFT(F773,3) &amp; "-" &amp; MID(F773,8,4)) + TIMEVALUE(MID(F773,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44711.490787037037</v>
       </c>
       <c r="B773">
@@ -27376,7 +27430,7 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774" s="10">
-        <f>DATEVALUE(MID(F774,5,2) &amp; "-" &amp; LEFT(F774,3) &amp; "-" &amp; MID(F774,8,4)) + TIMEVALUE(MID(F774,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44712.404641203706</v>
       </c>
       <c r="B774">
@@ -27397,7 +27451,7 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775" s="10">
-        <f>DATEVALUE(MID(F775,5,2) &amp; "-" &amp; LEFT(F775,3) &amp; "-" &amp; MID(F775,8,4)) + TIMEVALUE(MID(F775,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44713.397465277776</v>
       </c>
       <c r="B775">
@@ -27418,7 +27472,7 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776" s="10">
-        <f>DATEVALUE(MID(F776,5,2) &amp; "-" &amp; LEFT(F776,3) &amp; "-" &amp; MID(F776,8,4)) + TIMEVALUE(MID(F776,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44714.454652777778</v>
       </c>
       <c r="B776">
@@ -27439,7 +27493,7 @@
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A777" s="10">
-        <f>DATEVALUE(MID(F777,5,2) &amp; "-" &amp; LEFT(F777,3) &amp; "-" &amp; MID(F777,8,4)) + TIMEVALUE(MID(F777,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44715.416666666664</v>
       </c>
       <c r="B777">
@@ -27460,7 +27514,7 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A778" s="10">
-        <f>DATEVALUE(MID(F778,5,2) &amp; "-" &amp; LEFT(F778,3) &amp; "-" &amp; MID(F778,8,4)) + TIMEVALUE(MID(F778,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44716.459386574075</v>
       </c>
       <c r="B778">
@@ -27481,7 +27535,7 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A779" s="10">
-        <f>DATEVALUE(MID(F779,5,2) &amp; "-" &amp; LEFT(F779,3) &amp; "-" &amp; MID(F779,8,4)) + TIMEVALUE(MID(F779,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44717.509814814817</v>
       </c>
       <c r="B779">
@@ -27502,7 +27556,7 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A780" s="10">
-        <f>DATEVALUE(MID(F780,5,2) &amp; "-" &amp; LEFT(F780,3) &amp; "-" &amp; MID(F780,8,4)) + TIMEVALUE(MID(F780,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44718.45579861111</v>
       </c>
       <c r="B780">
@@ -27523,7 +27577,7 @@
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A781" s="10">
-        <f>DATEVALUE(MID(F781,5,2) &amp; "-" &amp; LEFT(F781,3) &amp; "-" &amp; MID(F781,8,4)) + TIMEVALUE(MID(F781,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44719.470543981479</v>
       </c>
       <c r="B781">
@@ -27544,7 +27598,7 @@
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A782" s="10">
-        <f>DATEVALUE(MID(F782,5,2) &amp; "-" &amp; LEFT(F782,3) &amp; "-" &amp; MID(F782,8,4)) + TIMEVALUE(MID(F782,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44720.450162037036</v>
       </c>
       <c r="B782">
@@ -27565,7 +27619,7 @@
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A783" s="10">
-        <f>DATEVALUE(MID(F783,5,2) &amp; "-" &amp; LEFT(F783,3) &amp; "-" &amp; MID(F783,8,4)) + TIMEVALUE(MID(F783,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44721.453611111108</v>
       </c>
       <c r="B783">
@@ -27586,7 +27640,7 @@
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A784" s="10">
-        <f>DATEVALUE(MID(F784,5,2) &amp; "-" &amp; LEFT(F784,3) &amp; "-" &amp; MID(F784,8,4)) + TIMEVALUE(MID(F784,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44722.516145833331</v>
       </c>
       <c r="B784">
@@ -27607,7 +27661,7 @@
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A785" s="10">
-        <f>DATEVALUE(MID(F785,5,2) &amp; "-" &amp; LEFT(F785,3) &amp; "-" &amp; MID(F785,8,4)) + TIMEVALUE(MID(F785,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44723.517233796294</v>
       </c>
       <c r="B785">
@@ -27628,7 +27682,7 @@
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A786" s="10">
-        <f>DATEVALUE(MID(F786,5,2) &amp; "-" &amp; LEFT(F786,3) &amp; "-" &amp; MID(F786,8,4)) + TIMEVALUE(MID(F786,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44724.437592592592</v>
       </c>
       <c r="B786">
@@ -27649,7 +27703,7 @@
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A787" s="10">
-        <f>DATEVALUE(MID(F787,5,2) &amp; "-" &amp; LEFT(F787,3) &amp; "-" &amp; MID(F787,8,4)) + TIMEVALUE(MID(F787,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44725.468587962961</v>
       </c>
       <c r="B787">
@@ -27670,7 +27724,7 @@
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A788" s="10">
-        <f>DATEVALUE(MID(F788,5,2) &amp; "-" &amp; LEFT(F788,3) &amp; "-" &amp; MID(F788,8,4)) + TIMEVALUE(MID(F788,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44726.441400462965</v>
       </c>
       <c r="B788">
@@ -27691,7 +27745,7 @@
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A789" s="10">
-        <f>DATEVALUE(MID(F789,5,2) &amp; "-" &amp; LEFT(F789,3) &amp; "-" &amp; MID(F789,8,4)) + TIMEVALUE(MID(F789,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44727.453148148146</v>
       </c>
       <c r="B789">
@@ -27712,7 +27766,7 @@
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A790" s="10">
-        <f>DATEVALUE(MID(F790,5,2) &amp; "-" &amp; LEFT(F790,3) &amp; "-" &amp; MID(F790,8,4)) + TIMEVALUE(MID(F790,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44728.527071759258</v>
       </c>
       <c r="B790">
@@ -27733,7 +27787,7 @@
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A791" s="10">
-        <f>DATEVALUE(MID(F791,5,2) &amp; "-" &amp; LEFT(F791,3) &amp; "-" &amp; MID(F791,8,4)) + TIMEVALUE(MID(F791,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44729.48238425926</v>
       </c>
       <c r="B791">
@@ -27754,7 +27808,7 @@
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A792" s="10">
-        <f>DATEVALUE(MID(F792,5,2) &amp; "-" &amp; LEFT(F792,3) &amp; "-" &amp; MID(F792,8,4)) + TIMEVALUE(MID(F792,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44730.487951388888</v>
       </c>
       <c r="B792">
@@ -27775,7 +27829,7 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A793" s="10">
-        <f>DATEVALUE(MID(F793,5,2) &amp; "-" &amp; LEFT(F793,3) &amp; "-" &amp; MID(F793,8,4)) + TIMEVALUE(MID(F793,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44731.48642361111</v>
       </c>
       <c r="B793">
@@ -27796,7 +27850,7 @@
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A794" s="10">
-        <f>DATEVALUE(MID(F794,5,2) &amp; "-" &amp; LEFT(F794,3) &amp; "-" &amp; MID(F794,8,4)) + TIMEVALUE(MID(F794,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44732.447372685187</v>
       </c>
       <c r="B794">
@@ -27817,7 +27871,7 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A795" s="10">
-        <f>DATEVALUE(MID(F795,5,2) &amp; "-" &amp; LEFT(F795,3) &amp; "-" &amp; MID(F795,8,4)) + TIMEVALUE(MID(F795,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44733.456886574073</v>
       </c>
       <c r="B795">
@@ -27838,7 +27892,7 @@
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A796" s="10">
-        <f>DATEVALUE(MID(F796,5,2) &amp; "-" &amp; LEFT(F796,3) &amp; "-" &amp; MID(F796,8,4)) + TIMEVALUE(MID(F796,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44734.422534722224</v>
       </c>
       <c r="B796">
@@ -27859,7 +27913,7 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A797" s="10">
-        <f>DATEVALUE(MID(F797,5,2) &amp; "-" &amp; LEFT(F797,3) &amp; "-" &amp; MID(F797,8,4)) + TIMEVALUE(MID(F797,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44735.391527777778</v>
       </c>
       <c r="B797">
@@ -27880,7 +27934,7 @@
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A798" s="10">
-        <f>DATEVALUE(MID(F798,5,2) &amp; "-" &amp; LEFT(F798,3) &amp; "-" &amp; MID(F798,8,4)) + TIMEVALUE(MID(F798,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44736.451504629629</v>
       </c>
       <c r="B798">
@@ -27901,7 +27955,7 @@
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A799" s="10">
-        <f>DATEVALUE(MID(F799,5,2) &amp; "-" &amp; LEFT(F799,3) &amp; "-" &amp; MID(F799,8,4)) + TIMEVALUE(MID(F799,13,11))</f>
+        <f t="shared" si="6"/>
         <v>44737.500879629632</v>
       </c>
       <c r="B799">
@@ -27922,7 +27976,7 @@
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A800" s="10">
-        <f>DATEVALUE(MID(F800,5,2) &amp; "-" &amp; LEFT(F800,3) &amp; "-" &amp; MID(F800,8,4)) + TIMEVALUE(MID(F800,13,11))</f>
+        <f t="shared" ref="A800:A863" si="7">DATEVALUE(MID(F800,5,2) &amp; "-" &amp; LEFT(F800,3) &amp; "-" &amp; MID(F800,8,4)) + TIMEVALUE(MID(F800,13,11))</f>
         <v>44738.503472222219</v>
       </c>
       <c r="B800">
@@ -27943,7 +27997,7 @@
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A801" s="10">
-        <f>DATEVALUE(MID(F801,5,2) &amp; "-" &amp; LEFT(F801,3) &amp; "-" &amp; MID(F801,8,4)) + TIMEVALUE(MID(F801,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44739.445277777777</v>
       </c>
       <c r="B801">
@@ -27964,7 +28018,7 @@
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A802" s="10">
-        <f>DATEVALUE(MID(F802,5,2) &amp; "-" &amp; LEFT(F802,3) &amp; "-" &amp; MID(F802,8,4)) + TIMEVALUE(MID(F802,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44740.429710648146</v>
       </c>
       <c r="B802">
@@ -27985,7 +28039,7 @@
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A803" s="10">
-        <f>DATEVALUE(MID(F803,5,2) &amp; "-" &amp; LEFT(F803,3) &amp; "-" &amp; MID(F803,8,4)) + TIMEVALUE(MID(F803,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44741.408148148148</v>
       </c>
       <c r="B803">
@@ -28006,7 +28060,7 @@
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A804" s="10">
-        <f>DATEVALUE(MID(F804,5,2) &amp; "-" &amp; LEFT(F804,3) &amp; "-" &amp; MID(F804,8,4)) + TIMEVALUE(MID(F804,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44742.401770833334</v>
       </c>
       <c r="B804">
@@ -28027,7 +28081,7 @@
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A805" s="10">
-        <f>DATEVALUE(MID(F805,5,2) &amp; "-" &amp; LEFT(F805,3) &amp; "-" &amp; MID(F805,8,4)) + TIMEVALUE(MID(F805,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44743.443715277775</v>
       </c>
       <c r="B805">
@@ -28048,7 +28102,7 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A806" s="10">
-        <f>DATEVALUE(MID(F806,5,2) &amp; "-" &amp; LEFT(F806,3) &amp; "-" &amp; MID(F806,8,4)) + TIMEVALUE(MID(F806,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44744.477719907409</v>
       </c>
       <c r="B806">
@@ -28069,7 +28123,7 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A807" s="10">
-        <f>DATEVALUE(MID(F807,5,2) &amp; "-" &amp; LEFT(F807,3) &amp; "-" &amp; MID(F807,8,4)) + TIMEVALUE(MID(F807,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44745.505162037036</v>
       </c>
       <c r="B807">
@@ -28090,7 +28144,7 @@
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A808" s="10">
-        <f>DATEVALUE(MID(F808,5,2) &amp; "-" &amp; LEFT(F808,3) &amp; "-" &amp; MID(F808,8,4)) + TIMEVALUE(MID(F808,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44746.464918981481</v>
       </c>
       <c r="B808">
@@ -28111,7 +28165,7 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A809" s="10">
-        <f>DATEVALUE(MID(F809,5,2) &amp; "-" &amp; LEFT(F809,3) &amp; "-" &amp; MID(F809,8,4)) + TIMEVALUE(MID(F809,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44747.459085648145</v>
       </c>
       <c r="B809">
@@ -28132,7 +28186,7 @@
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A810" s="10">
-        <f>DATEVALUE(MID(F810,5,2) &amp; "-" &amp; LEFT(F810,3) &amp; "-" &amp; MID(F810,8,4)) + TIMEVALUE(MID(F810,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44748.413171296299</v>
       </c>
       <c r="B810">
@@ -28153,7 +28207,7 @@
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A811" s="10">
-        <f>DATEVALUE(MID(F811,5,2) &amp; "-" &amp; LEFT(F811,3) &amp; "-" &amp; MID(F811,8,4)) + TIMEVALUE(MID(F811,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44749.422222222223</v>
       </c>
       <c r="B811">
@@ -28174,7 +28228,7 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812" s="10">
-        <f>DATEVALUE(MID(F812,5,2) &amp; "-" &amp; LEFT(F812,3) &amp; "-" &amp; MID(F812,8,4)) + TIMEVALUE(MID(F812,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44750.461134259262</v>
       </c>
       <c r="B812">
@@ -28195,7 +28249,7 @@
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A813" s="10">
-        <f>DATEVALUE(MID(F813,5,2) &amp; "-" &amp; LEFT(F813,3) &amp; "-" &amp; MID(F813,8,4)) + TIMEVALUE(MID(F813,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44751.508136574077</v>
       </c>
       <c r="B813">
@@ -28216,7 +28270,7 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A814" s="10">
-        <f>DATEVALUE(MID(F814,5,2) &amp; "-" &amp; LEFT(F814,3) &amp; "-" &amp; MID(F814,8,4)) + TIMEVALUE(MID(F814,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44752.444467592592</v>
       </c>
       <c r="B814">
@@ -28237,7 +28291,7 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A815" s="10">
-        <f>DATEVALUE(MID(F815,5,2) &amp; "-" &amp; LEFT(F815,3) &amp; "-" &amp; MID(F815,8,4)) + TIMEVALUE(MID(F815,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44754.465081018519</v>
       </c>
       <c r="B815">
@@ -28258,7 +28312,7 @@
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A816" s="10">
-        <f>DATEVALUE(MID(F816,5,2) &amp; "-" &amp; LEFT(F816,3) &amp; "-" &amp; MID(F816,8,4)) + TIMEVALUE(MID(F816,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44754.473912037036</v>
       </c>
       <c r="B816">
@@ -28279,7 +28333,7 @@
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A817" s="10">
-        <f>DATEVALUE(MID(F817,5,2) &amp; "-" &amp; LEFT(F817,3) &amp; "-" &amp; MID(F817,8,4)) + TIMEVALUE(MID(F817,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44757.489895833336</v>
       </c>
       <c r="B817">
@@ -28300,7 +28354,7 @@
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A818" s="10">
-        <f>DATEVALUE(MID(F818,5,2) &amp; "-" &amp; LEFT(F818,3) &amp; "-" &amp; MID(F818,8,4)) + TIMEVALUE(MID(F818,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44761.485891203702</v>
       </c>
       <c r="B818">
@@ -28321,7 +28375,7 @@
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A819" s="10">
-        <f>DATEVALUE(MID(F819,5,2) &amp; "-" &amp; LEFT(F819,3) &amp; "-" &amp; MID(F819,8,4)) + TIMEVALUE(MID(F819,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44762.486597222225</v>
       </c>
       <c r="B819">
@@ -28342,7 +28396,7 @@
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A820" s="10">
-        <f>DATEVALUE(MID(F820,5,2) &amp; "-" &amp; LEFT(F820,3) &amp; "-" &amp; MID(F820,8,4)) + TIMEVALUE(MID(F820,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44763.500590277778</v>
       </c>
       <c r="B820">
@@ -28363,7 +28417,7 @@
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A821" s="10">
-        <f>DATEVALUE(MID(F821,5,2) &amp; "-" &amp; LEFT(F821,3) &amp; "-" &amp; MID(F821,8,4)) + TIMEVALUE(MID(F821,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44764.514409722222</v>
       </c>
       <c r="B821">
@@ -28384,7 +28438,7 @@
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A822" s="10">
-        <f>DATEVALUE(MID(F822,5,2) &amp; "-" &amp; LEFT(F822,3) &amp; "-" &amp; MID(F822,8,4)) + TIMEVALUE(MID(F822,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44765.467870370368</v>
       </c>
       <c r="B822">
@@ -28405,7 +28459,7 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A823" s="10">
-        <f>DATEVALUE(MID(F823,5,2) &amp; "-" &amp; LEFT(F823,3) &amp; "-" &amp; MID(F823,8,4)) + TIMEVALUE(MID(F823,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44766.504849537036</v>
       </c>
       <c r="B823">
@@ -28426,7 +28480,7 @@
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A824" s="10">
-        <f>DATEVALUE(MID(F824,5,2) &amp; "-" &amp; LEFT(F824,3) &amp; "-" &amp; MID(F824,8,4)) + TIMEVALUE(MID(F824,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44768.449849537035</v>
       </c>
       <c r="B824">
@@ -28447,7 +28501,7 @@
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A825" s="10">
-        <f>DATEVALUE(MID(F825,5,2) &amp; "-" &amp; LEFT(F825,3) &amp; "-" &amp; MID(F825,8,4)) + TIMEVALUE(MID(F825,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44768.515451388892</v>
       </c>
       <c r="B825">
@@ -28468,7 +28522,7 @@
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A826" s="10">
-        <f>DATEVALUE(MID(F826,5,2) &amp; "-" &amp; LEFT(F826,3) &amp; "-" &amp; MID(F826,8,4)) + TIMEVALUE(MID(F826,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44769.453935185185</v>
       </c>
       <c r="B826">
@@ -28489,7 +28543,7 @@
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A827" s="10">
-        <f>DATEVALUE(MID(F827,5,2) &amp; "-" &amp; LEFT(F827,3) &amp; "-" &amp; MID(F827,8,4)) + TIMEVALUE(MID(F827,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44770.47047453704</v>
       </c>
       <c r="B827">
@@ -28510,7 +28564,7 @@
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A828" s="10">
-        <f>DATEVALUE(MID(F828,5,2) &amp; "-" &amp; LEFT(F828,3) &amp; "-" &amp; MID(F828,8,4)) + TIMEVALUE(MID(F828,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44771.482476851852</v>
       </c>
       <c r="B828">
@@ -28531,7 +28585,7 @@
     </row>
     <row r="829" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A829" s="10">
-        <f>DATEVALUE(MID(F829,5,2) &amp; "-" &amp; LEFT(F829,3) &amp; "-" &amp; MID(F829,8,4)) + TIMEVALUE(MID(F829,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44772.504317129627</v>
       </c>
       <c r="B829">
@@ -28552,7 +28606,7 @@
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A830" s="10">
-        <f>DATEVALUE(MID(F830,5,2) &amp; "-" &amp; LEFT(F830,3) &amp; "-" &amp; MID(F830,8,4)) + TIMEVALUE(MID(F830,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44773.4528587963</v>
       </c>
       <c r="B830">
@@ -28573,7 +28627,7 @@
     </row>
     <row r="831" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A831" s="10">
-        <f>DATEVALUE(MID(F831,5,2) &amp; "-" &amp; LEFT(F831,3) &amp; "-" &amp; MID(F831,8,4)) + TIMEVALUE(MID(F831,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44774.495173611111</v>
       </c>
       <c r="B831">
@@ -28594,7 +28648,7 @@
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A832" s="10">
-        <f>DATEVALUE(MID(F832,5,2) &amp; "-" &amp; LEFT(F832,3) &amp; "-" &amp; MID(F832,8,4)) + TIMEVALUE(MID(F832,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44775.484224537038</v>
       </c>
       <c r="B832">
@@ -28615,7 +28669,7 @@
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A833" s="10">
-        <f>DATEVALUE(MID(F833,5,2) &amp; "-" &amp; LEFT(F833,3) &amp; "-" &amp; MID(F833,8,4)) + TIMEVALUE(MID(F833,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44776.47619212963</v>
       </c>
       <c r="B833">
@@ -28636,7 +28690,7 @@
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A834" s="10">
-        <f>DATEVALUE(MID(F834,5,2) &amp; "-" &amp; LEFT(F834,3) &amp; "-" &amp; MID(F834,8,4)) + TIMEVALUE(MID(F834,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44777.4374537037</v>
       </c>
       <c r="B834">
@@ -28657,7 +28711,7 @@
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A835" s="10">
-        <f>DATEVALUE(MID(F835,5,2) &amp; "-" &amp; LEFT(F835,3) &amp; "-" &amp; MID(F835,8,4)) + TIMEVALUE(MID(F835,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44778.439027777778</v>
       </c>
       <c r="B835">
@@ -28678,7 +28732,7 @@
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A836" s="10">
-        <f>DATEVALUE(MID(F836,5,2) &amp; "-" &amp; LEFT(F836,3) &amp; "-" &amp; MID(F836,8,4)) + TIMEVALUE(MID(F836,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44780.488495370373</v>
       </c>
       <c r="B836">
@@ -28699,7 +28753,7 @@
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A837" s="10">
-        <f>DATEVALUE(MID(F837,5,2) &amp; "-" &amp; LEFT(F837,3) &amp; "-" &amp; MID(F837,8,4)) + TIMEVALUE(MID(F837,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44781.433599537035</v>
       </c>
       <c r="B837">
@@ -28720,7 +28774,7 @@
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A838" s="10">
-        <f>DATEVALUE(MID(F838,5,2) &amp; "-" &amp; LEFT(F838,3) &amp; "-" &amp; MID(F838,8,4)) + TIMEVALUE(MID(F838,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44783.45921296296</v>
       </c>
       <c r="B838">
@@ -28741,7 +28795,7 @@
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A839" s="10">
-        <f>DATEVALUE(MID(F839,5,2) &amp; "-" &amp; LEFT(F839,3) &amp; "-" &amp; MID(F839,8,4)) + TIMEVALUE(MID(F839,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44783.466203703705</v>
       </c>
       <c r="B839">
@@ -28762,7 +28816,7 @@
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A840" s="10">
-        <f>DATEVALUE(MID(F840,5,2) &amp; "-" &amp; LEFT(F840,3) &amp; "-" &amp; MID(F840,8,4)) + TIMEVALUE(MID(F840,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44784.391655092593</v>
       </c>
       <c r="B840">
@@ -28783,7 +28837,7 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A841" s="10">
-        <f>DATEVALUE(MID(F841,5,2) &amp; "-" &amp; LEFT(F841,3) &amp; "-" &amp; MID(F841,8,4)) + TIMEVALUE(MID(F841,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44785.475717592592</v>
       </c>
       <c r="B841">
@@ -28804,7 +28858,7 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A842" s="10">
-        <f>DATEVALUE(MID(F842,5,2) &amp; "-" &amp; LEFT(F842,3) &amp; "-" &amp; MID(F842,8,4)) + TIMEVALUE(MID(F842,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44786.450821759259</v>
       </c>
       <c r="B842">
@@ -28825,7 +28879,7 @@
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A843" s="10">
-        <f>DATEVALUE(MID(F843,5,2) &amp; "-" &amp; LEFT(F843,3) &amp; "-" &amp; MID(F843,8,4)) + TIMEVALUE(MID(F843,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44787.443344907406</v>
       </c>
       <c r="B843">
@@ -28846,7 +28900,7 @@
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A844" s="10">
-        <f>DATEVALUE(MID(F844,5,2) &amp; "-" &amp; LEFT(F844,3) &amp; "-" &amp; MID(F844,8,4)) + TIMEVALUE(MID(F844,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44788.380520833336</v>
       </c>
       <c r="B844">
@@ -28867,7 +28921,7 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A845" s="10">
-        <f>DATEVALUE(MID(F845,5,2) &amp; "-" &amp; LEFT(F845,3) &amp; "-" &amp; MID(F845,8,4)) + TIMEVALUE(MID(F845,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44790.450023148151</v>
       </c>
       <c r="B845">
@@ -28888,7 +28942,7 @@
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A846" s="10">
-        <f>DATEVALUE(MID(F846,5,2) &amp; "-" &amp; LEFT(F846,3) &amp; "-" &amp; MID(F846,8,4)) + TIMEVALUE(MID(F846,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44791.412233796298</v>
       </c>
       <c r="B846">
@@ -28909,7 +28963,7 @@
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A847" s="10">
-        <f>DATEVALUE(MID(F847,5,2) &amp; "-" &amp; LEFT(F847,3) &amp; "-" &amp; MID(F847,8,4)) + TIMEVALUE(MID(F847,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44793.461817129632</v>
       </c>
       <c r="B847">
@@ -28930,7 +28984,7 @@
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A848" s="10">
-        <f>DATEVALUE(MID(F848,5,2) &amp; "-" &amp; LEFT(F848,3) &amp; "-" &amp; MID(F848,8,4)) + TIMEVALUE(MID(F848,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44795.483622685184</v>
       </c>
       <c r="B848">
@@ -28951,7 +29005,7 @@
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A849" s="10">
-        <f>DATEVALUE(MID(F849,5,2) &amp; "-" &amp; LEFT(F849,3) &amp; "-" &amp; MID(F849,8,4)) + TIMEVALUE(MID(F849,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44796.48101851852</v>
       </c>
       <c r="B849">
@@ -28972,7 +29026,7 @@
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A850" s="10">
-        <f>DATEVALUE(MID(F850,5,2) &amp; "-" &amp; LEFT(F850,3) &amp; "-" &amp; MID(F850,8,4)) + TIMEVALUE(MID(F850,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44797.426238425927</v>
       </c>
       <c r="B850">
@@ -28993,7 +29047,7 @@
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A851" s="10">
-        <f>DATEVALUE(MID(F851,5,2) &amp; "-" &amp; LEFT(F851,3) &amp; "-" &amp; MID(F851,8,4)) + TIMEVALUE(MID(F851,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44798.43949074074</v>
       </c>
       <c r="B851">
@@ -29014,7 +29068,7 @@
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A852" s="10">
-        <f>DATEVALUE(MID(F852,5,2) &amp; "-" &amp; LEFT(F852,3) &amp; "-" &amp; MID(F852,8,4)) + TIMEVALUE(MID(F852,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44798.493310185186</v>
       </c>
       <c r="B852">
@@ -29035,7 +29089,7 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A853" s="10">
-        <f>DATEVALUE(MID(F853,5,2) &amp; "-" &amp; LEFT(F853,3) &amp; "-" &amp; MID(F853,8,4)) + TIMEVALUE(MID(F853,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44799.469456018516</v>
       </c>
       <c r="B853">
@@ -29056,7 +29110,7 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A854" s="10">
-        <f>DATEVALUE(MID(F854,5,2) &amp; "-" &amp; LEFT(F854,3) &amp; "-" &amp; MID(F854,8,4)) + TIMEVALUE(MID(F854,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44800.527604166666</v>
       </c>
       <c r="B854">
@@ -29077,7 +29131,7 @@
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A855" s="10">
-        <f>DATEVALUE(MID(F855,5,2) &amp; "-" &amp; LEFT(F855,3) &amp; "-" &amp; MID(F855,8,4)) + TIMEVALUE(MID(F855,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44801.494675925926</v>
       </c>
       <c r="B855">
@@ -29098,7 +29152,7 @@
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A856" s="10">
-        <f>DATEVALUE(MID(F856,5,2) &amp; "-" &amp; LEFT(F856,3) &amp; "-" &amp; MID(F856,8,4)) + TIMEVALUE(MID(F856,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44802.484918981485</v>
       </c>
       <c r="B856">
@@ -29119,7 +29173,7 @@
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A857" s="10">
-        <f>DATEVALUE(MID(F857,5,2) &amp; "-" &amp; LEFT(F857,3) &amp; "-" &amp; MID(F857,8,4)) + TIMEVALUE(MID(F857,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44804.518993055557</v>
       </c>
       <c r="B857">
@@ -29140,7 +29194,7 @@
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A858" s="10">
-        <f>DATEVALUE(MID(F858,5,2) &amp; "-" &amp; LEFT(F858,3) &amp; "-" &amp; MID(F858,8,4)) + TIMEVALUE(MID(F858,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44805.478113425925</v>
       </c>
       <c r="B858">
@@ -29161,7 +29215,7 @@
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A859" s="10">
-        <f>DATEVALUE(MID(F859,5,2) &amp; "-" &amp; LEFT(F859,3) &amp; "-" &amp; MID(F859,8,4)) + TIMEVALUE(MID(F859,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44806.466990740744</v>
       </c>
       <c r="B859">
@@ -29182,7 +29236,7 @@
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A860" s="10">
-        <f>DATEVALUE(MID(F860,5,2) &amp; "-" &amp; LEFT(F860,3) &amp; "-" &amp; MID(F860,8,4)) + TIMEVALUE(MID(F860,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44807.511030092595</v>
       </c>
       <c r="B860">
@@ -29203,7 +29257,7 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A861" s="10">
-        <f>DATEVALUE(MID(F861,5,2) &amp; "-" &amp; LEFT(F861,3) &amp; "-" &amp; MID(F861,8,4)) + TIMEVALUE(MID(F861,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44809.546655092592</v>
       </c>
       <c r="B861">
@@ -29224,7 +29278,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A862" s="10">
-        <f>DATEVALUE(MID(F862,5,2) &amp; "-" &amp; LEFT(F862,3) &amp; "-" &amp; MID(F862,8,4)) + TIMEVALUE(MID(F862,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44811.521469907406</v>
       </c>
       <c r="B862">
@@ -29245,7 +29299,7 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A863" s="10">
-        <f>DATEVALUE(MID(F863,5,2) &amp; "-" &amp; LEFT(F863,3) &amp; "-" &amp; MID(F863,8,4)) + TIMEVALUE(MID(F863,13,11))</f>
+        <f t="shared" si="7"/>
         <v>44812.409120370372</v>
       </c>
       <c r="B863">
@@ -29266,7 +29320,7 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A864" s="10">
-        <f>DATEVALUE(MID(F864,5,2) &amp; "-" &amp; LEFT(F864,3) &amp; "-" &amp; MID(F864,8,4)) + TIMEVALUE(MID(F864,13,11))</f>
+        <f t="shared" ref="A864:A927" si="8">DATEVALUE(MID(F864,5,2) &amp; "-" &amp; LEFT(F864,3) &amp; "-" &amp; MID(F864,8,4)) + TIMEVALUE(MID(F864,13,11))</f>
         <v>44813.430081018516</v>
       </c>
       <c r="B864">
@@ -29287,7 +29341,7 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A865" s="10">
-        <f>DATEVALUE(MID(F865,5,2) &amp; "-" &amp; LEFT(F865,3) &amp; "-" &amp; MID(F865,8,4)) + TIMEVALUE(MID(F865,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44814.410138888888</v>
       </c>
       <c r="B865">
@@ -29308,7 +29362,7 @@
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A866" s="10">
-        <f>DATEVALUE(MID(F866,5,2) &amp; "-" &amp; LEFT(F866,3) &amp; "-" &amp; MID(F866,8,4)) + TIMEVALUE(MID(F866,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44815.52615740741</v>
       </c>
       <c r="B866">
@@ -29329,7 +29383,7 @@
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A867" s="10">
-        <f>DATEVALUE(MID(F867,5,2) &amp; "-" &amp; LEFT(F867,3) &amp; "-" &amp; MID(F867,8,4)) + TIMEVALUE(MID(F867,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44816.455717592595</v>
       </c>
       <c r="B867">
@@ -29350,7 +29404,7 @@
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A868" s="10">
-        <f>DATEVALUE(MID(F868,5,2) &amp; "-" &amp; LEFT(F868,3) &amp; "-" &amp; MID(F868,8,4)) + TIMEVALUE(MID(F868,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44817.435370370367</v>
       </c>
       <c r="B868">
@@ -29371,7 +29425,7 @@
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A869" s="10">
-        <f>DATEVALUE(MID(F869,5,2) &amp; "-" &amp; LEFT(F869,3) &amp; "-" &amp; MID(F869,8,4)) + TIMEVALUE(MID(F869,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44818.461493055554</v>
       </c>
       <c r="B869">
@@ -29392,7 +29446,7 @@
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A870" s="10">
-        <f>DATEVALUE(MID(F870,5,2) &amp; "-" &amp; LEFT(F870,3) &amp; "-" &amp; MID(F870,8,4)) + TIMEVALUE(MID(F870,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44819.507557870369</v>
       </c>
       <c r="B870">
@@ -29413,7 +29467,7 @@
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A871" s="10">
-        <f>DATEVALUE(MID(F871,5,2) &amp; "-" &amp; LEFT(F871,3) &amp; "-" &amp; MID(F871,8,4)) + TIMEVALUE(MID(F871,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44822.441631944443</v>
       </c>
       <c r="B871">
@@ -29434,7 +29488,7 @@
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A872" s="10">
-        <f>DATEVALUE(MID(F872,5,2) &amp; "-" &amp; LEFT(F872,3) &amp; "-" &amp; MID(F872,8,4)) + TIMEVALUE(MID(F872,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44823.48201388889</v>
       </c>
       <c r="B872">
@@ -29455,7 +29509,7 @@
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A873" s="10">
-        <f>DATEVALUE(MID(F873,5,2) &amp; "-" &amp; LEFT(F873,3) &amp; "-" &amp; MID(F873,8,4)) + TIMEVALUE(MID(F873,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44824.460798611108</v>
       </c>
       <c r="B873">
@@ -29476,7 +29530,7 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A874" s="10">
-        <f>DATEVALUE(MID(F874,5,2) &amp; "-" &amp; LEFT(F874,3) &amp; "-" &amp; MID(F874,8,4)) + TIMEVALUE(MID(F874,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44825.476990740739</v>
       </c>
       <c r="B874">
@@ -29497,7 +29551,7 @@
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A875" s="10">
-        <f>DATEVALUE(MID(F875,5,2) &amp; "-" &amp; LEFT(F875,3) &amp; "-" &amp; MID(F875,8,4)) + TIMEVALUE(MID(F875,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44826.469733796293</v>
       </c>
       <c r="B875">
@@ -29518,7 +29572,7 @@
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A876" s="10">
-        <f>DATEVALUE(MID(F876,5,2) &amp; "-" &amp; LEFT(F876,3) &amp; "-" &amp; MID(F876,8,4)) + TIMEVALUE(MID(F876,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44827.441134259258</v>
       </c>
       <c r="B876">
@@ -29539,7 +29593,7 @@
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A877" s="10">
-        <f>DATEVALUE(MID(F877,5,2) &amp; "-" &amp; LEFT(F877,3) &amp; "-" &amp; MID(F877,8,4)) + TIMEVALUE(MID(F877,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44828.423483796294</v>
       </c>
       <c r="B877">
@@ -29560,7 +29614,7 @@
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A878" s="10">
-        <f>DATEVALUE(MID(F878,5,2) &amp; "-" &amp; LEFT(F878,3) &amp; "-" &amp; MID(F878,8,4)) + TIMEVALUE(MID(F878,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44832.466516203705</v>
       </c>
       <c r="B878">
@@ -29581,7 +29635,7 @@
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A879" s="10">
-        <f>DATEVALUE(MID(F879,5,2) &amp; "-" &amp; LEFT(F879,3) &amp; "-" &amp; MID(F879,8,4)) + TIMEVALUE(MID(F879,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44833.508935185186</v>
       </c>
       <c r="B879">
@@ -29602,7 +29656,7 @@
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A880" s="10">
-        <f>DATEVALUE(MID(F880,5,2) &amp; "-" &amp; LEFT(F880,3) &amp; "-" &amp; MID(F880,8,4)) + TIMEVALUE(MID(F880,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44834.473321759258</v>
       </c>
       <c r="B880">
@@ -29623,7 +29677,7 @@
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A881" s="10">
-        <f>DATEVALUE(MID(F881,5,2) &amp; "-" &amp; LEFT(F881,3) &amp; "-" &amp; MID(F881,8,4)) + TIMEVALUE(MID(F881,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44835.458807870367</v>
       </c>
       <c r="B881">
@@ -29644,7 +29698,7 @@
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A882" s="10">
-        <f>DATEVALUE(MID(F882,5,2) &amp; "-" &amp; LEFT(F882,3) &amp; "-" &amp; MID(F882,8,4)) + TIMEVALUE(MID(F882,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44838.454583333332</v>
       </c>
       <c r="B882">
@@ -29665,7 +29719,7 @@
     </row>
     <row r="883" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A883" s="10">
-        <f>DATEVALUE(MID(F883,5,2) &amp; "-" &amp; LEFT(F883,3) &amp; "-" &amp; MID(F883,8,4)) + TIMEVALUE(MID(F883,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44839.513101851851</v>
       </c>
       <c r="B883">
@@ -29686,7 +29740,7 @@
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A884" s="10">
-        <f>DATEVALUE(MID(F884,5,2) &amp; "-" &amp; LEFT(F884,3) &amp; "-" &amp; MID(F884,8,4)) + TIMEVALUE(MID(F884,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44840.498333333337</v>
       </c>
       <c r="B884">
@@ -29707,7 +29761,7 @@
     </row>
     <row r="885" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A885" s="10">
-        <f>DATEVALUE(MID(F885,5,2) &amp; "-" &amp; LEFT(F885,3) &amp; "-" &amp; MID(F885,8,4)) + TIMEVALUE(MID(F885,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44841.499374999999</v>
       </c>
       <c r="B885">
@@ -29728,7 +29782,7 @@
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A886" s="10">
-        <f>DATEVALUE(MID(F886,5,2) &amp; "-" &amp; LEFT(F886,3) &amp; "-" &amp; MID(F886,8,4)) + TIMEVALUE(MID(F886,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44842.483136574076</v>
       </c>
       <c r="B886">
@@ -29749,7 +29803,7 @@
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A887" s="10">
-        <f>DATEVALUE(MID(F887,5,2) &amp; "-" &amp; LEFT(F887,3) &amp; "-" &amp; MID(F887,8,4)) + TIMEVALUE(MID(F887,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44843.50708333333</v>
       </c>
       <c r="B887">
@@ -29770,7 +29824,7 @@
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A888" s="10">
-        <f>DATEVALUE(MID(F888,5,2) &amp; "-" &amp; LEFT(F888,3) &amp; "-" &amp; MID(F888,8,4)) + TIMEVALUE(MID(F888,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44844.465578703705</v>
       </c>
       <c r="B888">
@@ -29791,7 +29845,7 @@
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A889" s="10">
-        <f>DATEVALUE(MID(F889,5,2) &amp; "-" &amp; LEFT(F889,3) &amp; "-" &amp; MID(F889,8,4)) + TIMEVALUE(MID(F889,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44845.499062499999</v>
       </c>
       <c r="B889">
@@ -29812,7 +29866,7 @@
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A890" s="10">
-        <f>DATEVALUE(MID(F890,5,2) &amp; "-" &amp; LEFT(F890,3) &amp; "-" &amp; MID(F890,8,4)) + TIMEVALUE(MID(F890,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44846.437268518515</v>
       </c>
       <c r="B890">
@@ -29833,7 +29887,7 @@
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A891" s="10">
-        <f>DATEVALUE(MID(F891,5,2) &amp; "-" &amp; LEFT(F891,3) &amp; "-" &amp; MID(F891,8,4)) + TIMEVALUE(MID(F891,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44847.446608796294</v>
       </c>
       <c r="B891">
@@ -29854,7 +29908,7 @@
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A892" s="10">
-        <f>DATEVALUE(MID(F892,5,2) &amp; "-" &amp; LEFT(F892,3) &amp; "-" &amp; MID(F892,8,4)) + TIMEVALUE(MID(F892,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44848.482094907406</v>
       </c>
       <c r="B892">
@@ -29875,7 +29929,7 @@
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A893" s="10">
-        <f>DATEVALUE(MID(F893,5,2) &amp; "-" &amp; LEFT(F893,3) &amp; "-" &amp; MID(F893,8,4)) + TIMEVALUE(MID(F893,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44849.523912037039</v>
       </c>
       <c r="B893">
@@ -29896,7 +29950,7 @@
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A894" s="10">
-        <f>DATEVALUE(MID(F894,5,2) &amp; "-" &amp; LEFT(F894,3) &amp; "-" &amp; MID(F894,8,4)) + TIMEVALUE(MID(F894,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44850.483668981484</v>
       </c>
       <c r="B894">
@@ -29917,7 +29971,7 @@
     </row>
     <row r="895" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A895" s="10">
-        <f>DATEVALUE(MID(F895,5,2) &amp; "-" &amp; LEFT(F895,3) &amp; "-" &amp; MID(F895,8,4)) + TIMEVALUE(MID(F895,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44851.466967592591</v>
       </c>
       <c r="B895">
@@ -29938,7 +29992,7 @@
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A896" s="10">
-        <f>DATEVALUE(MID(F896,5,2) &amp; "-" &amp; LEFT(F896,3) &amp; "-" &amp; MID(F896,8,4)) + TIMEVALUE(MID(F896,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44852.465671296297</v>
       </c>
       <c r="B896">
@@ -29959,7 +30013,7 @@
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A897" s="10">
-        <f>DATEVALUE(MID(F897,5,2) &amp; "-" &amp; LEFT(F897,3) &amp; "-" &amp; MID(F897,8,4)) + TIMEVALUE(MID(F897,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44853.430138888885</v>
       </c>
       <c r="B897">
@@ -29980,7 +30034,7 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A898" s="10">
-        <f>DATEVALUE(MID(F898,5,2) &amp; "-" &amp; LEFT(F898,3) &amp; "-" &amp; MID(F898,8,4)) + TIMEVALUE(MID(F898,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44854.436435185184</v>
       </c>
       <c r="B898">
@@ -30001,7 +30055,7 @@
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A899" s="10">
-        <f>DATEVALUE(MID(F899,5,2) &amp; "-" &amp; LEFT(F899,3) &amp; "-" &amp; MID(F899,8,4)) + TIMEVALUE(MID(F899,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44855.398969907408</v>
       </c>
       <c r="B899">
@@ -30022,7 +30076,7 @@
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A900" s="10">
-        <f>DATEVALUE(MID(F900,5,2) &amp; "-" &amp; LEFT(F900,3) &amp; "-" &amp; MID(F900,8,4)) + TIMEVALUE(MID(F900,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44866.41746527778</v>
       </c>
       <c r="B900">
@@ -30043,7 +30097,7 @@
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A901" s="10">
-        <f>DATEVALUE(MID(F901,5,2) &amp; "-" &amp; LEFT(F901,3) &amp; "-" &amp; MID(F901,8,4)) + TIMEVALUE(MID(F901,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44868.43787037037</v>
       </c>
       <c r="B901">
@@ -30064,7 +30118,7 @@
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A902" s="10">
-        <f>DATEVALUE(MID(F902,5,2) &amp; "-" &amp; LEFT(F902,3) &amp; "-" &amp; MID(F902,8,4)) + TIMEVALUE(MID(F902,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44869.440092592595</v>
       </c>
       <c r="B902">
@@ -30085,7 +30139,7 @@
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A903" s="10">
-        <f>DATEVALUE(MID(F903,5,2) &amp; "-" &amp; LEFT(F903,3) &amp; "-" &amp; MID(F903,8,4)) + TIMEVALUE(MID(F903,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44870.520798611113</v>
       </c>
       <c r="B903">
@@ -30106,7 +30160,7 @@
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A904" s="10">
-        <f>DATEVALUE(MID(F904,5,2) &amp; "-" &amp; LEFT(F904,3) &amp; "-" &amp; MID(F904,8,4)) + TIMEVALUE(MID(F904,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44871.495462962965</v>
       </c>
       <c r="B904">
@@ -30127,7 +30181,7 @@
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A905" s="10">
-        <f>DATEVALUE(MID(F905,5,2) &amp; "-" &amp; LEFT(F905,3) &amp; "-" &amp; MID(F905,8,4)) + TIMEVALUE(MID(F905,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44872.46979166667</v>
       </c>
       <c r="B905">
@@ -30148,7 +30202,7 @@
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A906" s="10">
-        <f>DATEVALUE(MID(F906,5,2) &amp; "-" &amp; LEFT(F906,3) &amp; "-" &amp; MID(F906,8,4)) + TIMEVALUE(MID(F906,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44875.469039351854</v>
       </c>
       <c r="B906">
@@ -30169,7 +30223,7 @@
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A907" s="10">
-        <f>DATEVALUE(MID(F907,5,2) &amp; "-" &amp; LEFT(F907,3) &amp; "-" &amp; MID(F907,8,4)) + TIMEVALUE(MID(F907,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44878.542453703703</v>
       </c>
       <c r="B907">
@@ -30190,7 +30244,7 @@
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A908" s="10">
-        <f>DATEVALUE(MID(F908,5,2) &amp; "-" &amp; LEFT(F908,3) &amp; "-" &amp; MID(F908,8,4)) + TIMEVALUE(MID(F908,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44879.50640046296</v>
       </c>
       <c r="B908">
@@ -30211,7 +30265,7 @@
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A909" s="10">
-        <f>DATEVALUE(MID(F909,5,2) &amp; "-" &amp; LEFT(F909,3) &amp; "-" &amp; MID(F909,8,4)) + TIMEVALUE(MID(F909,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44880.523796296293</v>
       </c>
       <c r="B909">
@@ -30232,7 +30286,7 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A910" s="10">
-        <f>DATEVALUE(MID(F910,5,2) &amp; "-" &amp; LEFT(F910,3) &amp; "-" &amp; MID(F910,8,4)) + TIMEVALUE(MID(F910,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44881.513969907406</v>
       </c>
       <c r="B910">
@@ -30253,7 +30307,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A911" s="10">
-        <f>DATEVALUE(MID(F911,5,2) &amp; "-" &amp; LEFT(F911,3) &amp; "-" &amp; MID(F911,8,4)) + TIMEVALUE(MID(F911,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44882.523634259262</v>
       </c>
       <c r="B911">
@@ -30274,7 +30328,7 @@
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A912" s="10">
-        <f>DATEVALUE(MID(F912,5,2) &amp; "-" &amp; LEFT(F912,3) &amp; "-" &amp; MID(F912,8,4)) + TIMEVALUE(MID(F912,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44883.514849537038</v>
       </c>
       <c r="B912">
@@ -30295,7 +30349,7 @@
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A913" s="10">
-        <f>DATEVALUE(MID(F913,5,2) &amp; "-" &amp; LEFT(F913,3) &amp; "-" &amp; MID(F913,8,4)) + TIMEVALUE(MID(F913,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44884.566724537035</v>
       </c>
       <c r="B913">
@@ -30316,7 +30370,7 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A914" s="10">
-        <f>DATEVALUE(MID(F914,5,2) &amp; "-" &amp; LEFT(F914,3) &amp; "-" &amp; MID(F914,8,4)) + TIMEVALUE(MID(F914,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44885.552546296298</v>
       </c>
       <c r="B914">
@@ -30337,7 +30391,7 @@
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A915" s="10">
-        <f>DATEVALUE(MID(F915,5,2) &amp; "-" &amp; LEFT(F915,3) &amp; "-" &amp; MID(F915,8,4)) + TIMEVALUE(MID(F915,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44886.484490740739</v>
       </c>
       <c r="B915">
@@ -30358,7 +30412,7 @@
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A916" s="10">
-        <f>DATEVALUE(MID(F916,5,2) &amp; "-" &amp; LEFT(F916,3) &amp; "-" &amp; MID(F916,8,4)) + TIMEVALUE(MID(F916,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44887.509155092594</v>
       </c>
       <c r="B916">
@@ -30379,7 +30433,7 @@
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A917" s="10">
-        <f>DATEVALUE(MID(F917,5,2) &amp; "-" &amp; LEFT(F917,3) &amp; "-" &amp; MID(F917,8,4)) + TIMEVALUE(MID(F917,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44888.516192129631</v>
       </c>
       <c r="B917">
@@ -30400,7 +30454,7 @@
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A918" s="10">
-        <f>DATEVALUE(MID(F918,5,2) &amp; "-" &amp; LEFT(F918,3) &amp; "-" &amp; MID(F918,8,4)) + TIMEVALUE(MID(F918,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44889.483206018522</v>
       </c>
       <c r="B918">
@@ -30421,7 +30475,7 @@
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A919" s="10">
-        <f>DATEVALUE(MID(F919,5,2) &amp; "-" &amp; LEFT(F919,3) &amp; "-" &amp; MID(F919,8,4)) + TIMEVALUE(MID(F919,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44890.51730324074</v>
       </c>
       <c r="B919">
@@ -30442,7 +30496,7 @@
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A920" s="10">
-        <f>DATEVALUE(MID(F920,5,2) &amp; "-" &amp; LEFT(F920,3) &amp; "-" &amp; MID(F920,8,4)) + TIMEVALUE(MID(F920,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44891.500914351855</v>
       </c>
       <c r="B920">
@@ -30463,7 +30517,7 @@
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A921" s="10">
-        <f>DATEVALUE(MID(F921,5,2) &amp; "-" &amp; LEFT(F921,3) &amp; "-" &amp; MID(F921,8,4)) + TIMEVALUE(MID(F921,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44892.513668981483</v>
       </c>
       <c r="B921">
@@ -30484,7 +30538,7 @@
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A922" s="10">
-        <f>DATEVALUE(MID(F922,5,2) &amp; "-" &amp; LEFT(F922,3) &amp; "-" &amp; MID(F922,8,4)) + TIMEVALUE(MID(F922,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44894.498425925929</v>
       </c>
       <c r="B922">
@@ -30505,7 +30559,7 @@
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A923" s="10">
-        <f>DATEVALUE(MID(F923,5,2) &amp; "-" &amp; LEFT(F923,3) &amp; "-" &amp; MID(F923,8,4)) + TIMEVALUE(MID(F923,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44896.492418981485</v>
       </c>
       <c r="B923">
@@ -30526,7 +30580,7 @@
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A924" s="10">
-        <f>DATEVALUE(MID(F924,5,2) &amp; "-" &amp; LEFT(F924,3) &amp; "-" &amp; MID(F924,8,4)) + TIMEVALUE(MID(F924,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44897.493784722225</v>
       </c>
       <c r="B924">
@@ -30547,7 +30601,7 @@
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A925" s="10">
-        <f>DATEVALUE(MID(F925,5,2) &amp; "-" &amp; LEFT(F925,3) &amp; "-" &amp; MID(F925,8,4)) + TIMEVALUE(MID(F925,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44901.512488425928</v>
       </c>
       <c r="B925">
@@ -30568,7 +30622,7 @@
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A926" s="10">
-        <f>DATEVALUE(MID(F926,5,2) &amp; "-" &amp; LEFT(F926,3) &amp; "-" &amp; MID(F926,8,4)) + TIMEVALUE(MID(F926,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44902.487037037034</v>
       </c>
       <c r="B926">
@@ -30589,7 +30643,7 @@
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A927" s="10">
-        <f>DATEVALUE(MID(F927,5,2) &amp; "-" &amp; LEFT(F927,3) &amp; "-" &amp; MID(F927,8,4)) + TIMEVALUE(MID(F927,13,11))</f>
+        <f t="shared" si="8"/>
         <v>44903.542800925927</v>
       </c>
       <c r="B927">
@@ -30610,7 +30664,7 @@
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A928" s="10">
-        <f>DATEVALUE(MID(F928,5,2) &amp; "-" &amp; LEFT(F928,3) &amp; "-" &amp; MID(F928,8,4)) + TIMEVALUE(MID(F928,13,11))</f>
+        <f t="shared" ref="A928:A991" si="9">DATEVALUE(MID(F928,5,2) &amp; "-" &amp; LEFT(F928,3) &amp; "-" &amp; MID(F928,8,4)) + TIMEVALUE(MID(F928,13,11))</f>
         <v>44908.522233796299</v>
       </c>
       <c r="B928">
@@ -30631,7 +30685,7 @@
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A929" s="10">
-        <f>DATEVALUE(MID(F929,5,2) &amp; "-" &amp; LEFT(F929,3) &amp; "-" &amp; MID(F929,8,4)) + TIMEVALUE(MID(F929,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44927.549305555556</v>
       </c>
       <c r="B929">
@@ -30652,7 +30706,7 @@
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A930" s="10">
-        <f>DATEVALUE(MID(F930,5,2) &amp; "-" &amp; LEFT(F930,3) &amp; "-" &amp; MID(F930,8,4)) + TIMEVALUE(MID(F930,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44928.50980324074</v>
       </c>
       <c r="B930">
@@ -30673,7 +30727,7 @@
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A931" s="10">
-        <f>DATEVALUE(MID(F931,5,2) &amp; "-" &amp; LEFT(F931,3) &amp; "-" &amp; MID(F931,8,4)) + TIMEVALUE(MID(F931,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44929.509594907409</v>
       </c>
       <c r="B931">
@@ -30694,7 +30748,7 @@
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A932" s="10">
-        <f>DATEVALUE(MID(F932,5,2) &amp; "-" &amp; LEFT(F932,3) &amp; "-" &amp; MID(F932,8,4)) + TIMEVALUE(MID(F932,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44930.536319444444</v>
       </c>
       <c r="B932">
@@ -30715,7 +30769,7 @@
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A933" s="10">
-        <f>DATEVALUE(MID(F933,5,2) &amp; "-" &amp; LEFT(F933,3) &amp; "-" &amp; MID(F933,8,4)) + TIMEVALUE(MID(F933,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44931.492812500001</v>
       </c>
       <c r="B933">
@@ -30736,7 +30790,7 @@
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A934" s="10">
-        <f>DATEVALUE(MID(F934,5,2) &amp; "-" &amp; LEFT(F934,3) &amp; "-" &amp; MID(F934,8,4)) + TIMEVALUE(MID(F934,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44932.550243055557</v>
       </c>
       <c r="B934">
@@ -30757,7 +30811,7 @@
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A935" s="10">
-        <f>DATEVALUE(MID(F935,5,2) &amp; "-" &amp; LEFT(F935,3) &amp; "-" &amp; MID(F935,8,4)) + TIMEVALUE(MID(F935,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44933.547789351855</v>
       </c>
       <c r="B935">
@@ -30778,7 +30832,7 @@
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A936" s="10">
-        <f>DATEVALUE(MID(F936,5,2) &amp; "-" &amp; LEFT(F936,3) &amp; "-" &amp; MID(F936,8,4)) + TIMEVALUE(MID(F936,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44934.577662037038</v>
       </c>
       <c r="B936">
@@ -30799,7 +30853,7 @@
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A937" s="10">
-        <f>DATEVALUE(MID(F937,5,2) &amp; "-" &amp; LEFT(F937,3) &amp; "-" &amp; MID(F937,8,4)) + TIMEVALUE(MID(F937,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44935.540405092594</v>
       </c>
       <c r="B937">
@@ -30820,7 +30874,7 @@
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A938" s="10">
-        <f>DATEVALUE(MID(F938,5,2) &amp; "-" &amp; LEFT(F938,3) &amp; "-" &amp; MID(F938,8,4)) + TIMEVALUE(MID(F938,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44936.557395833333</v>
       </c>
       <c r="B938">
@@ -30841,7 +30895,7 @@
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A939" s="10">
-        <f>DATEVALUE(MID(F939,5,2) &amp; "-" &amp; LEFT(F939,3) &amp; "-" &amp; MID(F939,8,4)) + TIMEVALUE(MID(F939,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44937.527372685188</v>
       </c>
       <c r="B939">
@@ -30862,7 +30916,7 @@
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A940" s="10">
-        <f>DATEVALUE(MID(F940,5,2) &amp; "-" &amp; LEFT(F940,3) &amp; "-" &amp; MID(F940,8,4)) + TIMEVALUE(MID(F940,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44938.520868055559</v>
       </c>
       <c r="B940">
@@ -30883,7 +30937,7 @@
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A941" s="10">
-        <f>DATEVALUE(MID(F941,5,2) &amp; "-" &amp; LEFT(F941,3) &amp; "-" &amp; MID(F941,8,4)) + TIMEVALUE(MID(F941,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44939.528078703705</v>
       </c>
       <c r="B941">
@@ -30904,7 +30958,7 @@
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A942" s="10">
-        <f>DATEVALUE(MID(F942,5,2) &amp; "-" &amp; LEFT(F942,3) &amp; "-" &amp; MID(F942,8,4)) + TIMEVALUE(MID(F942,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44940.533865740741</v>
       </c>
       <c r="B942">
@@ -30925,7 +30979,7 @@
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A943" s="10">
-        <f>DATEVALUE(MID(F943,5,2) &amp; "-" &amp; LEFT(F943,3) &amp; "-" &amp; MID(F943,8,4)) + TIMEVALUE(MID(F943,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44941.543287037035</v>
       </c>
       <c r="B943">
@@ -30946,7 +31000,7 @@
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A944" s="10">
-        <f>DATEVALUE(MID(F944,5,2) &amp; "-" &amp; LEFT(F944,3) &amp; "-" &amp; MID(F944,8,4)) + TIMEVALUE(MID(F944,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44942.532453703701</v>
       </c>
       <c r="B944">
@@ -30967,7 +31021,7 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A945" s="10">
-        <f>DATEVALUE(MID(F945,5,2) &amp; "-" &amp; LEFT(F945,3) &amp; "-" &amp; MID(F945,8,4)) + TIMEVALUE(MID(F945,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44943.469444444447</v>
       </c>
       <c r="B945">
@@ -30988,7 +31042,7 @@
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A946" s="10">
-        <f>DATEVALUE(MID(F946,5,2) &amp; "-" &amp; LEFT(F946,3) &amp; "-" &amp; MID(F946,8,4)) + TIMEVALUE(MID(F946,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44944.550729166665</v>
       </c>
       <c r="B946">
@@ -31009,7 +31063,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A947" s="10">
-        <f>DATEVALUE(MID(F947,5,2) &amp; "-" &amp; LEFT(F947,3) &amp; "-" &amp; MID(F947,8,4)) + TIMEVALUE(MID(F947,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44945.504282407404</v>
       </c>
       <c r="B947">
@@ -31030,7 +31084,7 @@
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A948" s="10">
-        <f>DATEVALUE(MID(F948,5,2) &amp; "-" &amp; LEFT(F948,3) &amp; "-" &amp; MID(F948,8,4)) + TIMEVALUE(MID(F948,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44946.481759259259</v>
       </c>
       <c r="B948">
@@ -31051,7 +31105,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A949" s="10">
-        <f>DATEVALUE(MID(F949,5,2) &amp; "-" &amp; LEFT(F949,3) &amp; "-" &amp; MID(F949,8,4)) + TIMEVALUE(MID(F949,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44947.523321759261</v>
       </c>
       <c r="B949">
@@ -31072,7 +31126,7 @@
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A950" s="10">
-        <f>DATEVALUE(MID(F950,5,2) &amp; "-" &amp; LEFT(F950,3) &amp; "-" &amp; MID(F950,8,4)) + TIMEVALUE(MID(F950,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44948.544918981483</v>
       </c>
       <c r="B950">
@@ -31093,7 +31147,7 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A951" s="10">
-        <f>DATEVALUE(MID(F951,5,2) &amp; "-" &amp; LEFT(F951,3) &amp; "-" &amp; MID(F951,8,4)) + TIMEVALUE(MID(F951,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44949.517523148148</v>
       </c>
       <c r="B951">
@@ -31114,7 +31168,7 @@
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A952" s="10">
-        <f>DATEVALUE(MID(F952,5,2) &amp; "-" &amp; LEFT(F952,3) &amp; "-" &amp; MID(F952,8,4)) + TIMEVALUE(MID(F952,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44950.523935185185</v>
       </c>
       <c r="B952">
@@ -31135,7 +31189,7 @@
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A953" s="10">
-        <f>DATEVALUE(MID(F953,5,2) &amp; "-" &amp; LEFT(F953,3) &amp; "-" &amp; MID(F953,8,4)) + TIMEVALUE(MID(F953,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44951.493506944447</v>
       </c>
       <c r="B953">
@@ -31156,7 +31210,7 @@
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A954" s="10">
-        <f>DATEVALUE(MID(F954,5,2) &amp; "-" &amp; LEFT(F954,3) &amp; "-" &amp; MID(F954,8,4)) + TIMEVALUE(MID(F954,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44952.515393518515</v>
       </c>
       <c r="B954">
@@ -31177,7 +31231,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A955" s="10">
-        <f>DATEVALUE(MID(F955,5,2) &amp; "-" &amp; LEFT(F955,3) &amp; "-" &amp; MID(F955,8,4)) + TIMEVALUE(MID(F955,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44953.512407407405</v>
       </c>
       <c r="B955">
@@ -31198,7 +31252,7 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A956" s="10">
-        <f>DATEVALUE(MID(F956,5,2) &amp; "-" &amp; LEFT(F956,3) &amp; "-" &amp; MID(F956,8,4)) + TIMEVALUE(MID(F956,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44954.546875</v>
       </c>
       <c r="B956">
@@ -31219,7 +31273,7 @@
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A957" s="10">
-        <f>DATEVALUE(MID(F957,5,2) &amp; "-" &amp; LEFT(F957,3) &amp; "-" &amp; MID(F957,8,4)) + TIMEVALUE(MID(F957,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44955.547222222223</v>
       </c>
       <c r="B957">
@@ -31240,7 +31294,7 @@
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A958" s="10">
-        <f>DATEVALUE(MID(F958,5,2) &amp; "-" &amp; LEFT(F958,3) &amp; "-" &amp; MID(F958,8,4)) + TIMEVALUE(MID(F958,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44956.510393518518</v>
       </c>
       <c r="B958">
@@ -31261,7 +31315,7 @@
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A959" s="10">
-        <f>DATEVALUE(MID(F959,5,2) &amp; "-" &amp; LEFT(F959,3) &amp; "-" &amp; MID(F959,8,4)) + TIMEVALUE(MID(F959,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44957.520370370374</v>
       </c>
       <c r="B959">
@@ -31282,7 +31336,7 @@
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A960" s="10">
-        <f>DATEVALUE(MID(F960,5,2) &amp; "-" &amp; LEFT(F960,3) &amp; "-" &amp; MID(F960,8,4)) + TIMEVALUE(MID(F960,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44958.534560185188</v>
       </c>
       <c r="B960">
@@ -31303,7 +31357,7 @@
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A961" s="10">
-        <f>DATEVALUE(MID(F961,5,2) &amp; "-" &amp; LEFT(F961,3) &amp; "-" &amp; MID(F961,8,4)) + TIMEVALUE(MID(F961,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44959.518692129626</v>
       </c>
       <c r="B961">
@@ -31324,7 +31378,7 @@
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A962" s="10">
-        <f>DATEVALUE(MID(F962,5,2) &amp; "-" &amp; LEFT(F962,3) &amp; "-" &amp; MID(F962,8,4)) + TIMEVALUE(MID(F962,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44960.555034722223</v>
       </c>
       <c r="B962">
@@ -31345,7 +31399,7 @@
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A963" s="10">
-        <f>DATEVALUE(MID(F963,5,2) &amp; "-" &amp; LEFT(F963,3) &amp; "-" &amp; MID(F963,8,4)) + TIMEVALUE(MID(F963,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44961.503796296296</v>
       </c>
       <c r="B963">
@@ -31366,7 +31420,7 @@
     </row>
     <row r="964" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A964" s="10">
-        <f>DATEVALUE(MID(F964,5,2) &amp; "-" &amp; LEFT(F964,3) &amp; "-" &amp; MID(F964,8,4)) + TIMEVALUE(MID(F964,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44962.528715277775</v>
       </c>
       <c r="B964">
@@ -31387,7 +31441,7 @@
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A965" s="10">
-        <f>DATEVALUE(MID(F965,5,2) &amp; "-" &amp; LEFT(F965,3) &amp; "-" &amp; MID(F965,8,4)) + TIMEVALUE(MID(F965,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44963.527361111112</v>
       </c>
       <c r="B965">
@@ -31408,7 +31462,7 @@
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A966" s="10">
-        <f>DATEVALUE(MID(F966,5,2) &amp; "-" &amp; LEFT(F966,3) &amp; "-" &amp; MID(F966,8,4)) + TIMEVALUE(MID(F966,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44964.514594907407</v>
       </c>
       <c r="B966">
@@ -31429,7 +31483,7 @@
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A967" s="10">
-        <f>DATEVALUE(MID(F967,5,2) &amp; "-" &amp; LEFT(F967,3) &amp; "-" &amp; MID(F967,8,4)) + TIMEVALUE(MID(F967,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44965.488576388889</v>
       </c>
       <c r="B967">
@@ -31450,7 +31504,7 @@
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A968" s="10">
-        <f>DATEVALUE(MID(F968,5,2) &amp; "-" &amp; LEFT(F968,3) &amp; "-" &amp; MID(F968,8,4)) + TIMEVALUE(MID(F968,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44966.52847222222</v>
       </c>
       <c r="B968">
@@ -31471,7 +31525,7 @@
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A969" s="10">
-        <f>DATEVALUE(MID(F969,5,2) &amp; "-" &amp; LEFT(F969,3) &amp; "-" &amp; MID(F969,8,4)) + TIMEVALUE(MID(F969,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44967.491180555553</v>
       </c>
       <c r="B969">
@@ -31492,7 +31546,7 @@
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A970" s="10">
-        <f>DATEVALUE(MID(F970,5,2) &amp; "-" &amp; LEFT(F970,3) &amp; "-" &amp; MID(F970,8,4)) + TIMEVALUE(MID(F970,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44968.502962962964</v>
       </c>
       <c r="B970">
@@ -31513,7 +31567,7 @@
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A971" s="10">
-        <f>DATEVALUE(MID(F971,5,2) &amp; "-" &amp; LEFT(F971,3) &amp; "-" &amp; MID(F971,8,4)) + TIMEVALUE(MID(F971,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44969.492256944446</v>
       </c>
       <c r="B971">
@@ -31534,7 +31588,7 @@
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A972" s="10">
-        <f>DATEVALUE(MID(F972,5,2) &amp; "-" &amp; LEFT(F972,3) &amp; "-" &amp; MID(F972,8,4)) + TIMEVALUE(MID(F972,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44970.514675925922</v>
       </c>
       <c r="B972">
@@ -31555,7 +31609,7 @@
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A973" s="10">
-        <f>DATEVALUE(MID(F973,5,2) &amp; "-" &amp; LEFT(F973,3) &amp; "-" &amp; MID(F973,8,4)) + TIMEVALUE(MID(F973,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44971.379155092596</v>
       </c>
       <c r="B973">
@@ -31576,7 +31630,7 @@
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A974" s="10">
-        <f>DATEVALUE(MID(F974,5,2) &amp; "-" &amp; LEFT(F974,3) &amp; "-" &amp; MID(F974,8,4)) + TIMEVALUE(MID(F974,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44973.476168981484</v>
       </c>
       <c r="B974">
@@ -31597,7 +31651,7 @@
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A975" s="10">
-        <f>DATEVALUE(MID(F975,5,2) &amp; "-" &amp; LEFT(F975,3) &amp; "-" &amp; MID(F975,8,4)) + TIMEVALUE(MID(F975,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44973.497037037036</v>
       </c>
       <c r="B975">
@@ -31618,7 +31672,7 @@
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A976" s="10">
-        <f>DATEVALUE(MID(F976,5,2) &amp; "-" &amp; LEFT(F976,3) &amp; "-" &amp; MID(F976,8,4)) + TIMEVALUE(MID(F976,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44974.480833333335</v>
       </c>
       <c r="B976">
@@ -31639,7 +31693,7 @@
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A977" s="10">
-        <f>DATEVALUE(MID(F977,5,2) &amp; "-" &amp; LEFT(F977,3) &amp; "-" &amp; MID(F977,8,4)) + TIMEVALUE(MID(F977,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44977.497511574074</v>
       </c>
       <c r="B977">
@@ -31660,7 +31714,7 @@
     </row>
     <row r="978" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A978" s="10">
-        <f>DATEVALUE(MID(F978,5,2) &amp; "-" &amp; LEFT(F978,3) &amp; "-" &amp; MID(F978,8,4)) + TIMEVALUE(MID(F978,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44978.51630787037</v>
       </c>
       <c r="B978">
@@ -31681,7 +31735,7 @@
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A979" s="10">
-        <f>DATEVALUE(MID(F979,5,2) &amp; "-" &amp; LEFT(F979,3) &amp; "-" &amp; MID(F979,8,4)) + TIMEVALUE(MID(F979,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44979.495115740741</v>
       </c>
       <c r="B979">
@@ -31702,7 +31756,7 @@
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A980" s="10">
-        <f>DATEVALUE(MID(F980,5,2) &amp; "-" &amp; LEFT(F980,3) &amp; "-" &amp; MID(F980,8,4)) + TIMEVALUE(MID(F980,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44980.513101851851</v>
       </c>
       <c r="B980">
@@ -31723,7 +31777,7 @@
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A981" s="10">
-        <f>DATEVALUE(MID(F981,5,2) &amp; "-" &amp; LEFT(F981,3) &amp; "-" &amp; MID(F981,8,4)) + TIMEVALUE(MID(F981,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44980.563506944447</v>
       </c>
       <c r="B981">
@@ -31744,7 +31798,7 @@
     </row>
     <row r="982" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A982" s="10">
-        <f>DATEVALUE(MID(F982,5,2) &amp; "-" &amp; LEFT(F982,3) &amp; "-" &amp; MID(F982,8,4)) + TIMEVALUE(MID(F982,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44981.460405092592</v>
       </c>
       <c r="B982">
@@ -31765,7 +31819,7 @@
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A983" s="10">
-        <f>DATEVALUE(MID(F983,5,2) &amp; "-" &amp; LEFT(F983,3) &amp; "-" &amp; MID(F983,8,4)) + TIMEVALUE(MID(F983,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44982.532627314817</v>
       </c>
       <c r="B983">
@@ -31786,7 +31840,7 @@
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A984" s="10">
-        <f>DATEVALUE(MID(F984,5,2) &amp; "-" &amp; LEFT(F984,3) &amp; "-" &amp; MID(F984,8,4)) + TIMEVALUE(MID(F984,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44986.493750000001</v>
       </c>
       <c r="B984">
@@ -31807,7 +31861,7 @@
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A985" s="10">
-        <f>DATEVALUE(MID(F985,5,2) &amp; "-" &amp; LEFT(F985,3) &amp; "-" &amp; MID(F985,8,4)) + TIMEVALUE(MID(F985,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44987.497777777775</v>
       </c>
       <c r="B985">
@@ -31828,7 +31882,7 @@
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A986" s="10">
-        <f>DATEVALUE(MID(F986,5,2) &amp; "-" &amp; LEFT(F986,3) &amp; "-" &amp; MID(F986,8,4)) + TIMEVALUE(MID(F986,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44988.53230324074</v>
       </c>
       <c r="B986">
@@ -31849,7 +31903,7 @@
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A987" s="10">
-        <f>DATEVALUE(MID(F987,5,2) &amp; "-" &amp; LEFT(F987,3) &amp; "-" &amp; MID(F987,8,4)) + TIMEVALUE(MID(F987,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44989.543506944443</v>
       </c>
       <c r="B987">
@@ -31870,7 +31924,7 @@
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A988" s="10">
-        <f>DATEVALUE(MID(F988,5,2) &amp; "-" &amp; LEFT(F988,3) &amp; "-" &amp; MID(F988,8,4)) + TIMEVALUE(MID(F988,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44990.570509259262</v>
       </c>
       <c r="B988">
@@ -31891,7 +31945,7 @@
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A989" s="10">
-        <f>DATEVALUE(MID(F989,5,2) &amp; "-" &amp; LEFT(F989,3) &amp; "-" &amp; MID(F989,8,4)) + TIMEVALUE(MID(F989,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44991.517638888887</v>
       </c>
       <c r="B989">
@@ -31912,7 +31966,7 @@
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A990" s="10">
-        <f>DATEVALUE(MID(F990,5,2) &amp; "-" &amp; LEFT(F990,3) &amp; "-" &amp; MID(F990,8,4)) + TIMEVALUE(MID(F990,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44992.484965277778</v>
       </c>
       <c r="B990">
@@ -31933,7 +31987,7 @@
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A991" s="10">
-        <f>DATEVALUE(MID(F991,5,2) &amp; "-" &amp; LEFT(F991,3) &amp; "-" &amp; MID(F991,8,4)) + TIMEVALUE(MID(F991,13,11))</f>
+        <f t="shared" si="9"/>
         <v>44993.486192129632</v>
       </c>
       <c r="B991">
@@ -31954,7 +32008,7 @@
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A992" s="10">
-        <f>DATEVALUE(MID(F992,5,2) &amp; "-" &amp; LEFT(F992,3) &amp; "-" &amp; MID(F992,8,4)) + TIMEVALUE(MID(F992,13,11))</f>
+        <f t="shared" ref="A992:A1055" si="10">DATEVALUE(MID(F992,5,2) &amp; "-" &amp; LEFT(F992,3) &amp; "-" &amp; MID(F992,8,4)) + TIMEVALUE(MID(F992,13,11))</f>
         <v>44994.514467592591</v>
       </c>
       <c r="B992">
@@ -31975,7 +32029,7 @@
     </row>
     <row r="993" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A993" s="10">
-        <f>DATEVALUE(MID(F993,5,2) &amp; "-" &amp; LEFT(F993,3) &amp; "-" &amp; MID(F993,8,4)) + TIMEVALUE(MID(F993,13,11))</f>
+        <f t="shared" si="10"/>
         <v>44995.488055555557</v>
       </c>
       <c r="B993">
@@ -31996,7 +32050,7 @@
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A994" s="10">
-        <f>DATEVALUE(MID(F994,5,2) &amp; "-" &amp; LEFT(F994,3) &amp; "-" &amp; MID(F994,8,4)) + TIMEVALUE(MID(F994,13,11))</f>
+        <f t="shared" si="10"/>
         <v>44999.478773148148</v>
       </c>
       <c r="B994">
@@ -32017,7 +32071,7 @@
     </row>
     <row r="995" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A995" s="10">
-        <f>DATEVALUE(MID(F995,5,2) &amp; "-" &amp; LEFT(F995,3) &amp; "-" &amp; MID(F995,8,4)) + TIMEVALUE(MID(F995,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45000.470393518517</v>
       </c>
       <c r="B995">
@@ -32038,7 +32092,7 @@
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A996" s="10">
-        <f>DATEVALUE(MID(F996,5,2) &amp; "-" &amp; LEFT(F996,3) &amp; "-" &amp; MID(F996,8,4)) + TIMEVALUE(MID(F996,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45001.488541666666</v>
       </c>
       <c r="B996">
@@ -32059,7 +32113,7 @@
     </row>
     <row r="997" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A997" s="10">
-        <f>DATEVALUE(MID(F997,5,2) &amp; "-" &amp; LEFT(F997,3) &amp; "-" &amp; MID(F997,8,4)) + TIMEVALUE(MID(F997,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45006.462500000001</v>
       </c>
       <c r="B997">
@@ -32080,7 +32134,7 @@
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A998" s="10">
-        <f>DATEVALUE(MID(F998,5,2) &amp; "-" &amp; LEFT(F998,3) &amp; "-" &amp; MID(F998,8,4)) + TIMEVALUE(MID(F998,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45011.51321759259</v>
       </c>
       <c r="B998">
@@ -32101,7 +32155,7 @@
     </row>
     <row r="999" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A999" s="10">
-        <f>DATEVALUE(MID(F999,5,2) &amp; "-" &amp; LEFT(F999,3) &amp; "-" &amp; MID(F999,8,4)) + TIMEVALUE(MID(F999,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45012.493472222224</v>
       </c>
       <c r="B999">
@@ -32122,7 +32176,7 @@
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1000" s="10">
-        <f>DATEVALUE(MID(F1000,5,2) &amp; "-" &amp; LEFT(F1000,3) &amp; "-" &amp; MID(F1000,8,4)) + TIMEVALUE(MID(F1000,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45013.50886574074</v>
       </c>
       <c r="B1000">
@@ -32143,7 +32197,7 @@
     </row>
     <row r="1001" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1001" s="10">
-        <f>DATEVALUE(MID(F1001,5,2) &amp; "-" &amp; LEFT(F1001,3) &amp; "-" &amp; MID(F1001,8,4)) + TIMEVALUE(MID(F1001,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45013.509976851848</v>
       </c>
       <c r="B1001">
@@ -32164,7 +32218,7 @@
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1002" s="10">
-        <f>DATEVALUE(MID(F1002,5,2) &amp; "-" &amp; LEFT(F1002,3) &amp; "-" &amp; MID(F1002,8,4)) + TIMEVALUE(MID(F1002,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45014.493472222224</v>
       </c>
       <c r="B1002">
@@ -32185,7 +32239,7 @@
     </row>
     <row r="1003" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1003" s="10">
-        <f>DATEVALUE(MID(F1003,5,2) &amp; "-" &amp; LEFT(F1003,3) &amp; "-" &amp; MID(F1003,8,4)) + TIMEVALUE(MID(F1003,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45015.465590277781</v>
       </c>
       <c r="B1003">
@@ -32206,7 +32260,7 @@
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1004" s="10">
-        <f>DATEVALUE(MID(F1004,5,2) &amp; "-" &amp; LEFT(F1004,3) &amp; "-" &amp; MID(F1004,8,4)) + TIMEVALUE(MID(F1004,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45016.472372685188</v>
       </c>
       <c r="B1004">
@@ -32227,7 +32281,7 @@
     </row>
     <row r="1005" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1005" s="10">
-        <f>DATEVALUE(MID(F1005,5,2) &amp; "-" &amp; LEFT(F1005,3) &amp; "-" &amp; MID(F1005,8,4)) + TIMEVALUE(MID(F1005,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45017.42459490741</v>
       </c>
       <c r="B1005">
@@ -32248,7 +32302,7 @@
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1006" s="10">
-        <f>DATEVALUE(MID(F1006,5,2) &amp; "-" &amp; LEFT(F1006,3) &amp; "-" &amp; MID(F1006,8,4)) + TIMEVALUE(MID(F1006,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45018.52921296296</v>
       </c>
       <c r="B1006">
@@ -32269,7 +32323,7 @@
     </row>
     <row r="1007" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1007" s="10">
-        <f>DATEVALUE(MID(F1007,5,2) &amp; "-" &amp; LEFT(F1007,3) &amp; "-" &amp; MID(F1007,8,4)) + TIMEVALUE(MID(F1007,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45019.471145833333</v>
       </c>
       <c r="B1007">
@@ -32290,7 +32344,7 @@
     </row>
     <row r="1008" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1008" s="10">
-        <f>DATEVALUE(MID(F1008,5,2) &amp; "-" &amp; LEFT(F1008,3) &amp; "-" &amp; MID(F1008,8,4)) + TIMEVALUE(MID(F1008,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45020.480879629627</v>
       </c>
       <c r="B1008">
@@ -32311,7 +32365,7 @@
     </row>
     <row r="1009" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1009" s="10">
-        <f>DATEVALUE(MID(F1009,5,2) &amp; "-" &amp; LEFT(F1009,3) &amp; "-" &amp; MID(F1009,8,4)) + TIMEVALUE(MID(F1009,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45021.466412037036</v>
       </c>
       <c r="B1009">
@@ -32332,7 +32386,7 @@
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1010" s="10">
-        <f>DATEVALUE(MID(F1010,5,2) &amp; "-" &amp; LEFT(F1010,3) &amp; "-" &amp; MID(F1010,8,4)) + TIMEVALUE(MID(F1010,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45022.460439814815</v>
       </c>
       <c r="B1010">
@@ -32353,7 +32407,7 @@
     </row>
     <row r="1011" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1011" s="10">
-        <f>DATEVALUE(MID(F1011,5,2) &amp; "-" &amp; LEFT(F1011,3) &amp; "-" &amp; MID(F1011,8,4)) + TIMEVALUE(MID(F1011,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45023.509513888886</v>
       </c>
       <c r="B1011">
@@ -32374,7 +32428,7 @@
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1012" s="10">
-        <f>DATEVALUE(MID(F1012,5,2) &amp; "-" &amp; LEFT(F1012,3) &amp; "-" &amp; MID(F1012,8,4)) + TIMEVALUE(MID(F1012,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45024.522523148145</v>
       </c>
       <c r="B1012">
@@ -32395,7 +32449,7 @@
     </row>
     <row r="1013" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1013" s="10">
-        <f>DATEVALUE(MID(F1013,5,2) &amp; "-" &amp; LEFT(F1013,3) &amp; "-" &amp; MID(F1013,8,4)) + TIMEVALUE(MID(F1013,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45025.514270833337</v>
       </c>
       <c r="B1013">
@@ -32416,7 +32470,7 @@
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1014" s="10">
-        <f>DATEVALUE(MID(F1014,5,2) &amp; "-" &amp; LEFT(F1014,3) &amp; "-" &amp; MID(F1014,8,4)) + TIMEVALUE(MID(F1014,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45026.496319444443</v>
       </c>
       <c r="B1014">
@@ -32437,7 +32491,7 @@
     </row>
     <row r="1015" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1015" s="10">
-        <f>DATEVALUE(MID(F1015,5,2) &amp; "-" &amp; LEFT(F1015,3) &amp; "-" &amp; MID(F1015,8,4)) + TIMEVALUE(MID(F1015,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45027.469467592593</v>
       </c>
       <c r="B1015">
@@ -32458,7 +32512,7 @@
     </row>
     <row r="1016" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1016" s="10">
-        <f>DATEVALUE(MID(F1016,5,2) &amp; "-" &amp; LEFT(F1016,3) &amp; "-" &amp; MID(F1016,8,4)) + TIMEVALUE(MID(F1016,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45028.475162037037</v>
       </c>
       <c r="B1016">
@@ -32479,7 +32533,7 @@
     </row>
     <row r="1017" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1017" s="10">
-        <f>DATEVALUE(MID(F1017,5,2) &amp; "-" &amp; LEFT(F1017,3) &amp; "-" &amp; MID(F1017,8,4)) + TIMEVALUE(MID(F1017,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45029.453460648147</v>
       </c>
       <c r="B1017">
@@ -32500,7 +32554,7 @@
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1018" s="10">
-        <f>DATEVALUE(MID(F1018,5,2) &amp; "-" &amp; LEFT(F1018,3) &amp; "-" &amp; MID(F1018,8,4)) + TIMEVALUE(MID(F1018,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45030.488564814812</v>
       </c>
       <c r="B1018">
@@ -32521,7 +32575,7 @@
     </row>
     <row r="1019" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1019" s="10">
-        <f>DATEVALUE(MID(F1019,5,2) &amp; "-" &amp; LEFT(F1019,3) &amp; "-" &amp; MID(F1019,8,4)) + TIMEVALUE(MID(F1019,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45031.518657407411</v>
       </c>
       <c r="B1019">
@@ -32542,7 +32596,7 @@
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1020" s="10">
-        <f>DATEVALUE(MID(F1020,5,2) &amp; "-" &amp; LEFT(F1020,3) &amp; "-" &amp; MID(F1020,8,4)) + TIMEVALUE(MID(F1020,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45034.459629629629</v>
       </c>
       <c r="B1020">
@@ -32563,7 +32617,7 @@
     </row>
     <row r="1021" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1021" s="10">
-        <f>DATEVALUE(MID(F1021,5,2) &amp; "-" &amp; LEFT(F1021,3) &amp; "-" &amp; MID(F1021,8,4)) + TIMEVALUE(MID(F1021,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45035.484409722223</v>
       </c>
       <c r="B1021">
@@ -32584,7 +32638,7 @@
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1022" s="10">
-        <f>DATEVALUE(MID(F1022,5,2) &amp; "-" &amp; LEFT(F1022,3) &amp; "-" &amp; MID(F1022,8,4)) + TIMEVALUE(MID(F1022,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45036.472986111112</v>
       </c>
       <c r="B1022">
@@ -32605,7 +32659,7 @@
     </row>
     <row r="1023" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1023" s="10">
-        <f>DATEVALUE(MID(F1023,5,2) &amp; "-" &amp; LEFT(F1023,3) &amp; "-" &amp; MID(F1023,8,4)) + TIMEVALUE(MID(F1023,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45037.447870370372</v>
       </c>
       <c r="B1023">
@@ -32626,7 +32680,7 @@
     </row>
     <row r="1024" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1024" s="10">
-        <f>DATEVALUE(MID(F1024,5,2) &amp; "-" &amp; LEFT(F1024,3) &amp; "-" &amp; MID(F1024,8,4)) + TIMEVALUE(MID(F1024,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45039.487951388888</v>
       </c>
       <c r="B1024">
@@ -32647,7 +32701,7 @@
     </row>
     <row r="1025" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1025" s="10">
-        <f>DATEVALUE(MID(F1025,5,2) &amp; "-" &amp; LEFT(F1025,3) &amp; "-" &amp; MID(F1025,8,4)) + TIMEVALUE(MID(F1025,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45040.458773148152</v>
       </c>
       <c r="B1025">
@@ -32668,7 +32722,7 @@
     </row>
     <row r="1026" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1026" s="10">
-        <f>DATEVALUE(MID(F1026,5,2) &amp; "-" &amp; LEFT(F1026,3) &amp; "-" &amp; MID(F1026,8,4)) + TIMEVALUE(MID(F1026,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45041.456493055557</v>
       </c>
       <c r="B1026">
@@ -32689,7 +32743,7 @@
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1027" s="10">
-        <f>DATEVALUE(MID(F1027,5,2) &amp; "-" &amp; LEFT(F1027,3) &amp; "-" &amp; MID(F1027,8,4)) + TIMEVALUE(MID(F1027,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45042.436388888891</v>
       </c>
       <c r="B1027">
@@ -32710,7 +32764,7 @@
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1028" s="10">
-        <f>DATEVALUE(MID(F1028,5,2) &amp; "-" &amp; LEFT(F1028,3) &amp; "-" &amp; MID(F1028,8,4)) + TIMEVALUE(MID(F1028,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45043.463194444441</v>
       </c>
       <c r="B1028">
@@ -32731,7 +32785,7 @@
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1029" s="10">
-        <f>DATEVALUE(MID(F1029,5,2) &amp; "-" &amp; LEFT(F1029,3) &amp; "-" &amp; MID(F1029,8,4)) + TIMEVALUE(MID(F1029,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45044.43310185185</v>
       </c>
       <c r="B1029">
@@ -32752,7 +32806,7 @@
     </row>
     <row r="1030" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1030" s="10">
-        <f>DATEVALUE(MID(F1030,5,2) &amp; "-" &amp; LEFT(F1030,3) &amp; "-" &amp; MID(F1030,8,4)) + TIMEVALUE(MID(F1030,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45047.456354166665</v>
       </c>
       <c r="B1030">
@@ -32773,7 +32827,7 @@
     </row>
     <row r="1031" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1031" s="10">
-        <f>DATEVALUE(MID(F1031,5,2) &amp; "-" &amp; LEFT(F1031,3) &amp; "-" &amp; MID(F1031,8,4)) + TIMEVALUE(MID(F1031,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45048.45921296296</v>
       </c>
       <c r="B1031">
@@ -32794,7 +32848,7 @@
     </row>
     <row r="1032" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1032" s="10">
-        <f>DATEVALUE(MID(F1032,5,2) &amp; "-" &amp; LEFT(F1032,3) &amp; "-" &amp; MID(F1032,8,4)) + TIMEVALUE(MID(F1032,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45049.472349537034</v>
       </c>
       <c r="B1032">
@@ -32815,7 +32869,7 @@
     </row>
     <row r="1033" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1033" s="10">
-        <f>DATEVALUE(MID(F1033,5,2) &amp; "-" &amp; LEFT(F1033,3) &amp; "-" &amp; MID(F1033,8,4)) + TIMEVALUE(MID(F1033,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45050.48883101852</v>
       </c>
       <c r="B1033">
@@ -32836,7 +32890,7 @@
     </row>
     <row r="1034" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1034" s="10">
-        <f>DATEVALUE(MID(F1034,5,2) &amp; "-" &amp; LEFT(F1034,3) &amp; "-" &amp; MID(F1034,8,4)) + TIMEVALUE(MID(F1034,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45051.485462962963</v>
       </c>
       <c r="B1034">
@@ -32857,7 +32911,7 @@
     </row>
     <row r="1035" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1035" s="10">
-        <f>DATEVALUE(MID(F1035,5,2) &amp; "-" &amp; LEFT(F1035,3) &amp; "-" &amp; MID(F1035,8,4)) + TIMEVALUE(MID(F1035,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45052.482094907406</v>
       </c>
       <c r="B1035">
@@ -32878,7 +32932,7 @@
     </row>
     <row r="1036" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1036" s="10">
-        <f>DATEVALUE(MID(F1036,5,2) &amp; "-" &amp; LEFT(F1036,3) &amp; "-" &amp; MID(F1036,8,4)) + TIMEVALUE(MID(F1036,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45053.480821759258</v>
       </c>
       <c r="B1036">
@@ -32899,7 +32953,7 @@
     </row>
     <row r="1037" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1037" s="10">
-        <f>DATEVALUE(MID(F1037,5,2) &amp; "-" &amp; LEFT(F1037,3) &amp; "-" &amp; MID(F1037,8,4)) + TIMEVALUE(MID(F1037,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45054.485937500001</v>
       </c>
       <c r="B1037">
@@ -32920,7 +32974,7 @@
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1038" s="10">
-        <f>DATEVALUE(MID(F1038,5,2) &amp; "-" &amp; LEFT(F1038,3) &amp; "-" &amp; MID(F1038,8,4)) + TIMEVALUE(MID(F1038,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45055.474259259259</v>
       </c>
       <c r="B1038">
@@ -32941,7 +32995,7 @@
     </row>
     <row r="1039" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1039" s="10">
-        <f>DATEVALUE(MID(F1039,5,2) &amp; "-" &amp; LEFT(F1039,3) &amp; "-" &amp; MID(F1039,8,4)) + TIMEVALUE(MID(F1039,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45056.502256944441</v>
       </c>
       <c r="B1039">
@@ -32962,7 +33016,7 @@
     </row>
     <row r="1040" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1040" s="10">
-        <f>DATEVALUE(MID(F1040,5,2) &amp; "-" &amp; LEFT(F1040,3) &amp; "-" &amp; MID(F1040,8,4)) + TIMEVALUE(MID(F1040,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45057.451678240737</v>
       </c>
       <c r="B1040">
@@ -32983,7 +33037,7 @@
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1041" s="10">
-        <f>DATEVALUE(MID(F1041,5,2) &amp; "-" &amp; LEFT(F1041,3) &amp; "-" &amp; MID(F1041,8,4)) + TIMEVALUE(MID(F1041,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45058.462002314816</v>
       </c>
       <c r="B1041">
@@ -33004,7 +33058,7 @@
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1042" s="10">
-        <f>DATEVALUE(MID(F1042,5,2) &amp; "-" &amp; LEFT(F1042,3) &amp; "-" &amp; MID(F1042,8,4)) + TIMEVALUE(MID(F1042,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45059.471192129633</v>
       </c>
       <c r="B1042">
@@ -33025,7 +33079,7 @@
     </row>
     <row r="1043" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1043" s="10">
-        <f>DATEVALUE(MID(F1043,5,2) &amp; "-" &amp; LEFT(F1043,3) &amp; "-" &amp; MID(F1043,8,4)) + TIMEVALUE(MID(F1043,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45060.431967592594</v>
       </c>
       <c r="B1043">
@@ -33046,7 +33100,7 @@
     </row>
     <row r="1044" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1044" s="10">
-        <f>DATEVALUE(MID(F1044,5,2) &amp; "-" &amp; LEFT(F1044,3) &amp; "-" &amp; MID(F1044,8,4)) + TIMEVALUE(MID(F1044,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45061.419178240743</v>
       </c>
       <c r="B1044">
@@ -33067,7 +33121,7 @@
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1045" s="10">
-        <f>DATEVALUE(MID(F1045,5,2) &amp; "-" &amp; LEFT(F1045,3) &amp; "-" &amp; MID(F1045,8,4)) + TIMEVALUE(MID(F1045,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45062.392002314817</v>
       </c>
       <c r="B1045">
@@ -33088,7 +33142,7 @@
     </row>
     <row r="1046" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1046" s="10">
-        <f>DATEVALUE(MID(F1046,5,2) &amp; "-" &amp; LEFT(F1046,3) &amp; "-" &amp; MID(F1046,8,4)) + TIMEVALUE(MID(F1046,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45063.357766203706</v>
       </c>
       <c r="B1046">
@@ -33109,7 +33163,7 @@
     </row>
     <row r="1047" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1047" s="10">
-        <f>DATEVALUE(MID(F1047,5,2) &amp; "-" &amp; LEFT(F1047,3) &amp; "-" &amp; MID(F1047,8,4)) + TIMEVALUE(MID(F1047,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45064.443541666667</v>
       </c>
       <c r="B1047">
@@ -33130,7 +33184,7 @@
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1048" s="10">
-        <f>DATEVALUE(MID(F1048,5,2) &amp; "-" &amp; LEFT(F1048,3) &amp; "-" &amp; MID(F1048,8,4)) + TIMEVALUE(MID(F1048,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45065.349641203706</v>
       </c>
       <c r="B1048">
@@ -33151,7 +33205,7 @@
     </row>
     <row r="1049" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1049" s="10">
-        <f>DATEVALUE(MID(F1049,5,2) &amp; "-" &amp; LEFT(F1049,3) &amp; "-" &amp; MID(F1049,8,4)) + TIMEVALUE(MID(F1049,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45066.472592592596</v>
       </c>
       <c r="B1049">
@@ -33172,7 +33226,7 @@
     </row>
     <row r="1050" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1050" s="10">
-        <f>DATEVALUE(MID(F1050,5,2) &amp; "-" &amp; LEFT(F1050,3) &amp; "-" &amp; MID(F1050,8,4)) + TIMEVALUE(MID(F1050,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45067.473263888889</v>
       </c>
       <c r="B1050">
@@ -33193,7 +33247,7 @@
     </row>
     <row r="1051" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1051" s="10">
-        <f>DATEVALUE(MID(F1051,5,2) &amp; "-" &amp; LEFT(F1051,3) &amp; "-" &amp; MID(F1051,8,4)) + TIMEVALUE(MID(F1051,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45068.381886574076</v>
       </c>
       <c r="B1051">
@@ -33214,7 +33268,7 @@
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1052" s="10">
-        <f>DATEVALUE(MID(F1052,5,2) &amp; "-" &amp; LEFT(F1052,3) &amp; "-" &amp; MID(F1052,8,4)) + TIMEVALUE(MID(F1052,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45069.398726851854</v>
       </c>
       <c r="B1052">
@@ -33235,7 +33289,7 @@
     </row>
     <row r="1053" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1053" s="10">
-        <f>DATEVALUE(MID(F1053,5,2) &amp; "-" &amp; LEFT(F1053,3) &amp; "-" &amp; MID(F1053,8,4)) + TIMEVALUE(MID(F1053,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45070.387060185189</v>
       </c>
       <c r="B1053">
@@ -33256,7 +33310,7 @@
     </row>
     <row r="1054" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1054" s="10">
-        <f>DATEVALUE(MID(F1054,5,2) &amp; "-" &amp; LEFT(F1054,3) &amp; "-" &amp; MID(F1054,8,4)) + TIMEVALUE(MID(F1054,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45070.480312500003</v>
       </c>
       <c r="B1054">
@@ -33277,7 +33331,7 @@
     </row>
     <row r="1055" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1055" s="10">
-        <f>DATEVALUE(MID(F1055,5,2) &amp; "-" &amp; LEFT(F1055,3) &amp; "-" &amp; MID(F1055,8,4)) + TIMEVALUE(MID(F1055,13,11))</f>
+        <f t="shared" si="10"/>
         <v>45071.389791666668</v>
       </c>
       <c r="B1055">
@@ -33298,7 +33352,7 @@
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1056" s="10">
-        <f>DATEVALUE(MID(F1056,5,2) &amp; "-" &amp; LEFT(F1056,3) &amp; "-" &amp; MID(F1056,8,4)) + TIMEVALUE(MID(F1056,13,11))</f>
+        <f t="shared" ref="A1056:A1103" si="11">DATEVALUE(MID(F1056,5,2) &amp; "-" &amp; LEFT(F1056,3) &amp; "-" &amp; MID(F1056,8,4)) + TIMEVALUE(MID(F1056,13,11))</f>
         <v>45074.491273148145</v>
       </c>
       <c r="B1056">
@@ -33319,7 +33373,7 @@
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1057" s="10">
-        <f>DATEVALUE(MID(F1057,5,2) &amp; "-" &amp; LEFT(F1057,3) &amp; "-" &amp; MID(F1057,8,4)) + TIMEVALUE(MID(F1057,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45075.401331018518</v>
       </c>
       <c r="B1057">
@@ -33340,7 +33394,7 @@
     </row>
     <row r="1058" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1058" s="10">
-        <f>DATEVALUE(MID(F1058,5,2) &amp; "-" &amp; LEFT(F1058,3) &amp; "-" &amp; MID(F1058,8,4)) + TIMEVALUE(MID(F1058,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45076.410277777781</v>
       </c>
       <c r="B1058">
@@ -33361,7 +33415,7 @@
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1059" s="10">
-        <f>DATEVALUE(MID(F1059,5,2) &amp; "-" &amp; LEFT(F1059,3) &amp; "-" &amp; MID(F1059,8,4)) + TIMEVALUE(MID(F1059,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45078.399351851855</v>
       </c>
       <c r="B1059">
@@ -33382,7 +33436,7 @@
     </row>
     <row r="1060" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1060" s="10">
-        <f>DATEVALUE(MID(F1060,5,2) &amp; "-" &amp; LEFT(F1060,3) &amp; "-" &amp; MID(F1060,8,4)) + TIMEVALUE(MID(F1060,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45091.362430555557</v>
       </c>
       <c r="B1060">
@@ -33403,7 +33457,7 @@
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1061" s="10">
-        <f>DATEVALUE(MID(F1061,5,2) &amp; "-" &amp; LEFT(F1061,3) &amp; "-" &amp; MID(F1061,8,4)) + TIMEVALUE(MID(F1061,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45092.466145833336</v>
       </c>
       <c r="B1061">
@@ -33424,7 +33478,7 @@
     </row>
     <row r="1062" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1062" s="10">
-        <f>DATEVALUE(MID(F1062,5,2) &amp; "-" &amp; LEFT(F1062,3) &amp; "-" &amp; MID(F1062,8,4)) + TIMEVALUE(MID(F1062,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45093.448136574072</v>
       </c>
       <c r="B1062">
@@ -33445,7 +33499,7 @@
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1063" s="10">
-        <f>DATEVALUE(MID(F1063,5,2) &amp; "-" &amp; LEFT(F1063,3) &amp; "-" &amp; MID(F1063,8,4)) + TIMEVALUE(MID(F1063,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45094.441134259258</v>
       </c>
       <c r="B1063">
@@ -33466,7 +33520,7 @@
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1064" s="10">
-        <f>DATEVALUE(MID(F1064,5,2) &amp; "-" &amp; LEFT(F1064,3) &amp; "-" &amp; MID(F1064,8,4)) + TIMEVALUE(MID(F1064,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45095.437557870369</v>
       </c>
       <c r="B1064">
@@ -33487,7 +33541,7 @@
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1065" s="10">
-        <f>DATEVALUE(MID(F1065,5,2) &amp; "-" &amp; LEFT(F1065,3) &amp; "-" &amp; MID(F1065,8,4)) + TIMEVALUE(MID(F1065,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45096.417048611111</v>
       </c>
       <c r="B1065">
@@ -33508,7 +33562,7 @@
     </row>
     <row r="1066" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1066" s="10">
-        <f>DATEVALUE(MID(F1066,5,2) &amp; "-" &amp; LEFT(F1066,3) &amp; "-" &amp; MID(F1066,8,4)) + TIMEVALUE(MID(F1066,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45097.413807870369</v>
       </c>
       <c r="B1066">
@@ -33529,7 +33583,7 @@
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1067" s="10">
-        <f>DATEVALUE(MID(F1067,5,2) &amp; "-" &amp; LEFT(F1067,3) &amp; "-" &amp; MID(F1067,8,4)) + TIMEVALUE(MID(F1067,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45098.426828703705</v>
       </c>
       <c r="B1067">
@@ -33550,7 +33604,7 @@
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1068" s="10">
-        <f>DATEVALUE(MID(F1068,5,2) &amp; "-" &amp; LEFT(F1068,3) &amp; "-" &amp; MID(F1068,8,4)) + TIMEVALUE(MID(F1068,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45099.424722222226</v>
       </c>
       <c r="B1068">
@@ -33571,7 +33625,7 @@
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1069" s="10">
-        <f>DATEVALUE(MID(F1069,5,2) &amp; "-" &amp; LEFT(F1069,3) &amp; "-" &amp; MID(F1069,8,4)) + TIMEVALUE(MID(F1069,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45100.42832175926</v>
       </c>
       <c r="B1069">
@@ -33592,7 +33646,7 @@
     </row>
     <row r="1070" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1070" s="10">
-        <f>DATEVALUE(MID(F1070,5,2) &amp; "-" &amp; LEFT(F1070,3) &amp; "-" &amp; MID(F1070,8,4)) + TIMEVALUE(MID(F1070,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45101.420543981483</v>
       </c>
       <c r="B1070">
@@ -33613,7 +33667,7 @@
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1071" s="10">
-        <f>DATEVALUE(MID(F1071,5,2) &amp; "-" &amp; LEFT(F1071,3) &amp; "-" &amp; MID(F1071,8,4)) + TIMEVALUE(MID(F1071,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45104.406712962962</v>
       </c>
       <c r="B1071">
@@ -33634,7 +33688,7 @@
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1072" s="10">
-        <f>DATEVALUE(MID(F1072,5,2) &amp; "-" &amp; LEFT(F1072,3) &amp; "-" &amp; MID(F1072,8,4)) + TIMEVALUE(MID(F1072,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45105.362916666665</v>
       </c>
       <c r="B1072">
@@ -33655,7 +33709,7 @@
     </row>
     <row r="1073" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1073" s="10">
-        <f>DATEVALUE(MID(F1073,5,2) &amp; "-" &amp; LEFT(F1073,3) &amp; "-" &amp; MID(F1073,8,4)) + TIMEVALUE(MID(F1073,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45106.391284722224</v>
       </c>
       <c r="B1073">
@@ -33676,7 +33730,7 @@
     </row>
     <row r="1074" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1074" s="10">
-        <f>DATEVALUE(MID(F1074,5,2) &amp; "-" &amp; LEFT(F1074,3) &amp; "-" &amp; MID(F1074,8,4)) + TIMEVALUE(MID(F1074,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45107.425023148149</v>
       </c>
       <c r="B1074">
@@ -33697,7 +33751,7 @@
     </row>
     <row r="1075" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1075" s="10">
-        <f>DATEVALUE(MID(F1075,5,2) &amp; "-" &amp; LEFT(F1075,3) &amp; "-" &amp; MID(F1075,8,4)) + TIMEVALUE(MID(F1075,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45108.462743055556</v>
       </c>
       <c r="B1075">
@@ -33718,7 +33772,7 @@
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1076" s="10">
-        <f>DATEVALUE(MID(F1076,5,2) &amp; "-" &amp; LEFT(F1076,3) &amp; "-" &amp; MID(F1076,8,4)) + TIMEVALUE(MID(F1076,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45111.456712962965</v>
       </c>
       <c r="B1076">
@@ -33739,7 +33793,7 @@
     </row>
     <row r="1077" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1077" s="10">
-        <f>DATEVALUE(MID(F1077,5,2) &amp; "-" &amp; LEFT(F1077,3) &amp; "-" &amp; MID(F1077,8,4)) + TIMEVALUE(MID(F1077,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45112.436585648145</v>
       </c>
       <c r="B1077">
@@ -33760,7 +33814,7 @@
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1078" s="10">
-        <f>DATEVALUE(MID(F1078,5,2) &amp; "-" &amp; LEFT(F1078,3) &amp; "-" &amp; MID(F1078,8,4)) + TIMEVALUE(MID(F1078,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45113.4452662037</v>
       </c>
       <c r="B1078">
@@ -33781,7 +33835,7 @@
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1079" s="10">
-        <f>DATEVALUE(MID(F1079,5,2) &amp; "-" &amp; LEFT(F1079,3) &amp; "-" &amp; MID(F1079,8,4)) + TIMEVALUE(MID(F1079,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45114.330567129633</v>
       </c>
       <c r="B1079">
@@ -33802,7 +33856,7 @@
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1080" s="10">
-        <f>DATEVALUE(MID(F1080,5,2) &amp; "-" &amp; LEFT(F1080,3) &amp; "-" &amp; MID(F1080,8,4)) + TIMEVALUE(MID(F1080,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45115.391400462962</v>
       </c>
       <c r="B1080">
@@ -33823,7 +33877,7 @@
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1081" s="10">
-        <f>DATEVALUE(MID(F1081,5,2) &amp; "-" &amp; LEFT(F1081,3) &amp; "-" &amp; MID(F1081,8,4)) + TIMEVALUE(MID(F1081,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45118.42392361111</v>
       </c>
       <c r="B1081">
@@ -33844,7 +33898,7 @@
     </row>
     <row r="1082" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1082" s="10">
-        <f>DATEVALUE(MID(F1082,5,2) &amp; "-" &amp; LEFT(F1082,3) &amp; "-" &amp; MID(F1082,8,4)) + TIMEVALUE(MID(F1082,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45119.426446759258</v>
       </c>
       <c r="B1082">
@@ -33865,7 +33919,7 @@
     </row>
     <row r="1083" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1083" s="10">
-        <f>DATEVALUE(MID(F1083,5,2) &amp; "-" &amp; LEFT(F1083,3) &amp; "-" &amp; MID(F1083,8,4)) + TIMEVALUE(MID(F1083,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45120.367731481485</v>
       </c>
       <c r="B1083">
@@ -33886,7 +33940,7 @@
     </row>
     <row r="1084" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1084" s="10">
-        <f>DATEVALUE(MID(F1084,5,2) &amp; "-" &amp; LEFT(F1084,3) &amp; "-" &amp; MID(F1084,8,4)) + TIMEVALUE(MID(F1084,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45121.421643518515</v>
       </c>
       <c r="B1084">
@@ -33907,7 +33961,7 @@
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1085" s="10">
-        <f>DATEVALUE(MID(F1085,5,2) &amp; "-" &amp; LEFT(F1085,3) &amp; "-" &amp; MID(F1085,8,4)) + TIMEVALUE(MID(F1085,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45122.464108796295</v>
       </c>
       <c r="B1085">
@@ -33928,7 +33982,7 @@
     </row>
     <row r="1086" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1086" s="10">
-        <f>DATEVALUE(MID(F1086,5,2) &amp; "-" &amp; LEFT(F1086,3) &amp; "-" &amp; MID(F1086,8,4)) + TIMEVALUE(MID(F1086,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45123.481435185182</v>
       </c>
       <c r="B1086">
@@ -33949,7 +34003,7 @@
     </row>
     <row r="1087" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1087" s="10">
-        <f>DATEVALUE(MID(F1087,5,2) &amp; "-" &amp; LEFT(F1087,3) &amp; "-" &amp; MID(F1087,8,4)) + TIMEVALUE(MID(F1087,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45124.445590277777</v>
       </c>
       <c r="B1087">
@@ -33970,7 +34024,7 @@
     </row>
     <row r="1088" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1088" s="10">
-        <f>DATEVALUE(MID(F1088,5,2) &amp; "-" &amp; LEFT(F1088,3) &amp; "-" &amp; MID(F1088,8,4)) + TIMEVALUE(MID(F1088,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45125.428472222222</v>
       </c>
       <c r="B1088">
@@ -33991,7 +34045,7 @@
     </row>
     <row r="1089" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1089" s="10">
-        <f>DATEVALUE(MID(F1089,5,2) &amp; "-" &amp; LEFT(F1089,3) &amp; "-" &amp; MID(F1089,8,4)) + TIMEVALUE(MID(F1089,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45126.426238425927</v>
       </c>
       <c r="B1089">
@@ -34012,7 +34066,7 @@
     </row>
     <row r="1090" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1090" s="10">
-        <f>DATEVALUE(MID(F1090,5,2) &amp; "-" &amp; LEFT(F1090,3) &amp; "-" &amp; MID(F1090,8,4)) + TIMEVALUE(MID(F1090,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45127.466215277775</v>
       </c>
       <c r="B1090">
@@ -34033,7 +34087,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1091" s="10">
-        <f>DATEVALUE(MID(F1091,5,2) &amp; "-" &amp; LEFT(F1091,3) &amp; "-" &amp; MID(F1091,8,4)) + TIMEVALUE(MID(F1091,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45128.447881944441</v>
       </c>
       <c r="B1091">
@@ -34054,7 +34108,7 @@
     </row>
     <row r="1092" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1092" s="10">
-        <f>DATEVALUE(MID(F1092,5,2) &amp; "-" &amp; LEFT(F1092,3) &amp; "-" &amp; MID(F1092,8,4)) + TIMEVALUE(MID(F1092,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45130.446423611109</v>
       </c>
       <c r="B1092">
@@ -34075,7 +34129,7 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1093" s="10">
-        <f>DATEVALUE(MID(F1093,5,2) &amp; "-" &amp; LEFT(F1093,3) &amp; "-" &amp; MID(F1093,8,4)) + TIMEVALUE(MID(F1093,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45132.42355324074</v>
       </c>
       <c r="B1093">
@@ -34096,7 +34150,7 @@
     </row>
     <row r="1094" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1094" s="10">
-        <f>DATEVALUE(MID(F1094,5,2) &amp; "-" &amp; LEFT(F1094,3) &amp; "-" &amp; MID(F1094,8,4)) + TIMEVALUE(MID(F1094,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45133.466168981482</v>
       </c>
       <c r="B1094">
@@ -34117,7 +34171,7 @@
     </row>
     <row r="1095" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1095" s="10">
-        <f>DATEVALUE(MID(F1095,5,2) &amp; "-" &amp; LEFT(F1095,3) &amp; "-" &amp; MID(F1095,8,4)) + TIMEVALUE(MID(F1095,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45133.467141203706</v>
       </c>
       <c r="B1095">
@@ -34138,7 +34192,7 @@
     </row>
     <row r="1096" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1096" s="10">
-        <f>DATEVALUE(MID(F1096,5,2) &amp; "-" &amp; LEFT(F1096,3) &amp; "-" &amp; MID(F1096,8,4)) + TIMEVALUE(MID(F1096,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45134.390798611108</v>
       </c>
       <c r="B1096">
@@ -34159,7 +34213,7 @@
     </row>
     <row r="1097" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1097" s="10">
-        <f>DATEVALUE(MID(F1097,5,2) &amp; "-" &amp; LEFT(F1097,3) &amp; "-" &amp; MID(F1097,8,4)) + TIMEVALUE(MID(F1097,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45135.394930555558</v>
       </c>
       <c r="B1097">
@@ -34180,7 +34234,7 @@
     </row>
     <row r="1098" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1098" s="10">
-        <f>DATEVALUE(MID(F1098,5,2) &amp; "-" &amp; LEFT(F1098,3) &amp; "-" &amp; MID(F1098,8,4)) + TIMEVALUE(MID(F1098,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45136.404652777775</v>
       </c>
       <c r="B1098">
@@ -34201,7 +34255,7 @@
     </row>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1099" s="10">
-        <f>DATEVALUE(MID(F1099,5,2) &amp; "-" &amp; LEFT(F1099,3) &amp; "-" &amp; MID(F1099,8,4)) + TIMEVALUE(MID(F1099,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45137.407222222224</v>
       </c>
       <c r="B1099">
@@ -34222,7 +34276,7 @@
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1100" s="10">
-        <f>DATEVALUE(MID(F1100,5,2) &amp; "-" &amp; LEFT(F1100,3) &amp; "-" &amp; MID(F1100,8,4)) + TIMEVALUE(MID(F1100,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45138.447523148148</v>
       </c>
       <c r="B1100">
@@ -34243,7 +34297,7 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1101" s="10">
-        <f>DATEVALUE(MID(F1101,5,2) &amp; "-" &amp; LEFT(F1101,3) &amp; "-" &amp; MID(F1101,8,4)) + TIMEVALUE(MID(F1101,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45140.381805555553</v>
       </c>
       <c r="B1101">
@@ -34264,7 +34318,7 @@
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1102" s="10">
-        <f>DATEVALUE(MID(F1102,5,2) &amp; "-" &amp; LEFT(F1102,3) &amp; "-" &amp; MID(F1102,8,4)) + TIMEVALUE(MID(F1102,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45141.451203703706</v>
       </c>
       <c r="B1102">
@@ -34285,7 +34339,7 @@
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1103" s="10">
-        <f>DATEVALUE(MID(F1103,5,2) &amp; "-" &amp; LEFT(F1103,3) &amp; "-" &amp; MID(F1103,8,4)) + TIMEVALUE(MID(F1103,13,11))</f>
+        <f t="shared" si="11"/>
         <v>45142.393437500003</v>
       </c>
       <c r="B1103">
@@ -34306,7 +34360,7 @@
     </row>
     <row r="1104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1104" s="10">
-        <f t="shared" ref="A1104:A1167" si="0">DATEVALUE(MID(F1104,5,2) &amp; "-" &amp; LEFT(F1104,3) &amp; "-" &amp; MID(F1104,8,4)) + TIMEVALUE(MID(F1104,13,11))</f>
+        <f t="shared" ref="A1104:A1167" si="12">DATEVALUE(MID(F1104,5,2) &amp; "-" &amp; LEFT(F1104,3) &amp; "-" &amp; MID(F1104,8,4)) + TIMEVALUE(MID(F1104,13,11))</f>
         <v>45143.504537037035</v>
       </c>
       <c r="B1104">
@@ -34327,7 +34381,7 @@
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1105" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45144.426678240743</v>
       </c>
       <c r="B1105">
@@ -34348,7 +34402,7 @@
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1106" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45145.450243055559</v>
       </c>
       <c r="B1106">
@@ -34369,7 +34423,7 @@
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1107" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45146.407152777778</v>
       </c>
       <c r="B1107">
@@ -34390,7 +34444,7 @@
     </row>
     <row r="1108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1108" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45148.485254629632</v>
       </c>
       <c r="B1108">
@@ -34411,7 +34465,7 @@
     </row>
     <row r="1109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1109" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45149.427499999998</v>
       </c>
       <c r="B1109">
@@ -34432,7 +34486,7 @@
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1110" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45150.352303240739</v>
       </c>
       <c r="B1110">
@@ -34453,7 +34507,7 @@
     </row>
     <row r="1111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1111" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45154.431817129633</v>
       </c>
       <c r="B1111">
@@ -34474,7 +34528,7 @@
     </row>
     <row r="1112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1112" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45155.466249999998</v>
       </c>
       <c r="B1112">
@@ -34495,7 +34549,7 @@
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1113" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45157.467152777775</v>
       </c>
       <c r="B1113">
@@ -34516,7 +34570,7 @@
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1114" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45159.408541666664</v>
       </c>
       <c r="B1114">
@@ -34537,7 +34591,7 @@
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1115" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45160.406724537039</v>
       </c>
       <c r="B1115">
@@ -34558,7 +34612,7 @@
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1116" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45161.374236111114</v>
       </c>
       <c r="B1116">
@@ -34579,7 +34633,7 @@
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1117" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45162.398090277777</v>
       </c>
       <c r="B1117">
@@ -34600,7 +34654,7 @@
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1118" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45163.431817129633</v>
       </c>
       <c r="B1118">
@@ -34621,7 +34675,7 @@
     </row>
     <row r="1119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1119" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45163.48232638889</v>
       </c>
       <c r="B1119">
@@ -34642,7 +34696,7 @@
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1120" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45164.462719907409</v>
       </c>
       <c r="B1120">
@@ -34663,7 +34717,7 @@
     </row>
     <row r="1121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1121" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45167.414444444446</v>
       </c>
       <c r="B1121">
@@ -34684,7 +34738,7 @@
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1122" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45169.429537037038</v>
       </c>
       <c r="B1122">
@@ -34705,7 +34759,7 @@
     </row>
     <row r="1123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1123" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45171.476956018516</v>
       </c>
       <c r="B1123">
@@ -34726,7 +34780,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1124" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45171.478726851848</v>
       </c>
       <c r="B1124">
@@ -34747,7 +34801,7 @@
     </row>
     <row r="1125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1125" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45175.448981481481</v>
       </c>
       <c r="B1125">
@@ -34768,7 +34822,7 @@
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1126" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45176.458958333336</v>
       </c>
       <c r="B1126">
@@ -34789,7 +34843,7 @@
     </row>
     <row r="1127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1127" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45177.460659722223</v>
       </c>
       <c r="B1127">
@@ -34810,7 +34864,7 @@
     </row>
     <row r="1128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1128" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45178.412962962961</v>
       </c>
       <c r="B1128">
@@ -34831,7 +34885,7 @@
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1129" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45178.421597222223</v>
       </c>
       <c r="B1129">
@@ -34852,7 +34906,7 @@
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1130" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45181.443148148152</v>
       </c>
       <c r="B1130">
@@ -34873,7 +34927,7 @@
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1131" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45182.456145833334</v>
       </c>
       <c r="B1131">
@@ -34894,7 +34948,7 @@
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1132" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45183.457777777781</v>
       </c>
       <c r="B1132">
@@ -34915,7 +34969,7 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1133" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45184.353750000002</v>
       </c>
       <c r="B1133">
@@ -34936,7 +34990,7 @@
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1134" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45187.409016203703</v>
       </c>
       <c r="B1134">
@@ -34957,7 +35011,7 @@
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1135" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45188.427766203706</v>
       </c>
       <c r="B1135">
@@ -34978,7 +35032,7 @@
     </row>
     <row r="1136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1136" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45189.406805555554</v>
       </c>
       <c r="B1136">
@@ -34999,7 +35053,7 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1137" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45190.490995370368</v>
       </c>
       <c r="B1137">
@@ -35020,7 +35074,7 @@
     </row>
     <row r="1138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1138" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45191.434513888889</v>
       </c>
       <c r="B1138">
@@ -35041,7 +35095,7 @@
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1139" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45192.434259259258</v>
       </c>
       <c r="B1139">
@@ -35062,7 +35116,7 @@
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1140" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45193.423344907409</v>
       </c>
       <c r="B1140">
@@ -35083,7 +35137,7 @@
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1141" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45194.466956018521</v>
       </c>
       <c r="B1141">
@@ -35104,7 +35158,7 @@
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1142" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45195.433113425926</v>
       </c>
       <c r="B1142">
@@ -35125,7 +35179,7 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1143" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45198.383391203701</v>
       </c>
       <c r="B1143">
@@ -35146,7 +35200,7 @@
     </row>
     <row r="1144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1144" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45199.457395833335</v>
       </c>
       <c r="B1144">
@@ -35167,7 +35221,7 @@
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1145" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45200.401620370372</v>
       </c>
       <c r="B1145">
@@ -35188,7 +35242,7 @@
     </row>
     <row r="1146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1146" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45201.425763888888</v>
       </c>
       <c r="B1146">
@@ -35209,7 +35263,7 @@
     </row>
     <row r="1147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1147" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45202.407384259262</v>
       </c>
       <c r="B1147">
@@ -35230,7 +35284,7 @@
     </row>
     <row r="1148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1148" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45204.444201388891</v>
       </c>
       <c r="B1148">
@@ -35251,7 +35305,7 @@
     </row>
     <row r="1149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1149" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45205.461597222224</v>
       </c>
       <c r="B1149">
@@ -35272,7 +35326,7 @@
     </row>
     <row r="1150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1150" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45212.424143518518</v>
       </c>
       <c r="B1150">
@@ -35293,7 +35347,7 @@
     </row>
     <row r="1151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1151" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45213.497997685183</v>
       </c>
       <c r="B1151">
@@ -35314,7 +35368,7 @@
     </row>
     <row r="1152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1152" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45214.478842592594</v>
       </c>
       <c r="B1152">
@@ -35335,7 +35389,7 @@
     </row>
     <row r="1153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1153" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45215.47797453704</v>
       </c>
       <c r="B1153">
@@ -35356,7 +35410,7 @@
     </row>
     <row r="1154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1154" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45219.460486111115</v>
       </c>
       <c r="B1154">
@@ -35377,7 +35431,7 @@
     </row>
     <row r="1155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1155" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45223.425833333335</v>
       </c>
       <c r="B1155">
@@ -35398,7 +35452,7 @@
     </row>
     <row r="1156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1156" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45224.4374537037</v>
       </c>
       <c r="B1156">
@@ -35419,7 +35473,7 @@
     </row>
     <row r="1157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1157" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45228.438310185185</v>
       </c>
       <c r="B1157">
@@ -35440,7 +35494,7 @@
     </row>
     <row r="1158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1158" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45230.420671296299</v>
       </c>
       <c r="B1158">
@@ -35461,7 +35515,7 @@
     </row>
     <row r="1159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1159" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45231.399456018517</v>
       </c>
       <c r="B1159">
@@ -35482,7 +35536,7 @@
     </row>
     <row r="1160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1160" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45232.449456018519</v>
       </c>
       <c r="B1160">
@@ -35503,7 +35557,7 @@
     </row>
     <row r="1161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1161" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45233.452037037037</v>
       </c>
       <c r="B1161">
@@ -35524,7 +35578,7 @@
     </row>
     <row r="1162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1162" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45234.473449074074</v>
       </c>
       <c r="B1162">
@@ -35545,7 +35599,7 @@
     </row>
     <row r="1163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1163" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45235.4687962963</v>
       </c>
       <c r="B1163">
@@ -35566,7 +35620,7 @@
     </row>
     <row r="1164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1164" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45236.464305555557</v>
       </c>
       <c r="B1164">
@@ -35587,7 +35641,7 @@
     </row>
     <row r="1165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1165" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45237.461921296293</v>
       </c>
       <c r="B1165">
@@ -35608,7 +35662,7 @@
     </row>
     <row r="1166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1166" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45238.470775462964</v>
       </c>
       <c r="B1166">
@@ -35629,7 +35683,7 @@
     </row>
     <row r="1167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1167" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>45239.439398148148</v>
       </c>
       <c r="B1167">
@@ -35650,7 +35704,7 @@
     </row>
     <row r="1168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1168" s="10">
-        <f t="shared" ref="A1168:A1231" si="1">DATEVALUE(MID(F1168,5,2) &amp; "-" &amp; LEFT(F1168,3) &amp; "-" &amp; MID(F1168,8,4)) + TIMEVALUE(MID(F1168,13,11))</f>
+        <f t="shared" ref="A1168:A1231" si="13">DATEVALUE(MID(F1168,5,2) &amp; "-" &amp; LEFT(F1168,3) &amp; "-" &amp; MID(F1168,8,4)) + TIMEVALUE(MID(F1168,13,11))</f>
         <v>45240.441284722219</v>
       </c>
       <c r="B1168">
@@ -35671,7 +35725,7 @@
     </row>
     <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1169" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45241.545428240737</v>
       </c>
       <c r="B1169">
@@ -35692,7 +35746,7 @@
     </row>
     <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1170" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45242.529027777775</v>
       </c>
       <c r="B1170">
@@ -35713,7 +35767,7 @@
     </row>
     <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1171" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45243.451793981483</v>
       </c>
       <c r="B1171">
@@ -35734,7 +35788,7 @@
     </row>
     <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1172" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45244.45621527778</v>
       </c>
       <c r="B1172">
@@ -35755,7 +35809,7 @@
     </row>
     <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1173" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45245.506574074076</v>
       </c>
       <c r="B1173">
@@ -35776,7 +35830,7 @@
     </row>
     <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1174" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45246.51363425926</v>
       </c>
       <c r="B1174">
@@ -35797,7 +35851,7 @@
     </row>
     <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1175" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45247.422326388885</v>
       </c>
       <c r="B1175">
@@ -35818,7 +35872,7 @@
     </row>
     <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1176" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45248.41710648148</v>
       </c>
       <c r="B1176">
@@ -35839,7 +35893,7 @@
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1177" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45249.487766203703</v>
       </c>
       <c r="B1177">
@@ -35860,7 +35914,7 @@
     </row>
     <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1178" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45251.407453703701</v>
       </c>
       <c r="B1178">
@@ -35881,7 +35935,7 @@
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1179" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45253.481979166667</v>
       </c>
       <c r="B1179">
@@ -35902,7 +35956,7 @@
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1180" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45256.511331018519</v>
       </c>
       <c r="B1180">
@@ -35923,7 +35977,7 @@
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1181" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45257.50236111111</v>
       </c>
       <c r="B1181">
@@ -35944,7 +35998,7 @@
     </row>
     <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1182" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45258.490590277775</v>
       </c>
       <c r="B1182">
@@ -35965,7 +36019,7 @@
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1183" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45260.408217592594</v>
       </c>
       <c r="B1183">
@@ -35986,7 +36040,7 @@
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1184" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45262.583506944444</v>
       </c>
       <c r="B1184">
@@ -36007,7 +36061,7 @@
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1185" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45263.470868055556</v>
       </c>
       <c r="B1185">
@@ -36028,7 +36082,7 @@
     </row>
     <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1186" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45264.488842592589</v>
       </c>
       <c r="B1186">
@@ -36049,7 +36103,7 @@
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1187" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45265.547164351854</v>
       </c>
       <c r="B1187">
@@ -36070,7 +36124,7 @@
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1188" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45266.466990740744</v>
       </c>
       <c r="B1188">
@@ -36091,7 +36145,7 @@
     </row>
     <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1189" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45269.442418981482</v>
       </c>
       <c r="B1189">
@@ -36112,7 +36166,7 @@
     </row>
     <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1190" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45270.560243055559</v>
       </c>
       <c r="B1190">
@@ -36133,7 +36187,7 @@
     </row>
     <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1191" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45271.484224537038</v>
       </c>
       <c r="B1191">
@@ -36154,7 +36208,7 @@
     </row>
     <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1192" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45272.451770833337</v>
       </c>
       <c r="B1192">
@@ -36175,7 +36229,7 @@
     </row>
     <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1193" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45273.471875000003</v>
       </c>
       <c r="B1193">
@@ -36196,7 +36250,7 @@
     </row>
     <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1194" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45274.484803240739</v>
       </c>
       <c r="B1194">
@@ -36217,7 +36271,7 @@
     </row>
     <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1195" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45275.517384259256</v>
       </c>
       <c r="B1195">
@@ -36238,7 +36292,7 @@
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1196" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45278.486388888887</v>
       </c>
       <c r="B1196">
@@ -36259,7 +36313,7 @@
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1197" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45279.481122685182</v>
       </c>
       <c r="B1197">
@@ -36280,7 +36334,7 @@
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1198" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45286.576585648145</v>
       </c>
       <c r="B1198">
@@ -36301,7 +36355,7 @@
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1199" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45287.511412037034</v>
       </c>
       <c r="B1199">
@@ -36322,7 +36376,7 @@
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1200" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45288.57172453704</v>
       </c>
       <c r="B1200">
@@ -36343,7 +36397,7 @@
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1201" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45290.546898148146</v>
       </c>
       <c r="B1201">
@@ -36364,7 +36418,7 @@
     </row>
     <row r="1202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1202" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45291.559305555558</v>
       </c>
       <c r="B1202">
@@ -36385,7 +36439,7 @@
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1203" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45294.552488425928</v>
       </c>
       <c r="B1203">
@@ -36406,7 +36460,7 @@
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1204" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45295.569837962961</v>
       </c>
       <c r="B1204">
@@ -36427,7 +36481,7 @@
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1205" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45296.460138888891</v>
       </c>
       <c r="B1205">
@@ -36448,7 +36502,7 @@
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1206" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45297.519212962965</v>
       </c>
       <c r="B1206">
@@ -36469,7 +36523,7 @@
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1207" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45298.498043981483</v>
       </c>
       <c r="B1207">
@@ -36490,7 +36544,7 @@
     </row>
     <row r="1208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1208" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45299.537222222221</v>
       </c>
       <c r="B1208">
@@ -36511,7 +36565,7 @@
     </row>
     <row r="1209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1209" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45300.464618055557</v>
       </c>
       <c r="B1209">
@@ -36532,7 +36586,7 @@
     </row>
     <row r="1210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1210" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45301.535104166665</v>
       </c>
       <c r="B1210">
@@ -36553,7 +36607,7 @@
     </row>
     <row r="1211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1211" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45302.546157407407</v>
       </c>
       <c r="B1211">
@@ -36574,7 +36628,7 @@
     </row>
     <row r="1212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1212" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45303.508217592593</v>
       </c>
       <c r="B1212">
@@ -36595,7 +36649,7 @@
     </row>
     <row r="1213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1213" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45304.527673611112</v>
       </c>
       <c r="B1213">
@@ -36616,7 +36670,7 @@
     </row>
     <row r="1214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1214" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45305.50304398148</v>
       </c>
       <c r="B1214">
@@ -36637,7 +36691,7 @@
     </row>
     <row r="1215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1215" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45306.511770833335</v>
       </c>
       <c r="B1215">
@@ -36658,7 +36712,7 @@
     </row>
     <row r="1216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1216" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45307.511597222219</v>
       </c>
       <c r="B1216">
@@ -36679,7 +36733,7 @@
     </row>
     <row r="1217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1217" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45308.508981481478</v>
       </c>
       <c r="B1217">
@@ -36700,7 +36754,7 @@
     </row>
     <row r="1218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1218" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45309.513958333337</v>
       </c>
       <c r="B1218">
@@ -36721,7 +36775,7 @@
     </row>
     <row r="1219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1219" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45310.514293981483</v>
       </c>
       <c r="B1219">
@@ -36742,7 +36796,7 @@
     </row>
     <row r="1220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1220" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45311.538148148145</v>
       </c>
       <c r="B1220">
@@ -36763,7 +36817,7 @@
     </row>
     <row r="1221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1221" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45312.526828703703</v>
       </c>
       <c r="B1221">
@@ -36784,7 +36838,7 @@
     </row>
     <row r="1222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1222" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45313.511481481481</v>
       </c>
       <c r="B1222">
@@ -36805,7 +36859,7 @@
     </row>
     <row r="1223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1223" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45314.491122685184</v>
       </c>
       <c r="B1223">
@@ -36826,7 +36880,7 @@
     </row>
     <row r="1224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1224" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45315.512615740743</v>
       </c>
       <c r="B1224">
@@ -36847,7 +36901,7 @@
     </row>
     <row r="1225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1225" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45316.419571759259</v>
       </c>
       <c r="B1225">
@@ -36868,7 +36922,7 @@
     </row>
     <row r="1226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1226" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45317.502615740741</v>
       </c>
       <c r="B1226">
@@ -36889,7 +36943,7 @@
     </row>
     <row r="1227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1227" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45318.498912037037</v>
       </c>
       <c r="B1227">
@@ -36910,7 +36964,7 @@
     </row>
     <row r="1228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1228" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45319.512071759258</v>
       </c>
       <c r="B1228">
@@ -36931,7 +36985,7 @@
     </row>
     <row r="1229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1229" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45320.506249999999</v>
       </c>
       <c r="B1229">
@@ -36952,7 +37006,7 @@
     </row>
     <row r="1230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1230" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45321.456342592595</v>
       </c>
       <c r="B1230">
@@ -36973,7 +37027,7 @@
     </row>
     <row r="1231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1231" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45323.379675925928</v>
       </c>
       <c r="B1231">
@@ -36994,7 +37048,7 @@
     </row>
     <row r="1232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1232" s="10">
-        <f t="shared" ref="A1232:A1295" si="2">DATEVALUE(MID(F1232,5,2) &amp; "-" &amp; LEFT(F1232,3) &amp; "-" &amp; MID(F1232,8,4)) + TIMEVALUE(MID(F1232,13,11))</f>
+        <f t="shared" ref="A1232:A1295" si="14">DATEVALUE(MID(F1232,5,2) &amp; "-" &amp; LEFT(F1232,3) &amp; "-" &amp; MID(F1232,8,4)) + TIMEVALUE(MID(F1232,13,11))</f>
         <v>45324.481828703705</v>
       </c>
       <c r="B1232">
@@ -37015,7 +37069,7 @@
     </row>
     <row r="1233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1233" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45325.508252314816</v>
       </c>
       <c r="B1233">
@@ -37036,7 +37090,7 @@
     </row>
     <row r="1234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1234" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45325.511053240742</v>
       </c>
       <c r="B1234">
@@ -37057,7 +37111,7 @@
     </row>
     <row r="1235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1235" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45326.526469907411</v>
       </c>
       <c r="B1235">
@@ -37078,7 +37132,7 @@
     </row>
     <row r="1236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1236" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45327.48265046296</v>
       </c>
       <c r="B1236">
@@ -37099,7 +37153,7 @@
     </row>
     <row r="1237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1237" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45328.516435185185</v>
       </c>
       <c r="B1237">
@@ -37120,7 +37174,7 @@
     </row>
     <row r="1238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1238" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45330.496099537035</v>
       </c>
       <c r="B1238">
@@ -37141,7 +37195,7 @@
     </row>
     <row r="1239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1239" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45331.531018518515</v>
       </c>
       <c r="B1239">
@@ -37162,7 +37216,7 @@
     </row>
     <row r="1240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1240" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45332.521539351852</v>
       </c>
       <c r="B1240">
@@ -37183,7 +37237,7 @@
     </row>
     <row r="1241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1241" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45333.513240740744</v>
       </c>
       <c r="B1241">
@@ -37204,7 +37258,7 @@
     </row>
     <row r="1242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1242" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45334.498460648145</v>
       </c>
       <c r="B1242">
@@ -37225,7 +37279,7 @@
     </row>
     <row r="1243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1243" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45335.519131944442</v>
       </c>
       <c r="B1243">
@@ -37246,7 +37300,7 @@
     </row>
     <row r="1244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1244" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45336.534456018519</v>
       </c>
       <c r="B1244">
@@ -37267,7 +37321,7 @@
     </row>
     <row r="1245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1245" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45337.510312500002</v>
       </c>
       <c r="B1245">
@@ -37288,7 +37342,7 @@
     </row>
     <row r="1246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1246" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45338.51457175926</v>
       </c>
       <c r="B1246">
@@ -37309,7 +37363,7 @@
     </row>
     <row r="1247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1247" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45339.536076388889</v>
       </c>
       <c r="B1247">
@@ -37330,7 +37384,7 @@
     </row>
     <row r="1248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1248" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45340.542048611111</v>
       </c>
       <c r="B1248">
@@ -37351,7 +37405,7 @@
     </row>
     <row r="1249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1249" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45341.513159722221</v>
       </c>
       <c r="B1249">
@@ -37372,7 +37426,7 @@
     </row>
     <row r="1250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1250" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45342.493402777778</v>
       </c>
       <c r="B1250">
@@ -37393,7 +37447,7 @@
     </row>
     <row r="1251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1251" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45343.524305555555</v>
       </c>
       <c r="B1251">
@@ -37414,7 +37468,7 @@
     </row>
     <row r="1252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1252" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45344.518055555556</v>
       </c>
       <c r="B1252">
@@ -37435,7 +37489,7 @@
     </row>
     <row r="1253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1253" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45345.514884259261</v>
       </c>
       <c r="B1253">
@@ -37456,7 +37510,7 @@
     </row>
     <row r="1254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1254" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45346.506273148145</v>
       </c>
       <c r="B1254">
@@ -37477,7 +37531,7 @@
     </row>
     <row r="1255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1255" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45347.533252314817</v>
       </c>
       <c r="B1255">
@@ -37498,7 +37552,7 @@
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1256" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45348.504062499997</v>
       </c>
       <c r="B1256">
@@ -37519,7 +37573,7 @@
     </row>
     <row r="1257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1257" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45349.510555555556</v>
       </c>
       <c r="B1257">
@@ -37540,7 +37594,7 @@
     </row>
     <row r="1258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1258" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45350.451840277776</v>
       </c>
       <c r="B1258">
@@ -37561,7 +37615,7 @@
     </row>
     <row r="1259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1259" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45351.49900462963</v>
       </c>
       <c r="B1259">
@@ -37582,7 +37636,7 @@
     </row>
     <row r="1260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1260" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45352.505567129629</v>
       </c>
       <c r="B1260">
@@ -37603,7 +37657,7 @@
     </row>
     <row r="1261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1261" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45353.478715277779</v>
       </c>
       <c r="B1261">
@@ -37624,7 +37678,7 @@
     </row>
     <row r="1262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1262" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45354.539143518516</v>
       </c>
       <c r="B1262">
@@ -37645,7 +37699,7 @@
     </row>
     <row r="1263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1263" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45355.470555555556</v>
       </c>
       <c r="B1263">
@@ -37666,7 +37720,7 @@
     </row>
     <row r="1264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1264" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45356.453194444446</v>
       </c>
       <c r="B1264">
@@ -37687,7 +37741,7 @@
     </row>
     <row r="1265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1265" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45357.481192129628</v>
       </c>
       <c r="B1265">
@@ -37708,7 +37762,7 @@
     </row>
     <row r="1266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1266" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45357.490173611113</v>
       </c>
       <c r="B1266">
@@ -37729,7 +37783,7 @@
     </row>
     <row r="1267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1267" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45358.45621527778</v>
       </c>
       <c r="B1267">
@@ -37750,7 +37804,7 @@
     </row>
     <row r="1268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1268" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45359.488368055558</v>
       </c>
       <c r="B1268">
@@ -37771,7 +37825,7 @@
     </row>
     <row r="1269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1269" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45360.463969907411</v>
       </c>
       <c r="B1269">
@@ -37792,7 +37846,7 @@
     </row>
     <row r="1270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1270" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45361.444884259261</v>
       </c>
       <c r="B1270">
@@ -37813,7 +37867,7 @@
     </row>
     <row r="1271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1271" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45362.426226851851</v>
       </c>
       <c r="B1271">
@@ -37834,7 +37888,7 @@
     </row>
     <row r="1272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1272" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45363.451817129629</v>
       </c>
       <c r="B1272">
@@ -37855,7 +37909,7 @@
     </row>
     <row r="1273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1273" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45364.42260416667</v>
       </c>
       <c r="B1273">
@@ -37876,7 +37930,7 @@
     </row>
     <row r="1274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1274" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45365.415439814817</v>
       </c>
       <c r="B1274">
@@ -37897,7 +37951,7 @@
     </row>
     <row r="1275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1275" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45367.452048611114</v>
       </c>
       <c r="B1275">
@@ -37918,7 +37972,7 @@
     </row>
     <row r="1276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1276" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45368.419918981483</v>
       </c>
       <c r="B1276">
@@ -37939,7 +37993,7 @@
     </row>
     <row r="1277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1277" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45369.412905092591</v>
       </c>
       <c r="B1277">
@@ -37960,7 +38014,7 @@
     </row>
     <row r="1278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1278" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45370.4452662037</v>
       </c>
       <c r="B1278">
@@ -37981,7 +38035,7 @@
     </row>
     <row r="1279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1279" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45371.433229166665</v>
       </c>
       <c r="B1279">
@@ -38002,7 +38056,7 @@
     </row>
     <row r="1280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1280" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45372.459629629629</v>
       </c>
       <c r="B1280">
@@ -38023,7 +38077,7 @@
     </row>
     <row r="1281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1281" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45373.452291666668</v>
       </c>
       <c r="B1281">
@@ -38044,7 +38098,7 @@
     </row>
     <row r="1282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1282" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45374.430891203701</v>
       </c>
       <c r="B1282">
@@ -38065,7 +38119,7 @@
     </row>
     <row r="1283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1283" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45375.436354166668</v>
       </c>
       <c r="B1283">
@@ -38086,7 +38140,7 @@
     </row>
     <row r="1284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1284" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45376.470682870371</v>
       </c>
       <c r="B1284">
@@ -38107,7 +38161,7 @@
     </row>
     <row r="1285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1285" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45377.429444444446</v>
       </c>
       <c r="B1285">
@@ -38128,7 +38182,7 @@
     </row>
     <row r="1286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1286" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45378.481932870367</v>
       </c>
       <c r="B1286">
@@ -38149,7 +38203,7 @@
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1287" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45379.451307870368</v>
       </c>
       <c r="B1287">
@@ -38170,7 +38224,7 @@
     </row>
     <row r="1288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1288" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45380.427453703705</v>
       </c>
       <c r="B1288">
@@ -38191,7 +38245,7 @@
     </row>
     <row r="1289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1289" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45381.454884259256</v>
       </c>
       <c r="B1289">
@@ -38212,7 +38266,7 @@
     </row>
     <row r="1290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1290" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45382.476018518515</v>
       </c>
       <c r="B1290">
@@ -38233,7 +38287,7 @@
     </row>
     <row r="1291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1291" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45383.409074074072</v>
       </c>
       <c r="B1291">
@@ -38254,7 +38308,7 @@
     </row>
     <row r="1292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1292" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45384.431087962963</v>
       </c>
       <c r="B1292">
@@ -38275,7 +38329,7 @@
     </row>
     <row r="1293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1293" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45385.447384259256</v>
       </c>
       <c r="B1293">
@@ -38296,7 +38350,7 @@
     </row>
     <row r="1294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1294" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45386.433703703704</v>
       </c>
       <c r="B1294">
@@ -38317,7 +38371,7 @@
     </row>
     <row r="1295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1295" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>45387.354583333334</v>
       </c>
       <c r="B1295">
@@ -38338,7 +38392,7 @@
     </row>
     <row r="1296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1296" s="10">
-        <f t="shared" ref="A1296:A1359" si="3">DATEVALUE(MID(F1296,5,2) &amp; "-" &amp; LEFT(F1296,3) &amp; "-" &amp; MID(F1296,8,4)) + TIMEVALUE(MID(F1296,13,11))</f>
+        <f t="shared" ref="A1296:A1359" si="15">DATEVALUE(MID(F1296,5,2) &amp; "-" &amp; LEFT(F1296,3) &amp; "-" &amp; MID(F1296,8,4)) + TIMEVALUE(MID(F1296,13,11))</f>
         <v>45388.416932870372</v>
       </c>
       <c r="B1296">
@@ -38359,7 +38413,7 @@
     </row>
     <row r="1297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1297" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45388.460196759261</v>
       </c>
       <c r="B1297">
@@ -38380,7 +38434,7 @@
     </row>
     <row r="1298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1298" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45389.352268518516</v>
       </c>
       <c r="B1298">
@@ -38401,7 +38455,7 @@
     </row>
     <row r="1299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1299" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45389.378437500003</v>
       </c>
       <c r="B1299">
@@ -38422,7 +38476,7 @@
     </row>
     <row r="1300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1300" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45390.414699074077</v>
       </c>
       <c r="B1300">
@@ -38443,7 +38497,7 @@
     </row>
     <row r="1301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1301" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45391.377071759256</v>
       </c>
       <c r="B1301">
@@ -38464,7 +38518,7 @@
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1302" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45392.435243055559</v>
       </c>
       <c r="B1302">
@@ -38485,7 +38539,7 @@
     </row>
     <row r="1303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1303" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45393.452210648145</v>
       </c>
       <c r="B1303">
@@ -38506,7 +38560,7 @@
     </row>
     <row r="1304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1304" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45394.415983796294</v>
       </c>
       <c r="B1304">
@@ -38527,7 +38581,7 @@
     </row>
     <row r="1305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1305" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45399.445196759261</v>
       </c>
       <c r="B1305">
@@ -38548,7 +38602,7 @@
     </row>
     <row r="1306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1306" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45400.455590277779</v>
       </c>
       <c r="B1306">
@@ -38569,7 +38623,7 @@
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1307" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45401.452627314815</v>
       </c>
       <c r="B1307">
@@ -38590,7 +38644,7 @@
     </row>
     <row r="1308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1308" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45404.457662037035</v>
       </c>
       <c r="B1308">
@@ -38611,7 +38665,7 @@
     </row>
     <row r="1309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1309" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45405.456203703703</v>
       </c>
       <c r="B1309">
@@ -38632,7 +38686,7 @@
     </row>
     <row r="1310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1310" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45406.460810185185</v>
       </c>
       <c r="B1310">
@@ -38653,7 +38707,7 @@
     </row>
     <row r="1311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1311" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45407.478402777779</v>
       </c>
       <c r="B1311">
@@ -38674,7 +38728,7 @@
     </row>
     <row r="1312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1312" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45411.411446759259</v>
       </c>
       <c r="B1312">
@@ -38695,7 +38749,7 @@
     </row>
     <row r="1313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1313" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45413.434502314813</v>
       </c>
       <c r="B1313">
@@ -38716,7 +38770,7 @@
     </row>
     <row r="1314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1314" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45414.443437499998</v>
       </c>
       <c r="B1314">
@@ -38737,7 +38791,7 @@
     </row>
     <row r="1315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1315" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45415.431284722225</v>
       </c>
       <c r="B1315">
@@ -38758,7 +38812,7 @@
     </row>
     <row r="1316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1316" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45417.406770833331</v>
       </c>
       <c r="B1316">
@@ -38779,7 +38833,7 @@
     </row>
     <row r="1317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1317" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45420.452962962961</v>
       </c>
       <c r="B1317">
@@ -38800,7 +38854,7 @@
     </row>
     <row r="1318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1318" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45429.371655092589</v>
       </c>
       <c r="B1318">
@@ -38821,7 +38875,7 @@
     </row>
     <row r="1319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1319" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45435.426736111112</v>
       </c>
       <c r="B1319">
@@ -38842,7 +38896,7 @@
     </row>
     <row r="1320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1320" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45436.467638888891</v>
       </c>
       <c r="B1320">
@@ -38863,7 +38917,7 @@
     </row>
     <row r="1321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1321" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45437.489039351851</v>
       </c>
       <c r="B1321">
@@ -38884,7 +38938,7 @@
     </row>
     <row r="1322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1322" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45438.467650462961</v>
       </c>
       <c r="B1322">
@@ -38905,7 +38959,7 @@
     </row>
     <row r="1323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1323" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45439.415763888886</v>
       </c>
       <c r="B1323">
@@ -38926,7 +38980,7 @@
     </row>
     <row r="1324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1324" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45441.442881944444</v>
       </c>
       <c r="B1324">
@@ -38947,7 +39001,7 @@
     </row>
     <row r="1325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1325" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45442.404039351852</v>
       </c>
       <c r="B1325">
@@ -38968,7 +39022,7 @@
     </row>
     <row r="1326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1326" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45443.406886574077</v>
       </c>
       <c r="B1326">
@@ -38989,7 +39043,7 @@
     </row>
     <row r="1327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1327" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45444.462916666664</v>
       </c>
       <c r="B1327">
@@ -39010,7 +39064,7 @@
     </row>
     <row r="1328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1328" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45445.491759259261</v>
       </c>
       <c r="B1328">
@@ -39031,7 +39085,7 @@
     </row>
     <row r="1329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1329" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45446.446018518516</v>
       </c>
       <c r="B1329">
@@ -39052,7 +39106,7 @@
     </row>
     <row r="1330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1330" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45447.431157407409</v>
       </c>
       <c r="B1330">
@@ -39073,7 +39127,7 @@
     </row>
     <row r="1331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1331" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45450.454571759263</v>
       </c>
       <c r="B1331">
@@ -39094,7 +39148,7 @@
     </row>
     <row r="1332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1332" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45453.480046296296</v>
       </c>
       <c r="B1332">
@@ -39115,7 +39169,7 @@
     </row>
     <row r="1333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1333" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45454.454942129632</v>
       </c>
       <c r="B1333">
@@ -39136,7 +39190,7 @@
     </row>
     <row r="1334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1334" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45456.411851851852</v>
       </c>
       <c r="B1334">
@@ -39157,7 +39211,7 @@
     </row>
     <row r="1335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1335" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45457.481087962966</v>
       </c>
       <c r="B1335">
@@ -39178,7 +39232,7 @@
     </row>
     <row r="1336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1336" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45458.480034722219</v>
       </c>
       <c r="B1336">
@@ -39199,7 +39253,7 @@
     </row>
     <row r="1337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1337" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45460.437835648147</v>
       </c>
       <c r="B1337">
@@ -39220,7 +39274,7 @@
     </row>
     <row r="1338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1338" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45461.440752314818</v>
       </c>
       <c r="B1338">
@@ -39241,7 +39295,7 @@
     </row>
     <row r="1339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1339" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45462.408888888887</v>
       </c>
       <c r="B1339">
@@ -39262,7 +39316,7 @@
     </row>
     <row r="1340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1340" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45463.419270833336</v>
       </c>
       <c r="B1340">
@@ -39283,7 +39337,7 @@
     </row>
     <row r="1341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1341" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45467.426041666666</v>
       </c>
       <c r="B1341">
@@ -39304,7 +39358,7 @@
     </row>
     <row r="1342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1342" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45469.440555555557</v>
       </c>
       <c r="B1342">
@@ -39325,7 +39379,7 @@
     </row>
     <row r="1343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1343" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45470.41679398148</v>
       </c>
       <c r="B1343">
@@ -39346,7 +39400,7 @@
     </row>
     <row r="1344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1344" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45471.411354166667</v>
       </c>
       <c r="B1344">
@@ -39367,7 +39421,7 @@
     </row>
     <row r="1345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1345" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45474.46371527778</v>
       </c>
       <c r="B1345">
@@ -39388,7 +39442,7 @@
     </row>
     <row r="1346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1346" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45475.431898148148</v>
       </c>
       <c r="B1346">
@@ -39409,7 +39463,7 @@
     </row>
     <row r="1347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1347" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45476.446284722224</v>
       </c>
       <c r="B1347">
@@ -39430,7 +39484,7 @@
     </row>
     <row r="1348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1348" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45477.457511574074</v>
       </c>
       <c r="B1348">
@@ -39451,7 +39505,7 @@
     </row>
     <row r="1349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1349" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45479.469814814816</v>
       </c>
       <c r="B1349">
@@ -39472,7 +39526,7 @@
     </row>
     <row r="1350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1350" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45481.438263888886</v>
       </c>
       <c r="B1350">
@@ -39493,7 +39547,7 @@
     </row>
     <row r="1351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1351" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45481.438263888886</v>
       </c>
       <c r="B1351">
@@ -39514,7 +39568,7 @@
     </row>
     <row r="1352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1352" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45482.444143518522</v>
       </c>
       <c r="B1352">
@@ -39535,7 +39589,7 @@
     </row>
     <row r="1353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1353" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45483.414120370369</v>
       </c>
       <c r="B1353">
@@ -39556,7 +39610,7 @@
     </row>
     <row r="1354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1354" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45484.407476851855</v>
       </c>
       <c r="B1354">
@@ -39577,7 +39631,7 @@
     </row>
     <row r="1355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1355" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45492.462418981479</v>
       </c>
       <c r="B1355">
@@ -39598,7 +39652,7 @@
     </row>
     <row r="1356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1356" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45494.453553240739</v>
       </c>
       <c r="B1356">
@@ -39619,7 +39673,7 @@
     </row>
     <row r="1357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1357" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45495.448657407411</v>
       </c>
       <c r="B1357">
@@ -39640,7 +39694,7 @@
     </row>
     <row r="1358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1358" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45496.42396990741</v>
       </c>
       <c r="B1358">
@@ -39661,7 +39715,7 @@
     </row>
     <row r="1359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1359" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>45497.442939814813</v>
       </c>
       <c r="B1359">
@@ -39682,7 +39736,7 @@
     </row>
     <row r="1360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1360" s="10">
-        <f t="shared" ref="A1360:A1393" si="4">DATEVALUE(MID(F1360,5,2) &amp; "-" &amp; LEFT(F1360,3) &amp; "-" &amp; MID(F1360,8,4)) + TIMEVALUE(MID(F1360,13,11))</f>
+        <f t="shared" ref="A1360:A1393" si="16">DATEVALUE(MID(F1360,5,2) &amp; "-" &amp; LEFT(F1360,3) &amp; "-" &amp; MID(F1360,8,4)) + TIMEVALUE(MID(F1360,13,11))</f>
         <v>45498.484479166669</v>
       </c>
       <c r="B1360">
@@ -39703,7 +39757,7 @@
     </row>
     <row r="1361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1361" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45499.453634259262</v>
       </c>
       <c r="B1361">
@@ -39724,7 +39778,7 @@
     </row>
     <row r="1362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1362" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45500.472013888888</v>
       </c>
       <c r="B1362">
@@ -39745,7 +39799,7 @@
     </row>
     <row r="1363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1363" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45501.483854166669</v>
       </c>
       <c r="B1363">
@@ -39766,7 +39820,7 @@
     </row>
     <row r="1364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1364" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45502.425717592596</v>
       </c>
       <c r="B1364">
@@ -39787,7 +39841,7 @@
     </row>
     <row r="1365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1365" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45502.446759259263</v>
       </c>
       <c r="B1365">
@@ -39808,7 +39862,7 @@
     </row>
     <row r="1366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1366" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45503.452662037038</v>
       </c>
       <c r="B1366">
@@ -39829,7 +39883,7 @@
     </row>
     <row r="1367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1367" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45504.452824074076</v>
       </c>
       <c r="B1367">
@@ -39850,7 +39904,7 @@
     </row>
     <row r="1368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1368" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45505.443738425929</v>
       </c>
       <c r="B1368">
@@ -39871,7 +39925,7 @@
     </row>
     <row r="1369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1369" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45506.467303240737</v>
       </c>
       <c r="B1369">
@@ -39892,7 +39946,7 @@
     </row>
     <row r="1370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1370" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45507.493101851855</v>
       </c>
       <c r="B1370">
@@ -39913,7 +39967,7 @@
     </row>
     <row r="1371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1371" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45508.471562500003</v>
       </c>
       <c r="B1371">
@@ -39934,7 +39988,7 @@
     </row>
     <row r="1372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1372" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45509.439652777779</v>
       </c>
       <c r="B1372">
@@ -39955,7 +40009,7 @@
     </row>
     <row r="1373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1373" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45510.378078703703</v>
       </c>
       <c r="B1373">
@@ -39976,7 +40030,7 @@
     </row>
     <row r="1374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1374" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45511.470069444447</v>
       </c>
       <c r="B1374">
@@ -39997,7 +40051,7 @@
     </row>
     <row r="1375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1375" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45512.475914351853</v>
       </c>
       <c r="B1375">
@@ -40018,7 +40072,7 @@
     </row>
     <row r="1376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1376" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45513.445879629631</v>
       </c>
       <c r="B1376">
@@ -40039,7 +40093,7 @@
     </row>
     <row r="1377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1377" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45517.441793981481</v>
       </c>
       <c r="B1377">
@@ -40060,7 +40114,7 @@
     </row>
     <row r="1378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1378" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45518.471388888887</v>
       </c>
       <c r="B1378">
@@ -40081,7 +40135,7 @@
     </row>
     <row r="1379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1379" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45534.403356481482</v>
       </c>
       <c r="B1379">
@@ -40102,7 +40156,7 @@
     </row>
     <row r="1380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1380" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45543.462870370371</v>
       </c>
       <c r="B1380">
@@ -40123,7 +40177,7 @@
     </row>
     <row r="1381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1381" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45544.427523148152</v>
       </c>
       <c r="B1381">
@@ -40144,7 +40198,7 @@
     </row>
     <row r="1382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1382" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45545.460370370369</v>
       </c>
       <c r="B1382">
@@ -40165,7 +40219,7 @@
     </row>
     <row r="1383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1383" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45546.46366898148</v>
       </c>
       <c r="B1383">
@@ -40186,7 +40240,7 @@
     </row>
     <row r="1384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1384" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45548.44462962963</v>
       </c>
       <c r="B1384">
@@ -40207,7 +40261,7 @@
     </row>
     <row r="1385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1385" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45551.457604166666</v>
       </c>
       <c r="B1385">
@@ -40228,7 +40282,7 @@
     </row>
     <row r="1386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1386" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45553.482476851852</v>
       </c>
       <c r="B1386">
@@ -40249,7 +40303,7 @@
     </row>
     <row r="1387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1387" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45554.451527777775</v>
       </c>
       <c r="B1387">
@@ -40270,7 +40324,7 @@
     </row>
     <row r="1388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1388" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45555.424351851849</v>
       </c>
       <c r="B1388">
@@ -40291,7 +40345,7 @@
     </row>
     <row r="1389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1389" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45556.483217592591</v>
       </c>
       <c r="B1389">
@@ -40312,7 +40366,7 @@
     </row>
     <row r="1390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1390" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45557.494016203702</v>
       </c>
       <c r="B1390">
@@ -40333,7 +40387,7 @@
     </row>
     <row r="1391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1391" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45558.414004629631</v>
       </c>
       <c r="B1391">
@@ -40354,7 +40408,7 @@
     </row>
     <row r="1392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1392" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45559.450532407405</v>
       </c>
       <c r="B1392">
@@ -40375,7 +40429,7 @@
     </row>
     <row r="1393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1393" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>45560.453634259262</v>
       </c>
       <c r="B1393">
@@ -40392,6 +40446,78 @@
       </c>
       <c r="F1393" t="s">
         <v>1045</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1394" s="8">
+        <v>45561</v>
+      </c>
+      <c r="B1394">
+        <v>226.3</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1395" s="8">
+        <v>45562</v>
+      </c>
+      <c r="B1395">
+        <v>226.3</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1396" s="8">
+        <v>45563</v>
+      </c>
+      <c r="B1396">
+        <v>226.1</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1397" s="8">
+        <v>45564</v>
+      </c>
+      <c r="B1397">
+        <v>227.1</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1398" s="8">
+        <v>45565</v>
+      </c>
+      <c r="B1398">
+        <v>226.7</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1399" s="8">
+        <v>45566</v>
+      </c>
+      <c r="B1399">
+        <v>226.2</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1400" s="8">
+        <v>45567</v>
+      </c>
+      <c r="B1400">
+        <v>226.3</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1401" s="8">
+        <v>45574</v>
+      </c>
+      <c r="B1401">
+        <v>227.8</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1402" s="8">
+        <v>45575</v>
+      </c>
+      <c r="B1402">
+        <v>225.9</v>
       </c>
     </row>
   </sheetData>

--- a/weight/bathroom-scale.xlsx
+++ b/weight/bathroom-scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\lucent\health-data\weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029A4F5-1BCB-4286-AC3C-3F8CAC99E77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2483DDAB-1029-43E1-BA0C-26CA3C341E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15375" yWindow="4290" windowWidth="32940" windowHeight="16185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="weight" sheetId="1" r:id="rId1"/>
@@ -3674,7 +3674,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3689,6 +3689,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3825,10 +3826,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>weight!$A$2:$A$1402</c:f>
+              <c:f>weight!$A$2:$A$1506</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1401"/>
+                <c:ptCount val="1505"/>
                 <c:pt idx="0">
                   <c:v>36297</c:v>
                 </c:pt>
@@ -8031,16 +8032,328 @@
                 </c:pt>
                 <c:pt idx="1400">
                   <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="1401">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="1402">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="1403">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="1404">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="1405">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="1406">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="1407" formatCode="m/d/yyyy">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="1408" formatCode="m/d/yyyy">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="1409" formatCode="m/d/yyyy">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="1410" formatCode="m/d/yyyy">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="1411" formatCode="m/d/yyyy">
+                  <c:v>45588</c:v>
+                </c:pt>
+                <c:pt idx="1412" formatCode="m/d/yyyy">
+                  <c:v>45589</c:v>
+                </c:pt>
+                <c:pt idx="1413" formatCode="m/d/yyyy">
+                  <c:v>45590</c:v>
+                </c:pt>
+                <c:pt idx="1414" formatCode="m/d/yyyy">
+                  <c:v>45591</c:v>
+                </c:pt>
+                <c:pt idx="1415" formatCode="m/d/yyyy">
+                  <c:v>45592</c:v>
+                </c:pt>
+                <c:pt idx="1416" formatCode="m/d/yyyy">
+                  <c:v>45593</c:v>
+                </c:pt>
+                <c:pt idx="1417" formatCode="m/d/yyyy">
+                  <c:v>45594</c:v>
+                </c:pt>
+                <c:pt idx="1418" formatCode="m/d/yyyy">
+                  <c:v>45595</c:v>
+                </c:pt>
+                <c:pt idx="1419" formatCode="m/d/yyyy">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="1420" formatCode="m/d/yyyy">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="1421" formatCode="m/d/yyyy">
+                  <c:v>45598</c:v>
+                </c:pt>
+                <c:pt idx="1422" formatCode="m/d/yyyy">
+                  <c:v>45599</c:v>
+                </c:pt>
+                <c:pt idx="1423" formatCode="m/d/yyyy">
+                  <c:v>45599</c:v>
+                </c:pt>
+                <c:pt idx="1424" formatCode="m/d/yyyy">
+                  <c:v>45600</c:v>
+                </c:pt>
+                <c:pt idx="1425" formatCode="m/d/yyyy">
+                  <c:v>45601</c:v>
+                </c:pt>
+                <c:pt idx="1426" formatCode="m/d/yyyy">
+                  <c:v>45602</c:v>
+                </c:pt>
+                <c:pt idx="1427" formatCode="m/d/yyyy">
+                  <c:v>45603</c:v>
+                </c:pt>
+                <c:pt idx="1428" formatCode="m/d/yyyy">
+                  <c:v>45604</c:v>
+                </c:pt>
+                <c:pt idx="1429" formatCode="m/d/yyyy">
+                  <c:v>45605</c:v>
+                </c:pt>
+                <c:pt idx="1430" formatCode="m/d/yyyy">
+                  <c:v>45606</c:v>
+                </c:pt>
+                <c:pt idx="1431" formatCode="m/d/yyyy">
+                  <c:v>45607</c:v>
+                </c:pt>
+                <c:pt idx="1432" formatCode="m/d/yyyy">
+                  <c:v>45610</c:v>
+                </c:pt>
+                <c:pt idx="1433" formatCode="m/d/yyyy">
+                  <c:v>45610</c:v>
+                </c:pt>
+                <c:pt idx="1434" formatCode="m/d/yyyy">
+                  <c:v>45610</c:v>
+                </c:pt>
+                <c:pt idx="1435" formatCode="m/d/yyyy">
+                  <c:v>45611</c:v>
+                </c:pt>
+                <c:pt idx="1436" formatCode="m/d/yyyy">
+                  <c:v>45612</c:v>
+                </c:pt>
+                <c:pt idx="1437" formatCode="m/d/yyyy">
+                  <c:v>45613</c:v>
+                </c:pt>
+                <c:pt idx="1438" formatCode="m/d/yyyy">
+                  <c:v>45615</c:v>
+                </c:pt>
+                <c:pt idx="1439" formatCode="m/d/yyyy">
+                  <c:v>45616</c:v>
+                </c:pt>
+                <c:pt idx="1440" formatCode="m/d/yyyy">
+                  <c:v>45617</c:v>
+                </c:pt>
+                <c:pt idx="1441" formatCode="m/d/yyyy">
+                  <c:v>45618</c:v>
+                </c:pt>
+                <c:pt idx="1442" formatCode="m/d/yyyy">
+                  <c:v>45619</c:v>
+                </c:pt>
+                <c:pt idx="1443" formatCode="m/d/yyyy">
+                  <c:v>45619</c:v>
+                </c:pt>
+                <c:pt idx="1444" formatCode="m/d/yyyy">
+                  <c:v>45620</c:v>
+                </c:pt>
+                <c:pt idx="1445" formatCode="m/d/yyyy">
+                  <c:v>45621</c:v>
+                </c:pt>
+                <c:pt idx="1446" formatCode="m/d/yyyy">
+                  <c:v>45622</c:v>
+                </c:pt>
+                <c:pt idx="1447" formatCode="m/d/yyyy">
+                  <c:v>45628</c:v>
+                </c:pt>
+                <c:pt idx="1448" formatCode="m/d/yyyy">
+                  <c:v>45629</c:v>
+                </c:pt>
+                <c:pt idx="1449" formatCode="m/d/yyyy">
+                  <c:v>45630</c:v>
+                </c:pt>
+                <c:pt idx="1450" formatCode="m/d/yyyy">
+                  <c:v>45631</c:v>
+                </c:pt>
+                <c:pt idx="1451" formatCode="m/d/yyyy">
+                  <c:v>45632</c:v>
+                </c:pt>
+                <c:pt idx="1452" formatCode="m/d/yyyy">
+                  <c:v>45633</c:v>
+                </c:pt>
+                <c:pt idx="1453" formatCode="m/d/yyyy">
+                  <c:v>45634</c:v>
+                </c:pt>
+                <c:pt idx="1454" formatCode="m/d/yyyy">
+                  <c:v>45635</c:v>
+                </c:pt>
+                <c:pt idx="1455" formatCode="m/d/yyyy">
+                  <c:v>45636</c:v>
+                </c:pt>
+                <c:pt idx="1456" formatCode="m/d/yyyy">
+                  <c:v>45637</c:v>
+                </c:pt>
+                <c:pt idx="1457" formatCode="m/d/yyyy">
+                  <c:v>45638</c:v>
+                </c:pt>
+                <c:pt idx="1458" formatCode="m/d/yyyy">
+                  <c:v>45639</c:v>
+                </c:pt>
+                <c:pt idx="1459" formatCode="m/d/yyyy">
+                  <c:v>45640</c:v>
+                </c:pt>
+                <c:pt idx="1460" formatCode="m/d/yyyy">
+                  <c:v>45641</c:v>
+                </c:pt>
+                <c:pt idx="1461" formatCode="m/d/yyyy">
+                  <c:v>45642</c:v>
+                </c:pt>
+                <c:pt idx="1462" formatCode="m/d/yyyy">
+                  <c:v>45643</c:v>
+                </c:pt>
+                <c:pt idx="1463" formatCode="m/d/yyyy">
+                  <c:v>45653</c:v>
+                </c:pt>
+                <c:pt idx="1464" formatCode="m/d/yyyy">
+                  <c:v>45654</c:v>
+                </c:pt>
+                <c:pt idx="1465" formatCode="m/d/yyyy">
+                  <c:v>45655</c:v>
+                </c:pt>
+                <c:pt idx="1466" formatCode="m/d/yyyy">
+                  <c:v>45656</c:v>
+                </c:pt>
+                <c:pt idx="1467" formatCode="m/d/yyyy">
+                  <c:v>45657</c:v>
+                </c:pt>
+                <c:pt idx="1468" formatCode="m/d/yyyy">
+                  <c:v>45659</c:v>
+                </c:pt>
+                <c:pt idx="1469" formatCode="m/d/yyyy">
+                  <c:v>45660</c:v>
+                </c:pt>
+                <c:pt idx="1470" formatCode="m/d/yyyy">
+                  <c:v>45661</c:v>
+                </c:pt>
+                <c:pt idx="1471" formatCode="m/d/yyyy">
+                  <c:v>45662</c:v>
+                </c:pt>
+                <c:pt idx="1472" formatCode="m/d/yyyy">
+                  <c:v>45663</c:v>
+                </c:pt>
+                <c:pt idx="1473" formatCode="m/d/yyyy">
+                  <c:v>45664</c:v>
+                </c:pt>
+                <c:pt idx="1474" formatCode="m/d/yyyy">
+                  <c:v>45665</c:v>
+                </c:pt>
+                <c:pt idx="1475" formatCode="m/d/yyyy">
+                  <c:v>45666</c:v>
+                </c:pt>
+                <c:pt idx="1476" formatCode="m/d/yyyy">
+                  <c:v>45667</c:v>
+                </c:pt>
+                <c:pt idx="1477" formatCode="m/d/yyyy">
+                  <c:v>45668</c:v>
+                </c:pt>
+                <c:pt idx="1478" formatCode="m/d/yyyy">
+                  <c:v>45669</c:v>
+                </c:pt>
+                <c:pt idx="1479" formatCode="m/d/yyyy">
+                  <c:v>45670</c:v>
+                </c:pt>
+                <c:pt idx="1480" formatCode="m/d/yyyy">
+                  <c:v>45671</c:v>
+                </c:pt>
+                <c:pt idx="1481" formatCode="m/d/yyyy">
+                  <c:v>45672</c:v>
+                </c:pt>
+                <c:pt idx="1482" formatCode="m/d/yyyy">
+                  <c:v>45673</c:v>
+                </c:pt>
+                <c:pt idx="1483" formatCode="m/d/yyyy">
+                  <c:v>45674</c:v>
+                </c:pt>
+                <c:pt idx="1484" formatCode="m/d/yyyy">
+                  <c:v>45675</c:v>
+                </c:pt>
+                <c:pt idx="1485" formatCode="m/d/yyyy">
+                  <c:v>45676</c:v>
+                </c:pt>
+                <c:pt idx="1486" formatCode="m/d/yyyy">
+                  <c:v>45677</c:v>
+                </c:pt>
+                <c:pt idx="1487" formatCode="m/d/yyyy">
+                  <c:v>45678</c:v>
+                </c:pt>
+                <c:pt idx="1488" formatCode="m/d/yyyy">
+                  <c:v>45679</c:v>
+                </c:pt>
+                <c:pt idx="1489" formatCode="m/d/yyyy">
+                  <c:v>45680</c:v>
+                </c:pt>
+                <c:pt idx="1490" formatCode="m/d/yyyy">
+                  <c:v>45681</c:v>
+                </c:pt>
+                <c:pt idx="1491" formatCode="m/d/yyyy">
+                  <c:v>45682</c:v>
+                </c:pt>
+                <c:pt idx="1492" formatCode="m/d/yyyy">
+                  <c:v>45683</c:v>
+                </c:pt>
+                <c:pt idx="1493" formatCode="m/d/yyyy">
+                  <c:v>45684</c:v>
+                </c:pt>
+                <c:pt idx="1494" formatCode="m/d/yyyy">
+                  <c:v>45685</c:v>
+                </c:pt>
+                <c:pt idx="1495" formatCode="m/d/yyyy">
+                  <c:v>45686</c:v>
+                </c:pt>
+                <c:pt idx="1496" formatCode="m/d/yyyy">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="1497" formatCode="m/d/yyyy">
+                  <c:v>45688</c:v>
+                </c:pt>
+                <c:pt idx="1498" formatCode="m/d/yyyy">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="1499" formatCode="m/d/yyyy">
+                  <c:v>45690</c:v>
+                </c:pt>
+                <c:pt idx="1500" formatCode="m/d/yyyy">
+                  <c:v>45691</c:v>
+                </c:pt>
+                <c:pt idx="1501" formatCode="m/d/yyyy">
+                  <c:v>45692</c:v>
+                </c:pt>
+                <c:pt idx="1502" formatCode="m/d/yyyy">
+                  <c:v>45693</c:v>
+                </c:pt>
+                <c:pt idx="1503" formatCode="m/d/yyyy">
+                  <c:v>45694</c:v>
+                </c:pt>
+                <c:pt idx="1504" formatCode="m/d/yyyy">
+                  <c:v>45695</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>weight!$B$2:$B$1402</c:f>
+              <c:f>weight!$B$2:$B$1506</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="1401"/>
+                <c:ptCount val="1505"/>
                 <c:pt idx="0">
                   <c:v>217</c:v>
                 </c:pt>
@@ -12243,6 +12556,318 @@
                 </c:pt>
                 <c:pt idx="1400" formatCode="General">
                   <c:v>225.9</c:v>
+                </c:pt>
+                <c:pt idx="1401" formatCode="General">
+                  <c:v>226.2</c:v>
+                </c:pt>
+                <c:pt idx="1402" formatCode="General">
+                  <c:v>225.5</c:v>
+                </c:pt>
+                <c:pt idx="1403" formatCode="General">
+                  <c:v>226.6</c:v>
+                </c:pt>
+                <c:pt idx="1404" formatCode="General">
+                  <c:v>225.6</c:v>
+                </c:pt>
+                <c:pt idx="1405" formatCode="General">
+                  <c:v>225.8</c:v>
+                </c:pt>
+                <c:pt idx="1406" formatCode="General">
+                  <c:v>224.8</c:v>
+                </c:pt>
+                <c:pt idx="1407" formatCode="General">
+                  <c:v>224.4</c:v>
+                </c:pt>
+                <c:pt idx="1408" formatCode="General">
+                  <c:v>224.3</c:v>
+                </c:pt>
+                <c:pt idx="1409" formatCode="General">
+                  <c:v>223.8</c:v>
+                </c:pt>
+                <c:pt idx="1410" formatCode="General">
+                  <c:v>225.2</c:v>
+                </c:pt>
+                <c:pt idx="1411" formatCode="General">
+                  <c:v>225.2</c:v>
+                </c:pt>
+                <c:pt idx="1412" formatCode="General">
+                  <c:v>224.4</c:v>
+                </c:pt>
+                <c:pt idx="1413" formatCode="General">
+                  <c:v>224.3</c:v>
+                </c:pt>
+                <c:pt idx="1414" formatCode="General">
+                  <c:v>224.4</c:v>
+                </c:pt>
+                <c:pt idx="1415" formatCode="General">
+                  <c:v>225.1</c:v>
+                </c:pt>
+                <c:pt idx="1416" formatCode="General">
+                  <c:v>224.8</c:v>
+                </c:pt>
+                <c:pt idx="1417" formatCode="General">
+                  <c:v>224.4</c:v>
+                </c:pt>
+                <c:pt idx="1418" formatCode="General">
+                  <c:v>224.3</c:v>
+                </c:pt>
+                <c:pt idx="1419" formatCode="General">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="1420" formatCode="General">
+                  <c:v>223.3</c:v>
+                </c:pt>
+                <c:pt idx="1421" formatCode="General">
+                  <c:v>223.2</c:v>
+                </c:pt>
+                <c:pt idx="1422" formatCode="General">
+                  <c:v>223.1</c:v>
+                </c:pt>
+                <c:pt idx="1423" formatCode="General">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="1424" formatCode="General">
+                  <c:v>222.9</c:v>
+                </c:pt>
+                <c:pt idx="1425" formatCode="General">
+                  <c:v>222.6</c:v>
+                </c:pt>
+                <c:pt idx="1426" formatCode="General">
+                  <c:v>221.7</c:v>
+                </c:pt>
+                <c:pt idx="1427" formatCode="General">
+                  <c:v>222.2</c:v>
+                </c:pt>
+                <c:pt idx="1428" formatCode="General">
+                  <c:v>222.3</c:v>
+                </c:pt>
+                <c:pt idx="1429" formatCode="General">
+                  <c:v>221.7</c:v>
+                </c:pt>
+                <c:pt idx="1430" formatCode="General">
+                  <c:v>221.7</c:v>
+                </c:pt>
+                <c:pt idx="1431" formatCode="General">
+                  <c:v>223.4</c:v>
+                </c:pt>
+                <c:pt idx="1432" formatCode="General">
+                  <c:v>222.8</c:v>
+                </c:pt>
+                <c:pt idx="1433" formatCode="General">
+                  <c:v>222.8</c:v>
+                </c:pt>
+                <c:pt idx="1434" formatCode="General">
+                  <c:v>222.8</c:v>
+                </c:pt>
+                <c:pt idx="1435" formatCode="General">
+                  <c:v>222.2</c:v>
+                </c:pt>
+                <c:pt idx="1436" formatCode="General">
+                  <c:v>221.9</c:v>
+                </c:pt>
+                <c:pt idx="1437" formatCode="General">
+                  <c:v>223.2</c:v>
+                </c:pt>
+                <c:pt idx="1438" formatCode="General">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="1439" formatCode="General">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="1440" formatCode="General">
+                  <c:v>221.8</c:v>
+                </c:pt>
+                <c:pt idx="1441" formatCode="General">
+                  <c:v>222.1</c:v>
+                </c:pt>
+                <c:pt idx="1442" formatCode="General">
+                  <c:v>221.6</c:v>
+                </c:pt>
+                <c:pt idx="1443" formatCode="General">
+                  <c:v>221.2</c:v>
+                </c:pt>
+                <c:pt idx="1444" formatCode="General">
+                  <c:v>220.3</c:v>
+                </c:pt>
+                <c:pt idx="1445" formatCode="General">
+                  <c:v>221.5</c:v>
+                </c:pt>
+                <c:pt idx="1446" formatCode="General">
+                  <c:v>222.4</c:v>
+                </c:pt>
+                <c:pt idx="1447" formatCode="General">
+                  <c:v>221.9</c:v>
+                </c:pt>
+                <c:pt idx="1448" formatCode="General">
+                  <c:v>221.9</c:v>
+                </c:pt>
+                <c:pt idx="1449" formatCode="General">
+                  <c:v>221.7</c:v>
+                </c:pt>
+                <c:pt idx="1450" formatCode="General">
+                  <c:v>220.6</c:v>
+                </c:pt>
+                <c:pt idx="1451" formatCode="General">
+                  <c:v>219.8</c:v>
+                </c:pt>
+                <c:pt idx="1452" formatCode="General">
+                  <c:v>220.1</c:v>
+                </c:pt>
+                <c:pt idx="1453" formatCode="General">
+                  <c:v>221.2</c:v>
+                </c:pt>
+                <c:pt idx="1454" formatCode="General">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="1455" formatCode="General">
+                  <c:v>220.1</c:v>
+                </c:pt>
+                <c:pt idx="1456" formatCode="General">
+                  <c:v>221.1</c:v>
+                </c:pt>
+                <c:pt idx="1457" formatCode="General">
+                  <c:v>219.4</c:v>
+                </c:pt>
+                <c:pt idx="1458" formatCode="General">
+                  <c:v>218.5</c:v>
+                </c:pt>
+                <c:pt idx="1459" formatCode="General">
+                  <c:v>219.5</c:v>
+                </c:pt>
+                <c:pt idx="1460" formatCode="General">
+                  <c:v>219.6</c:v>
+                </c:pt>
+                <c:pt idx="1461" formatCode="General">
+                  <c:v>218.9</c:v>
+                </c:pt>
+                <c:pt idx="1462" formatCode="General">
+                  <c:v>218.7</c:v>
+                </c:pt>
+                <c:pt idx="1463" formatCode="General">
+                  <c:v>219.6</c:v>
+                </c:pt>
+                <c:pt idx="1464" formatCode="General">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="1465" formatCode="General">
+                  <c:v>219.4</c:v>
+                </c:pt>
+                <c:pt idx="1466" formatCode="General">
+                  <c:v>220.1</c:v>
+                </c:pt>
+                <c:pt idx="1467" formatCode="General">
+                  <c:v>219.9</c:v>
+                </c:pt>
+                <c:pt idx="1468" formatCode="General">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="1469" formatCode="General">
+                  <c:v>218.5</c:v>
+                </c:pt>
+                <c:pt idx="1470" formatCode="General">
+                  <c:v>218.3</c:v>
+                </c:pt>
+                <c:pt idx="1471" formatCode="General">
+                  <c:v>218.1</c:v>
+                </c:pt>
+                <c:pt idx="1472" formatCode="General">
+                  <c:v>218.8</c:v>
+                </c:pt>
+                <c:pt idx="1473" formatCode="General">
+                  <c:v>218.9</c:v>
+                </c:pt>
+                <c:pt idx="1474" formatCode="General">
+                  <c:v>219.1</c:v>
+                </c:pt>
+                <c:pt idx="1475" formatCode="General">
+                  <c:v>218.7</c:v>
+                </c:pt>
+                <c:pt idx="1476" formatCode="General">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="1477" formatCode="General">
+                  <c:v>216.3</c:v>
+                </c:pt>
+                <c:pt idx="1478" formatCode="General">
+                  <c:v>217.6</c:v>
+                </c:pt>
+                <c:pt idx="1479" formatCode="General">
+                  <c:v>218.3</c:v>
+                </c:pt>
+                <c:pt idx="1480" formatCode="General">
+                  <c:v>217.5</c:v>
+                </c:pt>
+                <c:pt idx="1481" formatCode="General">
+                  <c:v>217.8</c:v>
+                </c:pt>
+                <c:pt idx="1482" formatCode="General">
+                  <c:v>216.7</c:v>
+                </c:pt>
+                <c:pt idx="1483" formatCode="General">
+                  <c:v>216.9</c:v>
+                </c:pt>
+                <c:pt idx="1484" formatCode="General">
+                  <c:v>216.5</c:v>
+                </c:pt>
+                <c:pt idx="1485" formatCode="General">
+                  <c:v>217.3</c:v>
+                </c:pt>
+                <c:pt idx="1486" formatCode="General">
+                  <c:v>218.3</c:v>
+                </c:pt>
+                <c:pt idx="1487" formatCode="General">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="1488" formatCode="General">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="1489" formatCode="General">
+                  <c:v>216.6</c:v>
+                </c:pt>
+                <c:pt idx="1490" formatCode="General">
+                  <c:v>217.4</c:v>
+                </c:pt>
+                <c:pt idx="1491" formatCode="General">
+                  <c:v>217.6</c:v>
+                </c:pt>
+                <c:pt idx="1492" formatCode="General">
+                  <c:v>217.2</c:v>
+                </c:pt>
+                <c:pt idx="1493" formatCode="General">
+                  <c:v>216.4</c:v>
+                </c:pt>
+                <c:pt idx="1494" formatCode="General">
+                  <c:v>216.2</c:v>
+                </c:pt>
+                <c:pt idx="1495" formatCode="General">
+                  <c:v>217.3</c:v>
+                </c:pt>
+                <c:pt idx="1496" formatCode="General">
+                  <c:v>216.6</c:v>
+                </c:pt>
+                <c:pt idx="1497" formatCode="General">
+                  <c:v>216.1</c:v>
+                </c:pt>
+                <c:pt idx="1498" formatCode="General">
+                  <c:v>216.5</c:v>
+                </c:pt>
+                <c:pt idx="1499" formatCode="General">
+                  <c:v>217.2</c:v>
+                </c:pt>
+                <c:pt idx="1500" formatCode="General">
+                  <c:v>216.4</c:v>
+                </c:pt>
+                <c:pt idx="1501" formatCode="General">
+                  <c:v>216.5</c:v>
+                </c:pt>
+                <c:pt idx="1502" formatCode="General">
+                  <c:v>216.3</c:v>
+                </c:pt>
+                <c:pt idx="1503" formatCode="General">
+                  <c:v>215.9</c:v>
+                </c:pt>
+                <c:pt idx="1504" formatCode="General">
+                  <c:v>215.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14368,10 +14993,10 @@
       <xdr:rowOff>119061</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>72</xdr:col>
-      <xdr:colOff>419099</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14732,11 +15357,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1402"/>
+  <dimension ref="A1:F1506"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -40520,6 +41146,838 @@
         <v>225.9</v>
       </c>
     </row>
+    <row r="1403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1403" s="8">
+        <v>45576</v>
+      </c>
+      <c r="B1403">
+        <v>226.2</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1404" s="8">
+        <v>45577</v>
+      </c>
+      <c r="B1404">
+        <v>225.5</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1405" s="8">
+        <v>45578</v>
+      </c>
+      <c r="B1405">
+        <v>226.6</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1406" s="8">
+        <v>45580</v>
+      </c>
+      <c r="B1406">
+        <v>225.6</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1407" s="8">
+        <v>45581</v>
+      </c>
+      <c r="B1407">
+        <v>225.8</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1408" s="8">
+        <v>45582</v>
+      </c>
+      <c r="B1408">
+        <v>224.8</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1409" s="14">
+        <v>45583</v>
+      </c>
+      <c r="B1409">
+        <v>224.4</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1410" s="14">
+        <v>45584</v>
+      </c>
+      <c r="B1410">
+        <v>224.3</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1411" s="14">
+        <v>45585</v>
+      </c>
+      <c r="B1411">
+        <v>223.8</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1412" s="14">
+        <v>45586</v>
+      </c>
+      <c r="B1412">
+        <v>225.2</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1413" s="14">
+        <v>45588</v>
+      </c>
+      <c r="B1413">
+        <v>225.2</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1414" s="14">
+        <v>45589</v>
+      </c>
+      <c r="B1414">
+        <v>224.4</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1415" s="14">
+        <v>45590</v>
+      </c>
+      <c r="B1415">
+        <v>224.3</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1416" s="14">
+        <v>45591</v>
+      </c>
+      <c r="B1416">
+        <v>224.4</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1417" s="14">
+        <v>45592</v>
+      </c>
+      <c r="B1417">
+        <v>225.1</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1418" s="14">
+        <v>45593</v>
+      </c>
+      <c r="B1418">
+        <v>224.8</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1419" s="14">
+        <v>45594</v>
+      </c>
+      <c r="B1419">
+        <v>224.4</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1420" s="14">
+        <v>45595</v>
+      </c>
+      <c r="B1420">
+        <v>224.3</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1421" s="14">
+        <v>45596</v>
+      </c>
+      <c r="B1421">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1422" s="14">
+        <v>45597</v>
+      </c>
+      <c r="B1422">
+        <v>223.3</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1423" s="14">
+        <v>45598</v>
+      </c>
+      <c r="B1423">
+        <v>223.2</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1424" s="14">
+        <v>45599</v>
+      </c>
+      <c r="B1424">
+        <v>223.1</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1425" s="14">
+        <v>45599</v>
+      </c>
+      <c r="B1425">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1426" s="14">
+        <v>45600</v>
+      </c>
+      <c r="B1426">
+        <v>222.9</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1427" s="14">
+        <v>45601</v>
+      </c>
+      <c r="B1427">
+        <v>222.6</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1428" s="14">
+        <v>45602</v>
+      </c>
+      <c r="B1428">
+        <v>221.7</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1429" s="14">
+        <v>45603</v>
+      </c>
+      <c r="B1429">
+        <v>222.2</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1430" s="14">
+        <v>45604</v>
+      </c>
+      <c r="B1430">
+        <v>222.3</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1431" s="14">
+        <v>45605</v>
+      </c>
+      <c r="B1431">
+        <v>221.7</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1432" s="14">
+        <v>45606</v>
+      </c>
+      <c r="B1432">
+        <v>221.7</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1433" s="14">
+        <v>45607</v>
+      </c>
+      <c r="B1433">
+        <v>223.4</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1434" s="14">
+        <v>45610</v>
+      </c>
+      <c r="B1434">
+        <v>222.8</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1435" s="14">
+        <v>45610</v>
+      </c>
+      <c r="B1435">
+        <v>222.8</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1436" s="14">
+        <v>45610</v>
+      </c>
+      <c r="B1436">
+        <v>222.8</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1437" s="14">
+        <v>45611</v>
+      </c>
+      <c r="B1437">
+        <v>222.2</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1438" s="14">
+        <v>45612</v>
+      </c>
+      <c r="B1438">
+        <v>221.9</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1439" s="14">
+        <v>45613</v>
+      </c>
+      <c r="B1439">
+        <v>223.2</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1440" s="14">
+        <v>45615</v>
+      </c>
+      <c r="B1440">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1441" s="14">
+        <v>45616</v>
+      </c>
+      <c r="B1441">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1442" s="14">
+        <v>45617</v>
+      </c>
+      <c r="B1442">
+        <v>221.8</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1443" s="14">
+        <v>45618</v>
+      </c>
+      <c r="B1443">
+        <v>222.1</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1444" s="14">
+        <v>45619</v>
+      </c>
+      <c r="B1444">
+        <v>221.6</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1445" s="14">
+        <v>45619</v>
+      </c>
+      <c r="B1445">
+        <v>221.2</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1446" s="14">
+        <v>45620</v>
+      </c>
+      <c r="B1446">
+        <v>220.3</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1447" s="14">
+        <v>45621</v>
+      </c>
+      <c r="B1447">
+        <v>221.5</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1448" s="14">
+        <v>45622</v>
+      </c>
+      <c r="B1448">
+        <v>222.4</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1449" s="14">
+        <v>45628</v>
+      </c>
+      <c r="B1449">
+        <v>221.9</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1450" s="14">
+        <v>45629</v>
+      </c>
+      <c r="B1450">
+        <v>221.9</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1451" s="14">
+        <v>45630</v>
+      </c>
+      <c r="B1451">
+        <v>221.7</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1452" s="14">
+        <v>45631</v>
+      </c>
+      <c r="B1452">
+        <v>220.6</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1453" s="14">
+        <v>45632</v>
+      </c>
+      <c r="B1453">
+        <v>219.8</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1454" s="14">
+        <v>45633</v>
+      </c>
+      <c r="B1454">
+        <v>220.1</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1455" s="14">
+        <v>45634</v>
+      </c>
+      <c r="B1455">
+        <v>221.2</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1456" s="14">
+        <v>45635</v>
+      </c>
+      <c r="B1456">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1457" s="14">
+        <v>45636</v>
+      </c>
+      <c r="B1457">
+        <v>220.1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1458" s="14">
+        <v>45637</v>
+      </c>
+      <c r="B1458">
+        <v>221.1</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1459" s="14">
+        <v>45638</v>
+      </c>
+      <c r="B1459">
+        <v>219.4</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1460" s="14">
+        <v>45639</v>
+      </c>
+      <c r="B1460">
+        <v>218.5</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1461" s="14">
+        <v>45640</v>
+      </c>
+      <c r="B1461">
+        <v>219.5</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1462" s="14">
+        <v>45641</v>
+      </c>
+      <c r="B1462">
+        <v>219.6</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1463" s="14">
+        <v>45642</v>
+      </c>
+      <c r="B1463">
+        <v>218.9</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1464" s="14">
+        <v>45643</v>
+      </c>
+      <c r="B1464">
+        <v>218.7</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1465" s="14">
+        <v>45653</v>
+      </c>
+      <c r="B1465">
+        <v>219.6</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1466" s="14">
+        <v>45654</v>
+      </c>
+      <c r="B1466">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1467" s="14">
+        <v>45655</v>
+      </c>
+      <c r="B1467">
+        <v>219.4</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1468" s="14">
+        <v>45656</v>
+      </c>
+      <c r="B1468">
+        <v>220.1</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1469" s="14">
+        <v>45657</v>
+      </c>
+      <c r="B1469">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1470" s="14">
+        <v>45659</v>
+      </c>
+      <c r="B1470">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1471" s="14">
+        <v>45660</v>
+      </c>
+      <c r="B1471">
+        <v>218.5</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1472" s="14">
+        <v>45661</v>
+      </c>
+      <c r="B1472">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1473" s="14">
+        <v>45662</v>
+      </c>
+      <c r="B1473">
+        <v>218.1</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1474" s="14">
+        <v>45663</v>
+      </c>
+      <c r="B1474">
+        <v>218.8</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1475" s="14">
+        <v>45664</v>
+      </c>
+      <c r="B1475">
+        <v>218.9</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1476" s="14">
+        <v>45665</v>
+      </c>
+      <c r="B1476">
+        <v>219.1</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1477" s="14">
+        <v>45666</v>
+      </c>
+      <c r="B1477">
+        <v>218.7</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1478" s="14">
+        <v>45667</v>
+      </c>
+      <c r="B1478">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1479" s="14">
+        <v>45668</v>
+      </c>
+      <c r="B1479">
+        <v>216.3</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1480" s="14">
+        <v>45669</v>
+      </c>
+      <c r="B1480">
+        <v>217.6</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1481" s="14">
+        <v>45670</v>
+      </c>
+      <c r="B1481">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1482" s="14">
+        <v>45671</v>
+      </c>
+      <c r="B1482">
+        <v>217.5</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1483" s="14">
+        <v>45672</v>
+      </c>
+      <c r="B1483">
+        <v>217.8</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1484" s="14">
+        <v>45673</v>
+      </c>
+      <c r="B1484">
+        <v>216.7</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1485" s="14">
+        <v>45674</v>
+      </c>
+      <c r="B1485">
+        <v>216.9</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1486" s="14">
+        <v>45675</v>
+      </c>
+      <c r="B1486">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1487" s="14">
+        <v>45676</v>
+      </c>
+      <c r="B1487">
+        <v>217.3</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1488" s="14">
+        <v>45677</v>
+      </c>
+      <c r="B1488">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1489" s="14">
+        <v>45678</v>
+      </c>
+      <c r="B1489">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1490" s="14">
+        <v>45679</v>
+      </c>
+      <c r="B1490">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1491" s="14">
+        <v>45680</v>
+      </c>
+      <c r="B1491">
+        <v>216.6</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1492" s="14">
+        <v>45681</v>
+      </c>
+      <c r="B1492">
+        <v>217.4</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1493" s="14">
+        <v>45682</v>
+      </c>
+      <c r="B1493">
+        <v>217.6</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1494" s="14">
+        <v>45683</v>
+      </c>
+      <c r="B1494">
+        <v>217.2</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1495" s="14">
+        <v>45684</v>
+      </c>
+      <c r="B1495">
+        <v>216.4</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1496" s="14">
+        <v>45685</v>
+      </c>
+      <c r="B1496">
+        <v>216.2</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1497" s="14">
+        <v>45686</v>
+      </c>
+      <c r="B1497">
+        <v>217.3</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1498" s="14">
+        <v>45687</v>
+      </c>
+      <c r="B1498">
+        <v>216.6</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1499" s="14">
+        <v>45688</v>
+      </c>
+      <c r="B1499">
+        <v>216.1</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1500" s="14">
+        <v>45689</v>
+      </c>
+      <c r="B1500">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1501" s="14">
+        <v>45690</v>
+      </c>
+      <c r="B1501">
+        <v>217.2</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1502" s="14">
+        <v>45691</v>
+      </c>
+      <c r="B1502">
+        <v>216.4</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1503" s="14">
+        <v>45692</v>
+      </c>
+      <c r="B1503">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1504" s="14">
+        <v>45693</v>
+      </c>
+      <c r="B1504">
+        <v>216.3</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1505" s="14">
+        <v>45694</v>
+      </c>
+      <c r="B1505">
+        <v>215.9</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1506" s="14">
+        <v>45695</v>
+      </c>
+      <c r="B1506">
+        <v>215.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
